--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121126478</v>
+        <v>121125770</v>
       </c>
       <c r="B17" t="n">
-        <v>90705</v>
+        <v>78598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459368</v>
+        <v>459416</v>
       </c>
       <c r="R17" t="n">
-        <v>6987043</v>
+        <v>6986950</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121128528</v>
+        <v>121126478</v>
       </c>
       <c r="B18" t="n">
         <v>90705</v>
@@ -2524,17 +2524,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459225</v>
+        <v>459368</v>
       </c>
       <c r="R18" t="n">
-        <v>6987105</v>
+        <v>6987043</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121125770</v>
+        <v>121128528</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>90705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459416</v>
+        <v>459225</v>
       </c>
       <c r="R19" t="n">
-        <v>6986950</v>
+        <v>6987105</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210323</v>
+        <v>121210351</v>
       </c>
       <c r="B23" t="n">
-        <v>57364</v>
+        <v>90687</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,38 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459198</v>
+        <v>459109</v>
       </c>
       <c r="R23" t="n">
-        <v>6987270</v>
+        <v>6987053</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3127,11 +3123,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210351</v>
+        <v>121210323</v>
       </c>
       <c r="B24" t="n">
-        <v>90687</v>
+        <v>57364</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,34 +3165,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459109</v>
+        <v>459198</v>
       </c>
       <c r="R24" t="n">
-        <v>6987053</v>
+        <v>6987270</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3234,6 +3229,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4586,10 +4586,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210326</v>
+        <v>121210344</v>
       </c>
       <c r="B38" t="n">
-        <v>98071</v>
+        <v>74697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4598,25 +4598,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459248</v>
+        <v>459384</v>
       </c>
       <c r="R38" t="n">
-        <v>6987371</v>
+        <v>6986948</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210344</v>
+        <v>121210333</v>
       </c>
       <c r="B39" t="n">
-        <v>74697</v>
+        <v>74696</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459384</v>
+        <v>459276</v>
       </c>
       <c r="R39" t="n">
-        <v>6986948</v>
+        <v>6987463</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210333</v>
+        <v>121210328</v>
       </c>
       <c r="B40" t="n">
-        <v>74696</v>
+        <v>90705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459276</v>
+        <v>459363</v>
       </c>
       <c r="R40" t="n">
-        <v>6987463</v>
+        <v>6987053</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210328</v>
+        <v>121210329</v>
       </c>
       <c r="B41" t="n">
         <v>90705</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459363</v>
+        <v>459208</v>
       </c>
       <c r="R41" t="n">
-        <v>6987053</v>
+        <v>6987442</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210329</v>
+        <v>121210336</v>
       </c>
       <c r="B42" t="n">
-        <v>90705</v>
+        <v>74705</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459208</v>
+        <v>459289</v>
       </c>
       <c r="R42" t="n">
-        <v>6987442</v>
+        <v>6987454</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210336</v>
+        <v>121210326</v>
       </c>
       <c r="B43" t="n">
-        <v>74705</v>
+        <v>98071</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5108,25 +5108,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459289</v>
+        <v>459248</v>
       </c>
       <c r="R43" t="n">
-        <v>6987454</v>
+        <v>6987371</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227091</v>
+        <v>121227109</v>
       </c>
       <c r="B57" t="n">
-        <v>74697</v>
+        <v>82382</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459295</v>
+        <v>459277</v>
       </c>
       <c r="R57" t="n">
-        <v>6987078</v>
+        <v>6987050</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227109</v>
+        <v>121227091</v>
       </c>
       <c r="B58" t="n">
-        <v>82382</v>
+        <v>74697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459277</v>
+        <v>459295</v>
       </c>
       <c r="R58" t="n">
-        <v>6987050</v>
+        <v>6987078</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227102</v>
+        <v>121227113</v>
       </c>
       <c r="B86" t="n">
-        <v>90687</v>
+        <v>74696</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9546,38 +9546,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459461</v>
+        <v>459280</v>
       </c>
       <c r="R86" t="n">
-        <v>6987117</v>
+        <v>6987044</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9612,12 +9615,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9636,7 +9645,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227103</v>
+        <v>121227102</v>
       </c>
       <c r="B87" t="n">
         <v>90687</v>
@@ -9676,10 +9685,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459515</v>
+        <v>459461</v>
       </c>
       <c r="R87" t="n">
-        <v>6987120</v>
+        <v>6987117</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9738,10 +9747,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227135</v>
+        <v>121227103</v>
       </c>
       <c r="B88" t="n">
-        <v>57348</v>
+        <v>90687</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9754,42 +9763,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459252</v>
+        <v>459515</v>
       </c>
       <c r="R88" t="n">
-        <v>6987032</v>
+        <v>6987120</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9822,11 +9823,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9853,10 +9849,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227113</v>
+        <v>121227135</v>
       </c>
       <c r="B89" t="n">
-        <v>74696</v>
+        <v>57348</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9865,30 +9861,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9896,10 +9897,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459280</v>
+        <v>459252</v>
       </c>
       <c r="R89" t="n">
-        <v>6987044</v>
+        <v>6987032</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9936,7 +9937,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9945,7 +9946,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120971712</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>120972218</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120971669</v>
+        <v>120975648</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,19 +933,22 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459573</v>
+        <v>459597</v>
       </c>
       <c r="R4" t="n">
-        <v>6987191</v>
+        <v>6987210</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,27 +975,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975648</v>
+        <v>120972337</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,22 +1039,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459597</v>
+        <v>459550</v>
       </c>
       <c r="R5" t="n">
-        <v>6987210</v>
+        <v>6986963</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,18 +1078,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>120972401</v>
       </c>
       <c r="B6" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120972337</v>
+        <v>120971669</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,14 +1265,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459550</v>
+        <v>459573</v>
       </c>
       <c r="R7" t="n">
-        <v>6986963</v>
+        <v>6987191</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121131481</v>
+        <v>121126083</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,50 +1353,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459308</v>
+        <v>459373</v>
       </c>
       <c r="R8" t="n">
-        <v>6987012</v>
+        <v>6986932</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121128967</v>
+        <v>121125621</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,41 +1465,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459193</v>
+        <v>459423</v>
       </c>
       <c r="R9" t="n">
-        <v>6987308</v>
+        <v>6986917</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
         <v>121125668</v>
       </c>
       <c r="B10" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121125621</v>
+        <v>121128992</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,47 +1698,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459423</v>
+        <v>459186</v>
       </c>
       <c r="R11" t="n">
-        <v>6986917</v>
+        <v>6987297</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1770,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121126083</v>
+        <v>121125770</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459373</v>
+        <v>459416</v>
       </c>
       <c r="R12" t="n">
-        <v>6986932</v>
+        <v>6986950</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121126591</v>
+        <v>121126478</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,50 +1922,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459352</v>
+        <v>459368</v>
       </c>
       <c r="R13" t="n">
-        <v>6987044</v>
+        <v>6987043</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2003,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121127849</v>
+        <v>121128528</v>
       </c>
       <c r="B14" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459274</v>
+        <v>459225</v>
       </c>
       <c r="R14" t="n">
-        <v>6987068</v>
+        <v>6987105</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2115,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121128992</v>
+        <v>121131481</v>
       </c>
       <c r="B15" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,41 +2146,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459186</v>
+        <v>459308</v>
       </c>
       <c r="R15" t="n">
-        <v>6987297</v>
+        <v>6987012</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2258,7 @@
         <v>121125947</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121125770</v>
+        <v>121125895</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,41 +2379,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459416</v>
+        <v>459413</v>
       </c>
       <c r="R17" t="n">
-        <v>6986950</v>
+        <v>6986953</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121126478</v>
+        <v>121129187</v>
       </c>
       <c r="B18" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,13 +2528,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459368</v>
+        <v>459243</v>
       </c>
       <c r="R18" t="n">
-        <v>6987043</v>
+        <v>6987320</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121128528</v>
+        <v>121128967</v>
       </c>
       <c r="B19" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,17 +2636,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459225</v>
+        <v>459193</v>
       </c>
       <c r="R19" t="n">
-        <v>6987105</v>
+        <v>6987308</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121129187</v>
+        <v>121126591</v>
       </c>
       <c r="B20" t="n">
-        <v>90705</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,41 +2724,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459243</v>
+        <v>459352</v>
       </c>
       <c r="R20" t="n">
-        <v>6987320</v>
+        <v>6987044</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121125895</v>
+        <v>121127849</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>90715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,50 +2845,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459413</v>
+        <v>459274</v>
       </c>
       <c r="R21" t="n">
-        <v>6986953</v>
+        <v>6987068</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210324</v>
+        <v>121210331</v>
       </c>
       <c r="B22" t="n">
-        <v>91343</v>
+        <v>74699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>898</v>
+        <v>492</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459250</v>
+        <v>459255</v>
       </c>
       <c r="R22" t="n">
-        <v>6987362</v>
+        <v>6987011</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3050,7 +3050,7 @@
         <v>121210351</v>
       </c>
       <c r="B23" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210323</v>
+        <v>121210317</v>
       </c>
       <c r="B24" t="n">
-        <v>57364</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,42 +3161,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459198</v>
+        <v>459209</v>
       </c>
       <c r="R24" t="n">
-        <v>6987270</v>
+        <v>6986978</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3229,11 +3225,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210334</v>
+        <v>121210330</v>
       </c>
       <c r="B25" t="n">
-        <v>74705</v>
+        <v>74699</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,38 +3263,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459371</v>
+        <v>459263</v>
       </c>
       <c r="R25" t="n">
-        <v>6987042</v>
+        <v>6987015</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3338,12 +3332,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210312</v>
+        <v>121210346</v>
       </c>
       <c r="B26" t="n">
-        <v>74689</v>
+        <v>74700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459362</v>
+        <v>459235</v>
       </c>
       <c r="R26" t="n">
-        <v>6987057</v>
+        <v>6987465</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210335</v>
+        <v>121210328</v>
       </c>
       <c r="B27" t="n">
-        <v>74705</v>
+        <v>90715</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459344</v>
+        <v>459363</v>
       </c>
       <c r="R27" t="n">
-        <v>6987093</v>
+        <v>6987053</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210331</v>
+        <v>121210315</v>
       </c>
       <c r="B28" t="n">
-        <v>74696</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,38 +3578,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459255</v>
+        <v>459269</v>
       </c>
       <c r="R28" t="n">
-        <v>6987011</v>
+        <v>6987021</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3642,6 +3646,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210360</v>
+        <v>121210312</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>74692</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3680,25 +3689,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3708,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459359</v>
+        <v>459362</v>
       </c>
       <c r="R29" t="n">
-        <v>6987446</v>
+        <v>6987057</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3770,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210347</v>
+        <v>121210355</v>
       </c>
       <c r="B30" t="n">
-        <v>74697</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3786,21 +3795,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3810,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459274</v>
+        <v>459361</v>
       </c>
       <c r="R30" t="n">
-        <v>6987465</v>
+        <v>6986994</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3872,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210356</v>
+        <v>121210324</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>91353</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3884,25 +3893,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459060</v>
+        <v>459250</v>
       </c>
       <c r="R31" t="n">
-        <v>6987110</v>
+        <v>6987362</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3974,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210352</v>
+        <v>121210356</v>
       </c>
       <c r="B32" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3990,21 +3999,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4014,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459272</v>
+        <v>459060</v>
       </c>
       <c r="R32" t="n">
-        <v>6987314</v>
+        <v>6987110</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4076,10 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210318</v>
+        <v>121210323</v>
       </c>
       <c r="B33" t="n">
-        <v>90973</v>
+        <v>57367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4092,34 +4101,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459210</v>
+        <v>459198</v>
       </c>
       <c r="R33" t="n">
-        <v>6986977</v>
+        <v>6987270</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4152,6 +4165,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4178,10 +4196,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210320</v>
+        <v>121210345</v>
       </c>
       <c r="B34" t="n">
-        <v>82382</v>
+        <v>74700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4194,21 +4212,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,10 +4236,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459321</v>
+        <v>459225</v>
       </c>
       <c r="R34" t="n">
-        <v>6987092</v>
+        <v>6987464</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4280,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210354</v>
+        <v>121210350</v>
       </c>
       <c r="B35" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4296,21 +4314,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4320,10 +4338,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459368</v>
+        <v>459166</v>
       </c>
       <c r="R35" t="n">
-        <v>6986963</v>
+        <v>6987016</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4382,10 +4400,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210325</v>
+        <v>121210329</v>
       </c>
       <c r="B36" t="n">
-        <v>98071</v>
+        <v>90715</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4394,25 +4412,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4422,10 +4440,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459361</v>
+        <v>459208</v>
       </c>
       <c r="R36" t="n">
-        <v>6986971</v>
+        <v>6987442</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4484,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210355</v>
+        <v>121210333</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>74699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4496,25 +4514,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4524,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459361</v>
+        <v>459276</v>
       </c>
       <c r="R37" t="n">
-        <v>6986994</v>
+        <v>6987463</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4586,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210344</v>
+        <v>121210321</v>
       </c>
       <c r="B38" t="n">
-        <v>74697</v>
+        <v>82385</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4602,21 +4620,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4626,10 +4644,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459384</v>
+        <v>459138</v>
       </c>
       <c r="R38" t="n">
-        <v>6986948</v>
+        <v>6987016</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4688,10 +4706,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210333</v>
+        <v>121210326</v>
       </c>
       <c r="B39" t="n">
-        <v>74696</v>
+        <v>98081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4704,21 +4722,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459276</v>
+        <v>459248</v>
       </c>
       <c r="R39" t="n">
-        <v>6987463</v>
+        <v>6987371</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4790,10 +4808,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210328</v>
+        <v>121210327</v>
       </c>
       <c r="B40" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4830,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459363</v>
+        <v>459368</v>
       </c>
       <c r="R40" t="n">
-        <v>6987053</v>
+        <v>6986960</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4892,10 +4910,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210329</v>
+        <v>121210319</v>
       </c>
       <c r="B41" t="n">
-        <v>90705</v>
+        <v>57504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4908,21 +4926,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4932,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459208</v>
+        <v>459169</v>
       </c>
       <c r="R41" t="n">
-        <v>6987442</v>
+        <v>6987016</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4994,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210336</v>
+        <v>121210360</v>
       </c>
       <c r="B42" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5010,21 +5028,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5034,10 +5052,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459289</v>
+        <v>459359</v>
       </c>
       <c r="R42" t="n">
-        <v>6987454</v>
+        <v>6987446</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5096,10 +5114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210326</v>
+        <v>121210336</v>
       </c>
       <c r="B43" t="n">
-        <v>98071</v>
+        <v>74708</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5108,25 +5126,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5136,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459248</v>
+        <v>459289</v>
       </c>
       <c r="R43" t="n">
-        <v>6987371</v>
+        <v>6987454</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5198,10 +5216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210345</v>
+        <v>121210352</v>
       </c>
       <c r="B44" t="n">
-        <v>74697</v>
+        <v>90697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5214,21 +5232,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5256,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459225</v>
+        <v>459272</v>
       </c>
       <c r="R44" t="n">
-        <v>6987464</v>
+        <v>6987314</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5300,10 +5318,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210317</v>
+        <v>121210313</v>
       </c>
       <c r="B45" t="n">
-        <v>79715</v>
+        <v>95628</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5312,25 +5330,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5340,10 +5358,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459209</v>
+        <v>459274</v>
       </c>
       <c r="R45" t="n">
-        <v>6986978</v>
+        <v>6987056</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5402,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210350</v>
+        <v>121210316</v>
       </c>
       <c r="B46" t="n">
-        <v>90687</v>
+        <v>90693</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5418,21 +5436,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5442,10 +5460,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459166</v>
+        <v>459238</v>
       </c>
       <c r="R46" t="n">
-        <v>6987016</v>
+        <v>6986977</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5504,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210346</v>
+        <v>121210325</v>
       </c>
       <c r="B47" t="n">
-        <v>74697</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5516,25 +5534,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459235</v>
+        <v>459361</v>
       </c>
       <c r="R47" t="n">
-        <v>6987465</v>
+        <v>6986971</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5606,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210316</v>
+        <v>121210354</v>
       </c>
       <c r="B48" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5622,21 +5640,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5646,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459238</v>
+        <v>459368</v>
       </c>
       <c r="R48" t="n">
-        <v>6986977</v>
+        <v>6986963</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5708,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210319</v>
+        <v>121210344</v>
       </c>
       <c r="B49" t="n">
-        <v>57501</v>
+        <v>74700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5724,21 +5742,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5748,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459169</v>
+        <v>459384</v>
       </c>
       <c r="R49" t="n">
-        <v>6987016</v>
+        <v>6986948</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5810,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210313</v>
+        <v>121210334</v>
       </c>
       <c r="B50" t="n">
-        <v>95618</v>
+        <v>74708</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5826,21 +5844,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5850,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459274</v>
+        <v>459371</v>
       </c>
       <c r="R50" t="n">
-        <v>6987056</v>
+        <v>6987042</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5912,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210327</v>
+        <v>121210335</v>
       </c>
       <c r="B51" t="n">
-        <v>90705</v>
+        <v>74708</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5928,21 +5946,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5952,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459368</v>
+        <v>459344</v>
       </c>
       <c r="R51" t="n">
-        <v>6986960</v>
+        <v>6987093</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6014,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210315</v>
+        <v>121210318</v>
       </c>
       <c r="B52" t="n">
-        <v>57348</v>
+        <v>90983</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6030,38 +6048,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459269</v>
+        <v>459210</v>
       </c>
       <c r="R52" t="n">
-        <v>6987021</v>
+        <v>6986977</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6094,11 +6108,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6125,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210321</v>
+        <v>121210320</v>
       </c>
       <c r="B53" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6165,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459138</v>
+        <v>459321</v>
       </c>
       <c r="R53" t="n">
-        <v>6987016</v>
+        <v>6987092</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6227,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210330</v>
+        <v>121210347</v>
       </c>
       <c r="B54" t="n">
-        <v>74696</v>
+        <v>74700</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6239,41 +6248,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459263</v>
+        <v>459274</v>
       </c>
       <c r="R54" t="n">
-        <v>6987015</v>
+        <v>6987465</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6308,18 +6314,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227112</v>
+        <v>121227123</v>
       </c>
       <c r="B55" t="n">
-        <v>74696</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6350,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459315</v>
+        <v>458981</v>
       </c>
       <c r="R55" t="n">
-        <v>6987128</v>
+        <v>6987164</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227092</v>
+        <v>121227124</v>
       </c>
       <c r="B56" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459307</v>
+        <v>459222</v>
       </c>
       <c r="R56" t="n">
-        <v>6986981</v>
+        <v>6987047</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227109</v>
+        <v>121227111</v>
       </c>
       <c r="B57" t="n">
-        <v>82382</v>
+        <v>74699</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6554,25 +6554,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459277</v>
+        <v>459244</v>
       </c>
       <c r="R57" t="n">
-        <v>6987050</v>
+        <v>6987057</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227091</v>
+        <v>121227102</v>
       </c>
       <c r="B58" t="n">
-        <v>74697</v>
+        <v>90697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459295</v>
+        <v>459461</v>
       </c>
       <c r="R58" t="n">
-        <v>6987078</v>
+        <v>6987117</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227110</v>
+        <v>121227088</v>
       </c>
       <c r="B59" t="n">
-        <v>74696</v>
+        <v>74692</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6758,25 +6758,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>492</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459494</v>
+        <v>459493</v>
       </c>
       <c r="R59" t="n">
         <v>6987097</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227122</v>
+        <v>121227116</v>
       </c>
       <c r="B60" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459010</v>
+        <v>459437</v>
       </c>
       <c r="R60" t="n">
-        <v>6987146</v>
+        <v>6987156</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227136</v>
+        <v>121227120</v>
       </c>
       <c r="B61" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,42 +6966,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459339</v>
+        <v>459057</v>
       </c>
       <c r="R61" t="n">
-        <v>6986928</v>
+        <v>6987082</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7034,11 +7026,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7065,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227104</v>
+        <v>121227126</v>
       </c>
       <c r="B62" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7081,21 +7068,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7105,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459343</v>
+        <v>459333</v>
       </c>
       <c r="R62" t="n">
-        <v>6987095</v>
+        <v>6987132</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7167,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227094</v>
+        <v>121227129</v>
       </c>
       <c r="B63" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7183,21 +7170,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458978</v>
+        <v>459255</v>
       </c>
       <c r="R63" t="n">
-        <v>6987169</v>
+        <v>6987069</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7269,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227116</v>
+        <v>121227101</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7285,21 +7272,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7309,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459437</v>
+        <v>459430</v>
       </c>
       <c r="R64" t="n">
-        <v>6987156</v>
+        <v>6986932</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7371,10 +7358,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227129</v>
+        <v>121227121</v>
       </c>
       <c r="B65" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7411,10 +7398,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459255</v>
+        <v>459050</v>
       </c>
       <c r="R65" t="n">
-        <v>6987069</v>
+        <v>6987112</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7473,10 +7460,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227098</v>
+        <v>121227113</v>
       </c>
       <c r="B66" t="n">
-        <v>90705</v>
+        <v>74699</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7485,38 +7472,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459468</v>
+        <v>459280</v>
       </c>
       <c r="R66" t="n">
-        <v>6987119</v>
+        <v>6987044</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7551,12 +7541,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7575,10 +7571,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227105</v>
+        <v>121227109</v>
       </c>
       <c r="B67" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7615,10 +7611,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459387</v>
+        <v>459277</v>
       </c>
       <c r="R67" t="n">
-        <v>6987097</v>
+        <v>6987050</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7677,10 +7673,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227086</v>
+        <v>121227092</v>
       </c>
       <c r="B68" t="n">
-        <v>79680</v>
+        <v>79682</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7693,21 +7689,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7717,10 +7713,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459312</v>
+        <v>459307</v>
       </c>
       <c r="R68" t="n">
-        <v>6986982</v>
+        <v>6986981</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7779,10 +7775,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227127</v>
+        <v>121227136</v>
       </c>
       <c r="B69" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7795,34 +7791,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459310</v>
+        <v>459339</v>
       </c>
       <c r="R69" t="n">
-        <v>6987151</v>
+        <v>6986928</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7855,6 +7859,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7881,10 +7890,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227134</v>
+        <v>121227094</v>
       </c>
       <c r="B70" t="n">
-        <v>57348</v>
+        <v>79682</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7897,50 +7906,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458986</v>
+        <v>458978</v>
       </c>
       <c r="R70" t="n">
-        <v>6987138</v>
+        <v>6987169</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7973,11 +7966,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8004,10 +7992,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227111</v>
+        <v>121227131</v>
       </c>
       <c r="B71" t="n">
-        <v>74696</v>
+        <v>78601</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8016,25 +8004,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8044,10 +8032,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459244</v>
+        <v>459299</v>
       </c>
       <c r="R71" t="n">
-        <v>6987057</v>
+        <v>6986980</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8109,7 +8097,7 @@
         <v>121227114</v>
       </c>
       <c r="B72" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8208,10 +8196,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227118</v>
+        <v>121227128</v>
       </c>
       <c r="B73" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8248,10 +8236,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459411</v>
+        <v>459291</v>
       </c>
       <c r="R73" t="n">
-        <v>6987131</v>
+        <v>6987123</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8310,10 +8298,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227120</v>
+        <v>121227103</v>
       </c>
       <c r="B74" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8326,21 +8314,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8350,10 +8338,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459057</v>
+        <v>459515</v>
       </c>
       <c r="R74" t="n">
-        <v>6987082</v>
+        <v>6987120</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8412,10 +8400,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227097</v>
+        <v>121227089</v>
       </c>
       <c r="B75" t="n">
-        <v>74705</v>
+        <v>90983</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8428,21 +8416,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8452,10 +8440,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459089</v>
+        <v>459514</v>
       </c>
       <c r="R75" t="n">
-        <v>6987126</v>
+        <v>6987120</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8514,10 +8502,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227128</v>
+        <v>121227096</v>
       </c>
       <c r="B76" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8530,21 +8518,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8554,10 +8542,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459291</v>
+        <v>459090</v>
       </c>
       <c r="R76" t="n">
-        <v>6987123</v>
+        <v>6987125</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8616,10 +8604,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227101</v>
+        <v>121227097</v>
       </c>
       <c r="B77" t="n">
-        <v>90687</v>
+        <v>74708</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8632,21 +8620,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8656,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459430</v>
+        <v>459089</v>
       </c>
       <c r="R77" t="n">
-        <v>6986932</v>
+        <v>6987126</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8718,10 +8706,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227108</v>
+        <v>121227100</v>
       </c>
       <c r="B78" t="n">
-        <v>82382</v>
+        <v>90715</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8734,21 +8722,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8758,10 +8746,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459299</v>
+        <v>459252</v>
       </c>
       <c r="R78" t="n">
-        <v>6987083</v>
+        <v>6987048</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8820,10 +8808,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227124</v>
+        <v>121227108</v>
       </c>
       <c r="B79" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8836,21 +8824,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8860,10 +8848,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459222</v>
+        <v>459299</v>
       </c>
       <c r="R79" t="n">
-        <v>6987047</v>
+        <v>6987083</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8922,10 +8910,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227117</v>
+        <v>121227099</v>
       </c>
       <c r="B80" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8938,21 +8926,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8962,10 +8950,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459430</v>
+        <v>459187</v>
       </c>
       <c r="R80" t="n">
-        <v>6987144</v>
+        <v>6987057</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9024,10 +9012,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227099</v>
+        <v>121227118</v>
       </c>
       <c r="B81" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9040,21 +9028,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9064,10 +9052,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459187</v>
+        <v>459411</v>
       </c>
       <c r="R81" t="n">
-        <v>6987057</v>
+        <v>6987131</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9126,10 +9114,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227125</v>
+        <v>121227098</v>
       </c>
       <c r="B82" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9142,21 +9130,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9166,10 +9154,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459256</v>
+        <v>459468</v>
       </c>
       <c r="R82" t="n">
-        <v>6987066</v>
+        <v>6987119</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9228,10 +9216,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227100</v>
+        <v>121227127</v>
       </c>
       <c r="B83" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9244,21 +9232,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9268,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459252</v>
+        <v>459310</v>
       </c>
       <c r="R83" t="n">
-        <v>6987048</v>
+        <v>6987151</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9330,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227106</v>
+        <v>121227117</v>
       </c>
       <c r="B84" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9346,21 +9334,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9370,10 +9358,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459365</v>
+        <v>459430</v>
       </c>
       <c r="R84" t="n">
-        <v>6987091</v>
+        <v>6987144</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9432,10 +9420,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227131</v>
+        <v>121227119</v>
       </c>
       <c r="B85" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9472,10 +9460,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459299</v>
+        <v>459217</v>
       </c>
       <c r="R85" t="n">
-        <v>6986980</v>
+        <v>6987069</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9534,10 +9522,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227113</v>
+        <v>121227135</v>
       </c>
       <c r="B86" t="n">
-        <v>74696</v>
+        <v>57351</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9546,30 +9534,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9577,10 +9570,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459280</v>
+        <v>459252</v>
       </c>
       <c r="R86" t="n">
-        <v>6987044</v>
+        <v>6987032</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9617,7 +9610,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9626,7 +9619,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9645,10 +9637,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227102</v>
+        <v>121227115</v>
       </c>
       <c r="B87" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9661,21 +9653,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9685,10 +9677,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459461</v>
+        <v>459332</v>
       </c>
       <c r="R87" t="n">
-        <v>6987117</v>
+        <v>6986979</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9747,10 +9739,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227103</v>
+        <v>121227091</v>
       </c>
       <c r="B88" t="n">
-        <v>90687</v>
+        <v>74700</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9763,21 +9755,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9787,10 +9779,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459515</v>
+        <v>459295</v>
       </c>
       <c r="R88" t="n">
-        <v>6987120</v>
+        <v>6987078</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9849,10 +9841,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227135</v>
+        <v>121227112</v>
       </c>
       <c r="B89" t="n">
-        <v>57348</v>
+        <v>74699</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9861,46 +9853,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459252</v>
+        <v>459315</v>
       </c>
       <c r="R89" t="n">
-        <v>6987032</v>
+        <v>6987128</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9933,11 +9917,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9964,10 +9943,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227126</v>
+        <v>121227125</v>
       </c>
       <c r="B90" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,10 +9983,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459333</v>
+        <v>459256</v>
       </c>
       <c r="R90" t="n">
-        <v>6987132</v>
+        <v>6987066</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10066,10 +10045,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227119</v>
+        <v>121227122</v>
       </c>
       <c r="B91" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,10 +10085,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459217</v>
+        <v>459010</v>
       </c>
       <c r="R91" t="n">
-        <v>6987069</v>
+        <v>6987146</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10168,10 +10147,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227088</v>
+        <v>121227104</v>
       </c>
       <c r="B92" t="n">
-        <v>74689</v>
+        <v>90697</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10180,25 +10159,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10208,10 +10187,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459493</v>
+        <v>459343</v>
       </c>
       <c r="R92" t="n">
-        <v>6987097</v>
+        <v>6987095</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10270,10 +10249,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227096</v>
+        <v>121227086</v>
       </c>
       <c r="B93" t="n">
-        <v>74705</v>
+        <v>79683</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10286,21 +10265,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10310,10 +10289,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459090</v>
+        <v>459312</v>
       </c>
       <c r="R93" t="n">
-        <v>6987125</v>
+        <v>6986982</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10372,10 +10351,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227121</v>
+        <v>121227134</v>
       </c>
       <c r="B94" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10388,34 +10367,50 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459050</v>
+        <v>458986</v>
       </c>
       <c r="R94" t="n">
-        <v>6987112</v>
+        <v>6987138</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10448,6 +10443,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227115</v>
+        <v>121227105</v>
       </c>
       <c r="B95" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10490,21 +10490,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459332</v>
+        <v>459387</v>
       </c>
       <c r="R95" t="n">
-        <v>6986979</v>
+        <v>6987097</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227089</v>
+        <v>121227110</v>
       </c>
       <c r="B96" t="n">
-        <v>90973</v>
+        <v>74699</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10588,25 +10588,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459514</v>
+        <v>459494</v>
       </c>
       <c r="R96" t="n">
-        <v>6987120</v>
+        <v>6987097</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227123</v>
+        <v>121227106</v>
       </c>
       <c r="B97" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458981</v>
+        <v>459365</v>
       </c>
       <c r="R97" t="n">
-        <v>6987164</v>
+        <v>6987091</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121125947</v>
+        <v>121125895</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,41 +2267,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459414</v>
+        <v>459413</v>
       </c>
       <c r="R16" t="n">
-        <v>6986942</v>
+        <v>6986953</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121125895</v>
+        <v>121125947</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,50 +2388,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459413</v>
+        <v>459414</v>
       </c>
       <c r="R17" t="n">
-        <v>6986953</v>
+        <v>6986942</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210324</v>
+        <v>121210323</v>
       </c>
       <c r="B31" t="n">
-        <v>91353</v>
+        <v>57367</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,38 +3893,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459250</v>
+        <v>459198</v>
       </c>
       <c r="R31" t="n">
-        <v>6987362</v>
+        <v>6987270</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3957,6 +3961,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,10 +3992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210356</v>
+        <v>121210324</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>91353</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3995,25 +4004,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4032,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459060</v>
+        <v>459250</v>
       </c>
       <c r="R32" t="n">
-        <v>6987110</v>
+        <v>6987362</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4085,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210323</v>
+        <v>121210356</v>
       </c>
       <c r="B33" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4101,38 +4110,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459198</v>
+        <v>459060</v>
       </c>
       <c r="R33" t="n">
-        <v>6987270</v>
+        <v>6987110</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4165,11 +4170,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120971712</v>
+        <v>120975648</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459526</v>
+        <v>459597</v>
       </c>
       <c r="R2" t="n">
-        <v>6987171</v>
+        <v>6987210</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +751,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120972218</v>
+        <v>120972337</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459512</v>
+        <v>459550</v>
       </c>
       <c r="R3" t="n">
-        <v>6987017</v>
+        <v>6986963</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120975648</v>
+        <v>120971669</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -933,22 +927,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459597</v>
+        <v>459573</v>
       </c>
       <c r="R4" t="n">
-        <v>6987210</v>
+        <v>6987191</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +966,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120972337</v>
+        <v>120971712</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459550</v>
+        <v>459526</v>
       </c>
       <c r="R5" t="n">
-        <v>6986963</v>
+        <v>6987171</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120972401</v>
+        <v>120972218</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459577</v>
+        <v>459512</v>
       </c>
       <c r="R6" t="n">
-        <v>6986952</v>
+        <v>6987017</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120971669</v>
+        <v>120972401</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,34 +1245,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459573</v>
+        <v>459577</v>
       </c>
       <c r="R7" t="n">
-        <v>6987191</v>
+        <v>6986952</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121125621</v>
+        <v>121127849</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,47 +1465,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459423</v>
+        <v>459274</v>
       </c>
       <c r="R9" t="n">
-        <v>6986917</v>
+        <v>6987068</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1537,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121125668</v>
+        <v>121125895</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,41 +1577,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459429</v>
+        <v>459413</v>
       </c>
       <c r="R10" t="n">
-        <v>6986951</v>
+        <v>6986953</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121128992</v>
+        <v>121131481</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,41 +1698,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459186</v>
+        <v>459308</v>
       </c>
       <c r="R11" t="n">
-        <v>6987297</v>
+        <v>6987012</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1807,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121125770</v>
+        <v>121125947</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1838,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459416</v>
+        <v>459414</v>
       </c>
       <c r="R12" t="n">
-        <v>6986950</v>
+        <v>6986942</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,7 +1919,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121126478</v>
+        <v>121129187</v>
       </c>
       <c r="B13" t="n">
         <v>90715</v>
@@ -1950,13 +1959,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459368</v>
+        <v>459243</v>
       </c>
       <c r="R13" t="n">
-        <v>6987043</v>
+        <v>6987320</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121131481</v>
+        <v>121126478</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,47 +2155,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459308</v>
+        <v>459368</v>
       </c>
       <c r="R15" t="n">
-        <v>6987012</v>
+        <v>6987043</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121125895</v>
+        <v>121126591</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2300,17 +2300,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459413</v>
+        <v>459352</v>
       </c>
       <c r="R16" t="n">
-        <v>6986953</v>
+        <v>6987044</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121125947</v>
+        <v>121128992</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459414</v>
+        <v>459186</v>
       </c>
       <c r="R17" t="n">
-        <v>6986942</v>
+        <v>6987297</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121129187</v>
+        <v>121125668</v>
       </c>
       <c r="B18" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,34 +2504,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459243</v>
+        <v>459429</v>
       </c>
       <c r="R18" t="n">
-        <v>6987320</v>
+        <v>6986951</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121126591</v>
+        <v>121125770</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,47 +2724,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459352</v>
+        <v>459416</v>
       </c>
       <c r="R20" t="n">
-        <v>6987044</v>
+        <v>6986950</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2796,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2797,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121127849</v>
+        <v>121125621</v>
       </c>
       <c r="B21" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,38 +2836,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459274</v>
+        <v>459423</v>
       </c>
       <c r="R21" t="n">
-        <v>6987068</v>
+        <v>6986917</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,7 +2945,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210331</v>
+        <v>121210330</v>
       </c>
       <c r="B22" t="n">
         <v>74699</v>
@@ -2979,16 +2979,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459255</v>
+        <v>459263</v>
       </c>
       <c r="R22" t="n">
-        <v>6987011</v>
+        <v>6987015</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3023,12 +3026,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3047,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210351</v>
+        <v>121210335</v>
       </c>
       <c r="B23" t="n">
-        <v>90697</v>
+        <v>74708</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3072,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3096,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459109</v>
+        <v>459344</v>
       </c>
       <c r="R23" t="n">
-        <v>6987053</v>
+        <v>6987093</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3149,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210317</v>
+        <v>121210313</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>95628</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,25 +3170,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459209</v>
+        <v>459274</v>
       </c>
       <c r="R24" t="n">
-        <v>6986978</v>
+        <v>6987056</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3251,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210330</v>
+        <v>121210328</v>
       </c>
       <c r="B25" t="n">
-        <v>74699</v>
+        <v>90715</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,41 +3272,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459263</v>
+        <v>459363</v>
       </c>
       <c r="R25" t="n">
-        <v>6987015</v>
+        <v>6987053</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3332,18 +3338,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210346</v>
+        <v>121210324</v>
       </c>
       <c r="B26" t="n">
-        <v>74700</v>
+        <v>91353</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459235</v>
+        <v>459250</v>
       </c>
       <c r="R26" t="n">
-        <v>6987465</v>
+        <v>6987362</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210328</v>
+        <v>121210351</v>
       </c>
       <c r="B27" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459363</v>
+        <v>459109</v>
       </c>
       <c r="R27" t="n">
         <v>6987053</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210315</v>
+        <v>121210336</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>74708</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,38 +3582,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459269</v>
+        <v>459289</v>
       </c>
       <c r="R28" t="n">
-        <v>6987021</v>
+        <v>6987454</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3646,11 +3642,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210312</v>
+        <v>121210317</v>
       </c>
       <c r="B29" t="n">
-        <v>74692</v>
+        <v>79718</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,21 +3684,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3717,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459362</v>
+        <v>459209</v>
       </c>
       <c r="R29" t="n">
-        <v>6987057</v>
+        <v>6986978</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3779,10 +3770,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210355</v>
+        <v>121210350</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,21 +3786,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3819,10 +3810,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459361</v>
+        <v>459166</v>
       </c>
       <c r="R30" t="n">
-        <v>6986994</v>
+        <v>6987016</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3881,10 +3872,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210323</v>
+        <v>121210321</v>
       </c>
       <c r="B31" t="n">
-        <v>57367</v>
+        <v>82385</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3897,38 +3888,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459198</v>
+        <v>459138</v>
       </c>
       <c r="R31" t="n">
-        <v>6987270</v>
+        <v>6987016</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3961,11 +3948,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210324</v>
+        <v>121210320</v>
       </c>
       <c r="B32" t="n">
-        <v>91353</v>
+        <v>82385</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,25 +3986,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>898</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4032,10 +4014,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459250</v>
+        <v>459321</v>
       </c>
       <c r="R32" t="n">
-        <v>6987362</v>
+        <v>6987092</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4094,7 +4076,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210356</v>
+        <v>121210354</v>
       </c>
       <c r="B33" t="n">
         <v>78601</v>
@@ -4134,10 +4116,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459060</v>
+        <v>459368</v>
       </c>
       <c r="R33" t="n">
-        <v>6987110</v>
+        <v>6986963</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4196,7 +4178,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210345</v>
+        <v>121210344</v>
       </c>
       <c r="B34" t="n">
         <v>74700</v>
@@ -4236,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459225</v>
+        <v>459384</v>
       </c>
       <c r="R34" t="n">
-        <v>6987464</v>
+        <v>6986948</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4298,10 +4280,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210350</v>
+        <v>121210315</v>
       </c>
       <c r="B35" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,34 +4296,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459166</v>
+        <v>459269</v>
       </c>
       <c r="R35" t="n">
-        <v>6987016</v>
+        <v>6987021</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4374,6 +4360,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4400,10 +4391,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210329</v>
+        <v>121210347</v>
       </c>
       <c r="B36" t="n">
-        <v>90715</v>
+        <v>74700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,21 +4407,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4440,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459208</v>
+        <v>459274</v>
       </c>
       <c r="R36" t="n">
-        <v>6987442</v>
+        <v>6987465</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4502,10 +4493,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210333</v>
+        <v>121210356</v>
       </c>
       <c r="B37" t="n">
-        <v>74699</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4514,25 +4505,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4542,10 +4533,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459276</v>
+        <v>459060</v>
       </c>
       <c r="R37" t="n">
-        <v>6987463</v>
+        <v>6987110</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4604,10 +4595,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210321</v>
+        <v>121210333</v>
       </c>
       <c r="B38" t="n">
-        <v>82385</v>
+        <v>74699</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,25 +4607,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4644,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459138</v>
+        <v>459276</v>
       </c>
       <c r="R38" t="n">
-        <v>6987016</v>
+        <v>6987463</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4706,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210326</v>
+        <v>121210316</v>
       </c>
       <c r="B39" t="n">
-        <v>98081</v>
+        <v>90693</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4718,25 +4709,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4746,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459248</v>
+        <v>459238</v>
       </c>
       <c r="R39" t="n">
-        <v>6987371</v>
+        <v>6986977</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4808,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210327</v>
+        <v>121210355</v>
       </c>
       <c r="B40" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,21 +4815,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4848,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459368</v>
+        <v>459361</v>
       </c>
       <c r="R40" t="n">
-        <v>6986960</v>
+        <v>6986994</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4910,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210319</v>
+        <v>121210329</v>
       </c>
       <c r="B41" t="n">
-        <v>57504</v>
+        <v>90715</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4926,21 +4917,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459169</v>
+        <v>459208</v>
       </c>
       <c r="R41" t="n">
-        <v>6987016</v>
+        <v>6987442</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5012,10 +5003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210360</v>
+        <v>121210331</v>
       </c>
       <c r="B42" t="n">
-        <v>78601</v>
+        <v>74699</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5024,25 +5015,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5052,10 +5043,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459359</v>
+        <v>459255</v>
       </c>
       <c r="R42" t="n">
-        <v>6987446</v>
+        <v>6987011</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5114,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210336</v>
+        <v>121210360</v>
       </c>
       <c r="B43" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5130,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5154,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459289</v>
+        <v>459359</v>
       </c>
       <c r="R43" t="n">
-        <v>6987454</v>
+        <v>6987446</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5216,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210352</v>
+        <v>121210318</v>
       </c>
       <c r="B44" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5232,21 +5223,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5256,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459272</v>
+        <v>459210</v>
       </c>
       <c r="R44" t="n">
-        <v>6987314</v>
+        <v>6986977</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5318,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210313</v>
+        <v>121210352</v>
       </c>
       <c r="B45" t="n">
-        <v>95628</v>
+        <v>90697</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5334,21 +5325,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5358,10 +5349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459274</v>
+        <v>459272</v>
       </c>
       <c r="R45" t="n">
-        <v>6987056</v>
+        <v>6987314</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5420,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210316</v>
+        <v>121210323</v>
       </c>
       <c r="B46" t="n">
-        <v>90693</v>
+        <v>57367</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5436,34 +5427,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459238</v>
+        <v>459198</v>
       </c>
       <c r="R46" t="n">
-        <v>6986977</v>
+        <v>6987270</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5496,6 +5491,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210325</v>
+        <v>121210345</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>74700</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5534,25 +5534,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459361</v>
+        <v>459225</v>
       </c>
       <c r="R47" t="n">
-        <v>6986971</v>
+        <v>6987464</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5624,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210354</v>
+        <v>121210346</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>74700</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459368</v>
+        <v>459235</v>
       </c>
       <c r="R48" t="n">
-        <v>6986963</v>
+        <v>6987465</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210344</v>
+        <v>121210326</v>
       </c>
       <c r="B49" t="n">
-        <v>74700</v>
+        <v>98081</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459384</v>
+        <v>459248</v>
       </c>
       <c r="R49" t="n">
-        <v>6986948</v>
+        <v>6987371</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210334</v>
+        <v>121210327</v>
       </c>
       <c r="B50" t="n">
-        <v>74708</v>
+        <v>90715</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,21 +5844,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459371</v>
+        <v>459368</v>
       </c>
       <c r="R50" t="n">
-        <v>6987042</v>
+        <v>6986960</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210335</v>
+        <v>121210312</v>
       </c>
       <c r="B51" t="n">
-        <v>74708</v>
+        <v>74692</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5942,25 +5942,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459344</v>
+        <v>459362</v>
       </c>
       <c r="R51" t="n">
-        <v>6987093</v>
+        <v>6987057</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210318</v>
+        <v>121210325</v>
       </c>
       <c r="B52" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6044,25 +6044,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459210</v>
+        <v>459361</v>
       </c>
       <c r="R52" t="n">
-        <v>6986977</v>
+        <v>6986971</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210320</v>
+        <v>121210334</v>
       </c>
       <c r="B53" t="n">
-        <v>82385</v>
+        <v>74708</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459321</v>
+        <v>459371</v>
       </c>
       <c r="R53" t="n">
-        <v>6987092</v>
+        <v>6987042</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210347</v>
+        <v>121210319</v>
       </c>
       <c r="B54" t="n">
-        <v>74700</v>
+        <v>57504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459274</v>
+        <v>459169</v>
       </c>
       <c r="R54" t="n">
-        <v>6987465</v>
+        <v>6987016</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227123</v>
+        <v>121227111</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>74699</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6350,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458981</v>
+        <v>459244</v>
       </c>
       <c r="R55" t="n">
-        <v>6987164</v>
+        <v>6987057</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227124</v>
+        <v>121227114</v>
       </c>
       <c r="B56" t="n">
         <v>78601</v>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459222</v>
+        <v>459383</v>
       </c>
       <c r="R56" t="n">
-        <v>6987047</v>
+        <v>6986968</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227111</v>
+        <v>121227098</v>
       </c>
       <c r="B57" t="n">
-        <v>74699</v>
+        <v>90715</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6554,25 +6554,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459244</v>
+        <v>459468</v>
       </c>
       <c r="R57" t="n">
-        <v>6987057</v>
+        <v>6987119</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227102</v>
+        <v>121227100</v>
       </c>
       <c r="B58" t="n">
-        <v>90697</v>
+        <v>90715</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459461</v>
+        <v>459252</v>
       </c>
       <c r="R58" t="n">
-        <v>6987117</v>
+        <v>6987048</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227088</v>
+        <v>121227108</v>
       </c>
       <c r="B59" t="n">
-        <v>74692</v>
+        <v>82385</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6758,25 +6758,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459493</v>
+        <v>459299</v>
       </c>
       <c r="R59" t="n">
-        <v>6987097</v>
+        <v>6987083</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227116</v>
+        <v>121227115</v>
       </c>
       <c r="B60" t="n">
         <v>78601</v>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459437</v>
+        <v>459332</v>
       </c>
       <c r="R60" t="n">
-        <v>6987156</v>
+        <v>6986979</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227120</v>
+        <v>121227128</v>
       </c>
       <c r="B61" t="n">
         <v>78601</v>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459057</v>
+        <v>459291</v>
       </c>
       <c r="R61" t="n">
-        <v>6987082</v>
+        <v>6987123</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7052,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227126</v>
+        <v>121227091</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>74700</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,21 +7068,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459333</v>
+        <v>459295</v>
       </c>
       <c r="R62" t="n">
-        <v>6987132</v>
+        <v>6987078</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227129</v>
+        <v>121227099</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7170,21 +7170,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7194,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459255</v>
+        <v>459187</v>
       </c>
       <c r="R63" t="n">
-        <v>6987069</v>
+        <v>6987057</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7256,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227101</v>
+        <v>121227127</v>
       </c>
       <c r="B64" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7272,21 +7272,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459430</v>
+        <v>459310</v>
       </c>
       <c r="R64" t="n">
-        <v>6986932</v>
+        <v>6987151</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7358,10 +7358,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227121</v>
+        <v>121227103</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7374,21 +7374,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459050</v>
+        <v>459515</v>
       </c>
       <c r="R65" t="n">
-        <v>6987112</v>
+        <v>6987120</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7460,10 +7460,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227113</v>
+        <v>121227106</v>
       </c>
       <c r="B66" t="n">
-        <v>74699</v>
+        <v>82385</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7472,41 +7472,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459280</v>
+        <v>459365</v>
       </c>
       <c r="R66" t="n">
-        <v>6987044</v>
+        <v>6987091</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7541,18 +7538,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7571,10 +7562,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227109</v>
+        <v>121227092</v>
       </c>
       <c r="B67" t="n">
-        <v>82385</v>
+        <v>79682</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7587,21 +7578,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7611,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459277</v>
+        <v>459307</v>
       </c>
       <c r="R67" t="n">
-        <v>6987050</v>
+        <v>6986981</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7673,10 +7664,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227092</v>
+        <v>121227089</v>
       </c>
       <c r="B68" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7689,21 +7680,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7713,10 +7704,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459307</v>
+        <v>459514</v>
       </c>
       <c r="R68" t="n">
-        <v>6986981</v>
+        <v>6987120</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7775,10 +7766,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227136</v>
+        <v>121227119</v>
       </c>
       <c r="B69" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7791,42 +7782,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459339</v>
+        <v>459217</v>
       </c>
       <c r="R69" t="n">
-        <v>6986928</v>
+        <v>6987069</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7859,11 +7842,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7890,10 +7868,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227094</v>
+        <v>121227123</v>
       </c>
       <c r="B70" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7906,21 +7884,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7930,10 +7908,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458978</v>
+        <v>458981</v>
       </c>
       <c r="R70" t="n">
-        <v>6987169</v>
+        <v>6987164</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7992,10 +7970,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227131</v>
+        <v>121227113</v>
       </c>
       <c r="B71" t="n">
-        <v>78601</v>
+        <v>74699</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8004,38 +7982,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459299</v>
+        <v>459280</v>
       </c>
       <c r="R71" t="n">
-        <v>6986980</v>
+        <v>6987044</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8070,12 +8051,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8094,10 +8081,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227114</v>
+        <v>121227112</v>
       </c>
       <c r="B72" t="n">
-        <v>78601</v>
+        <v>74699</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8106,25 +8093,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8134,10 +8121,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459383</v>
+        <v>459315</v>
       </c>
       <c r="R72" t="n">
-        <v>6986968</v>
+        <v>6987128</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8196,10 +8183,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227128</v>
+        <v>121227102</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8212,21 +8199,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8236,10 +8223,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459291</v>
+        <v>459461</v>
       </c>
       <c r="R73" t="n">
-        <v>6987123</v>
+        <v>6987117</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8298,7 +8285,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227103</v>
+        <v>121227101</v>
       </c>
       <c r="B74" t="n">
         <v>90697</v>
@@ -8338,10 +8325,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459515</v>
+        <v>459430</v>
       </c>
       <c r="R74" t="n">
-        <v>6987120</v>
+        <v>6986932</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8400,10 +8387,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227089</v>
+        <v>121227117</v>
       </c>
       <c r="B75" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8416,21 +8403,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8440,10 +8427,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459514</v>
+        <v>459430</v>
       </c>
       <c r="R75" t="n">
-        <v>6987120</v>
+        <v>6987144</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8502,10 +8489,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227096</v>
+        <v>121227121</v>
       </c>
       <c r="B76" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8518,21 +8505,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8542,10 +8529,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459090</v>
+        <v>459050</v>
       </c>
       <c r="R76" t="n">
-        <v>6987125</v>
+        <v>6987112</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8604,10 +8591,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227097</v>
+        <v>121227104</v>
       </c>
       <c r="B77" t="n">
-        <v>74708</v>
+        <v>90697</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8620,21 +8607,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8644,10 +8631,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459089</v>
+        <v>459343</v>
       </c>
       <c r="R77" t="n">
-        <v>6987126</v>
+        <v>6987095</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8706,10 +8693,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227100</v>
+        <v>121227135</v>
       </c>
       <c r="B78" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8722,24 +8709,32 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
@@ -8749,7 +8744,7 @@
         <v>459252</v>
       </c>
       <c r="R78" t="n">
-        <v>6987048</v>
+        <v>6987032</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8782,6 +8777,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8808,10 +8808,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227108</v>
+        <v>121227116</v>
       </c>
       <c r="B79" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8824,21 +8824,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459299</v>
+        <v>459437</v>
       </c>
       <c r="R79" t="n">
-        <v>6987083</v>
+        <v>6987156</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227099</v>
+        <v>121227105</v>
       </c>
       <c r="B80" t="n">
-        <v>90715</v>
+        <v>82385</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8926,21 +8926,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459187</v>
+        <v>459387</v>
       </c>
       <c r="R80" t="n">
-        <v>6987057</v>
+        <v>6987097</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227118</v>
+        <v>121227124</v>
       </c>
       <c r="B81" t="n">
         <v>78601</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459411</v>
+        <v>459222</v>
       </c>
       <c r="R81" t="n">
-        <v>6987131</v>
+        <v>6987047</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227098</v>
+        <v>121227088</v>
       </c>
       <c r="B82" t="n">
-        <v>90715</v>
+        <v>74692</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9126,25 +9126,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459468</v>
+        <v>459493</v>
       </c>
       <c r="R82" t="n">
-        <v>6987119</v>
+        <v>6987097</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227127</v>
+        <v>121227094</v>
       </c>
       <c r="B83" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9232,21 +9232,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459310</v>
+        <v>458978</v>
       </c>
       <c r="R83" t="n">
-        <v>6987151</v>
+        <v>6987169</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9318,7 +9318,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227117</v>
+        <v>121227122</v>
       </c>
       <c r="B84" t="n">
         <v>78601</v>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459430</v>
+        <v>459010</v>
       </c>
       <c r="R84" t="n">
-        <v>6987144</v>
+        <v>6987146</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9420,10 +9420,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227119</v>
+        <v>121227096</v>
       </c>
       <c r="B85" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9436,21 +9436,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459217</v>
+        <v>459090</v>
       </c>
       <c r="R85" t="n">
-        <v>6987069</v>
+        <v>6987125</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227135</v>
+        <v>121227126</v>
       </c>
       <c r="B86" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9538,42 +9538,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459252</v>
+        <v>459333</v>
       </c>
       <c r="R86" t="n">
-        <v>6987032</v>
+        <v>6987132</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9606,11 +9598,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9637,7 +9624,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227115</v>
+        <v>121227120</v>
       </c>
       <c r="B87" t="n">
         <v>78601</v>
@@ -9677,10 +9664,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459332</v>
+        <v>459057</v>
       </c>
       <c r="R87" t="n">
-        <v>6986979</v>
+        <v>6987082</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9739,10 +9726,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227091</v>
+        <v>121227097</v>
       </c>
       <c r="B88" t="n">
-        <v>74700</v>
+        <v>74708</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9755,21 +9742,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9779,10 +9766,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459295</v>
+        <v>459089</v>
       </c>
       <c r="R88" t="n">
-        <v>6987078</v>
+        <v>6987126</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9841,10 +9828,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227112</v>
+        <v>121227118</v>
       </c>
       <c r="B89" t="n">
-        <v>74699</v>
+        <v>78601</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9853,25 +9840,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9881,10 +9868,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459315</v>
+        <v>459411</v>
       </c>
       <c r="R89" t="n">
-        <v>6987128</v>
+        <v>6987131</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9943,7 +9930,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227125</v>
+        <v>121227129</v>
       </c>
       <c r="B90" t="n">
         <v>78601</v>
@@ -9983,10 +9970,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459256</v>
+        <v>459255</v>
       </c>
       <c r="R90" t="n">
-        <v>6987066</v>
+        <v>6987069</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10045,10 +10032,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227122</v>
+        <v>121227136</v>
       </c>
       <c r="B91" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10061,34 +10048,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459010</v>
+        <v>459339</v>
       </c>
       <c r="R91" t="n">
-        <v>6987146</v>
+        <v>6986928</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10121,6 +10116,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10147,10 +10147,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227104</v>
+        <v>121227109</v>
       </c>
       <c r="B92" t="n">
-        <v>90697</v>
+        <v>82385</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10163,21 +10163,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459343</v>
+        <v>459277</v>
       </c>
       <c r="R92" t="n">
-        <v>6987095</v>
+        <v>6987050</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227086</v>
+        <v>121227131</v>
       </c>
       <c r="B93" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10265,21 +10265,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459312</v>
+        <v>459299</v>
       </c>
       <c r="R93" t="n">
-        <v>6986982</v>
+        <v>6986980</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227134</v>
+        <v>121227125</v>
       </c>
       <c r="B94" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10367,50 +10367,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458986</v>
+        <v>459256</v>
       </c>
       <c r="R94" t="n">
-        <v>6987138</v>
+        <v>6987066</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10443,11 +10427,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,10 +10453,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227105</v>
+        <v>121227134</v>
       </c>
       <c r="B95" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10490,34 +10469,50 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459387</v>
+        <v>458986</v>
       </c>
       <c r="R95" t="n">
-        <v>6987097</v>
+        <v>6987138</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10550,6 +10545,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227106</v>
+        <v>121227086</v>
       </c>
       <c r="B97" t="n">
-        <v>82385</v>
+        <v>79683</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459365</v>
+        <v>459312</v>
       </c>
       <c r="R97" t="n">
-        <v>6987091</v>
+        <v>6986982</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -3362,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210324</v>
+        <v>121210336</v>
       </c>
       <c r="B26" t="n">
-        <v>91353</v>
+        <v>74708</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459250</v>
+        <v>459289</v>
       </c>
       <c r="R26" t="n">
-        <v>6987362</v>
+        <v>6987454</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210351</v>
+        <v>121210324</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>91353</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,25 +3476,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459109</v>
+        <v>459250</v>
       </c>
       <c r="R27" t="n">
-        <v>6987053</v>
+        <v>6987362</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210336</v>
+        <v>121210351</v>
       </c>
       <c r="B28" t="n">
-        <v>74708</v>
+        <v>90697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,21 +3582,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459289</v>
+        <v>459109</v>
       </c>
       <c r="R28" t="n">
-        <v>6987454</v>
+        <v>6987053</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210317</v>
+        <v>121210350</v>
       </c>
       <c r="B29" t="n">
-        <v>79718</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3680,25 +3680,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459209</v>
+        <v>459166</v>
       </c>
       <c r="R29" t="n">
-        <v>6986978</v>
+        <v>6987016</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210350</v>
+        <v>121210317</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>79718</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3782,25 +3782,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459166</v>
+        <v>459209</v>
       </c>
       <c r="R30" t="n">
-        <v>6987016</v>
+        <v>6986978</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210315</v>
+        <v>121210347</v>
       </c>
       <c r="B35" t="n">
-        <v>57351</v>
+        <v>74700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4296,38 +4296,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459269</v>
+        <v>459274</v>
       </c>
       <c r="R35" t="n">
-        <v>6987021</v>
+        <v>6987465</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4360,11 +4356,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4391,10 +4382,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210347</v>
+        <v>121210315</v>
       </c>
       <c r="B36" t="n">
-        <v>74700</v>
+        <v>57351</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4407,34 +4398,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459274</v>
+        <v>459269</v>
       </c>
       <c r="R36" t="n">
-        <v>6987465</v>
+        <v>6987021</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4467,6 +4462,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210345</v>
+        <v>121210326</v>
       </c>
       <c r="B47" t="n">
-        <v>74700</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5534,25 +5534,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459225</v>
+        <v>459248</v>
       </c>
       <c r="R47" t="n">
-        <v>6987464</v>
+        <v>6987371</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210346</v>
+        <v>121210345</v>
       </c>
       <c r="B48" t="n">
         <v>74700</v>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459235</v>
+        <v>459225</v>
       </c>
       <c r="R48" t="n">
-        <v>6987465</v>
+        <v>6987464</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210326</v>
+        <v>121210346</v>
       </c>
       <c r="B49" t="n">
-        <v>98081</v>
+        <v>74700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459248</v>
+        <v>459235</v>
       </c>
       <c r="R49" t="n">
-        <v>6987371</v>
+        <v>6987465</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227102</v>
+        <v>121227117</v>
       </c>
       <c r="B73" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8199,21 +8199,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459461</v>
+        <v>459430</v>
       </c>
       <c r="R73" t="n">
-        <v>6987117</v>
+        <v>6987144</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8285,10 +8285,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227101</v>
+        <v>121227121</v>
       </c>
       <c r="B74" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8301,21 +8301,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459430</v>
+        <v>459050</v>
       </c>
       <c r="R74" t="n">
-        <v>6986932</v>
+        <v>6987112</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227117</v>
+        <v>121227102</v>
       </c>
       <c r="B75" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8403,21 +8403,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459430</v>
+        <v>459461</v>
       </c>
       <c r="R75" t="n">
-        <v>6987144</v>
+        <v>6987117</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8489,10 +8489,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227121</v>
+        <v>121227101</v>
       </c>
       <c r="B76" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459050</v>
+        <v>459430</v>
       </c>
       <c r="R76" t="n">
-        <v>6987112</v>
+        <v>6986932</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8693,10 +8693,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227135</v>
+        <v>121227116</v>
       </c>
       <c r="B78" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8709,42 +8709,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459252</v>
+        <v>459437</v>
       </c>
       <c r="R78" t="n">
-        <v>6987032</v>
+        <v>6987156</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8777,11 +8769,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8808,10 +8795,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227116</v>
+        <v>121227135</v>
       </c>
       <c r="B79" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8824,34 +8811,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459437</v>
+        <v>459252</v>
       </c>
       <c r="R79" t="n">
-        <v>6987156</v>
+        <v>6987032</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8884,6 +8879,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10147,10 +10147,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227109</v>
+        <v>121227131</v>
       </c>
       <c r="B92" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10163,21 +10163,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459277</v>
+        <v>459299</v>
       </c>
       <c r="R92" t="n">
-        <v>6987050</v>
+        <v>6986980</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10249,7 +10249,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227131</v>
+        <v>121227125</v>
       </c>
       <c r="B93" t="n">
         <v>78601</v>
@@ -10289,10 +10289,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459299</v>
+        <v>459256</v>
       </c>
       <c r="R93" t="n">
-        <v>6986980</v>
+        <v>6987066</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227125</v>
+        <v>121227134</v>
       </c>
       <c r="B94" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10367,34 +10367,50 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459256</v>
+        <v>458986</v>
       </c>
       <c r="R94" t="n">
-        <v>6987066</v>
+        <v>6987138</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10427,6 +10443,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10453,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227134</v>
+        <v>121227109</v>
       </c>
       <c r="B95" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10469,50 +10490,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458986</v>
+        <v>459277</v>
       </c>
       <c r="R95" t="n">
-        <v>6987138</v>
+        <v>6987050</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10545,11 +10550,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120975648</v>
+        <v>120972401</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459597</v>
+        <v>459577</v>
       </c>
       <c r="R2" t="n">
-        <v>6987210</v>
+        <v>6986952</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,18 +748,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120972337</v>
+        <v>120971712</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459550</v>
+        <v>459526</v>
       </c>
       <c r="R3" t="n">
-        <v>6986963</v>
+        <v>6987171</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120971669</v>
+        <v>120972337</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459573</v>
+        <v>459550</v>
       </c>
       <c r="R4" t="n">
-        <v>6987191</v>
+        <v>6986963</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -968,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120971712</v>
+        <v>120975648</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,37 +1027,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459526</v>
+        <v>459597</v>
       </c>
       <c r="R5" t="n">
-        <v>6987171</v>
+        <v>6987210</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,27 +1087,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>120972218</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120972401</v>
+        <v>120971669</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,34 +1245,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459577</v>
+        <v>459573</v>
       </c>
       <c r="R7" t="n">
-        <v>6986952</v>
+        <v>6987191</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121126083</v>
+        <v>121125947</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459373</v>
+        <v>459414</v>
       </c>
       <c r="R8" t="n">
-        <v>6986932</v>
+        <v>6986942</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>121127849</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121125895</v>
+        <v>121128967</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,50 +1577,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459413</v>
+        <v>459193</v>
       </c>
       <c r="R10" t="n">
-        <v>6986953</v>
+        <v>6987308</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121131481</v>
+        <v>121126478</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,47 +1689,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459308</v>
+        <v>459368</v>
       </c>
       <c r="R11" t="n">
-        <v>6987012</v>
+        <v>6987043</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121125947</v>
+        <v>121126083</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459414</v>
+        <v>459373</v>
       </c>
       <c r="R12" t="n">
-        <v>6986942</v>
+        <v>6986932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1904,7 @@
         <v>121129187</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,7 +2016,7 @@
         <v>121128528</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2143,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121126478</v>
+        <v>121128992</v>
       </c>
       <c r="B15" t="n">
-        <v>90715</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,21 +2141,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459368</v>
+        <v>459186</v>
       </c>
       <c r="R15" t="n">
-        <v>6987043</v>
+        <v>6987297</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121126591</v>
+        <v>121125668</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,50 +2249,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459352</v>
+        <v>459429</v>
       </c>
       <c r="R16" t="n">
-        <v>6987044</v>
+        <v>6986951</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121128992</v>
+        <v>121125895</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,41 +2361,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459186</v>
+        <v>459413</v>
       </c>
       <c r="R17" t="n">
-        <v>6987297</v>
+        <v>6986953</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121125668</v>
+        <v>121126591</v>
       </c>
       <c r="B18" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,41 +2482,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459429</v>
+        <v>459352</v>
       </c>
       <c r="R18" t="n">
-        <v>6986951</v>
+        <v>6987044</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121128967</v>
+        <v>121125621</v>
       </c>
       <c r="B19" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,41 +2603,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459193</v>
+        <v>459423</v>
       </c>
       <c r="R19" t="n">
-        <v>6987308</v>
+        <v>6986917</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,7 +2715,7 @@
         <v>121125770</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121125621</v>
+        <v>121131481</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459423</v>
+        <v>459308</v>
       </c>
       <c r="R21" t="n">
-        <v>6986917</v>
+        <v>6987012</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,7 +2948,7 @@
         <v>121210330</v>
       </c>
       <c r="B22" t="n">
-        <v>74699</v>
+        <v>74701</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210335</v>
+        <v>121210319</v>
       </c>
       <c r="B23" t="n">
-        <v>74708</v>
+        <v>57504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,21 +3072,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459344</v>
+        <v>459169</v>
       </c>
       <c r="R23" t="n">
-        <v>6987093</v>
+        <v>6987016</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210313</v>
+        <v>121210315</v>
       </c>
       <c r="B24" t="n">
-        <v>95628</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,34 +3174,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459274</v>
+        <v>459269</v>
       </c>
       <c r="R24" t="n">
-        <v>6987056</v>
+        <v>6987021</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3234,6 +3238,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210328</v>
+        <v>121210320</v>
       </c>
       <c r="B25" t="n">
-        <v>90715</v>
+        <v>82388</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459363</v>
+        <v>459321</v>
       </c>
       <c r="R25" t="n">
-        <v>6987053</v>
+        <v>6987092</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3362,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210336</v>
+        <v>121210324</v>
       </c>
       <c r="B26" t="n">
-        <v>74708</v>
+        <v>91365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,25 +3383,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459289</v>
+        <v>459250</v>
       </c>
       <c r="R26" t="n">
-        <v>6987454</v>
+        <v>6987362</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3464,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210324</v>
+        <v>121210327</v>
       </c>
       <c r="B27" t="n">
-        <v>91353</v>
+        <v>90727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,25 +3485,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3504,10 +3513,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459250</v>
+        <v>459368</v>
       </c>
       <c r="R27" t="n">
-        <v>6987362</v>
+        <v>6986960</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3566,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210351</v>
+        <v>121210345</v>
       </c>
       <c r="B28" t="n">
-        <v>90697</v>
+        <v>74702</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,21 +3591,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459109</v>
+        <v>459225</v>
       </c>
       <c r="R28" t="n">
-        <v>6987053</v>
+        <v>6987464</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3668,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210350</v>
+        <v>121210351</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3708,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459166</v>
+        <v>459109</v>
       </c>
       <c r="R29" t="n">
-        <v>6987016</v>
+        <v>6987053</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3770,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210317</v>
+        <v>121210344</v>
       </c>
       <c r="B30" t="n">
-        <v>79718</v>
+        <v>74702</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3782,25 +3791,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3810,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459209</v>
+        <v>459384</v>
       </c>
       <c r="R30" t="n">
-        <v>6986978</v>
+        <v>6986948</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3872,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210321</v>
+        <v>121210352</v>
       </c>
       <c r="B31" t="n">
-        <v>82385</v>
+        <v>90709</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,21 +3897,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459138</v>
+        <v>459272</v>
       </c>
       <c r="R31" t="n">
-        <v>6987016</v>
+        <v>6987314</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3974,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210320</v>
+        <v>121210321</v>
       </c>
       <c r="B32" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459321</v>
+        <v>459138</v>
       </c>
       <c r="R32" t="n">
-        <v>6987092</v>
+        <v>6987016</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4076,10 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210354</v>
+        <v>121210328</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4092,21 +4101,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4116,10 +4125,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459368</v>
+        <v>459363</v>
       </c>
       <c r="R33" t="n">
-        <v>6986963</v>
+        <v>6987053</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4178,10 +4187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210344</v>
+        <v>121210355</v>
       </c>
       <c r="B34" t="n">
-        <v>74700</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4194,21 +4203,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,10 +4227,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459384</v>
+        <v>459361</v>
       </c>
       <c r="R34" t="n">
-        <v>6986948</v>
+        <v>6986994</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4280,10 +4289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210347</v>
+        <v>121210360</v>
       </c>
       <c r="B35" t="n">
-        <v>74700</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4296,21 +4305,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4320,10 +4329,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459274</v>
+        <v>459359</v>
       </c>
       <c r="R35" t="n">
-        <v>6987465</v>
+        <v>6987446</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4382,10 +4391,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210315</v>
+        <v>121210336</v>
       </c>
       <c r="B36" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4398,38 +4407,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459269</v>
+        <v>459289</v>
       </c>
       <c r="R36" t="n">
-        <v>6987021</v>
+        <v>6987454</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4462,11 +4467,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210356</v>
+        <v>121210354</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459060</v>
+        <v>459368</v>
       </c>
       <c r="R37" t="n">
-        <v>6987110</v>
+        <v>6986963</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210333</v>
+        <v>121210334</v>
       </c>
       <c r="B38" t="n">
-        <v>74699</v>
+        <v>74710</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4607,25 +4607,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459276</v>
+        <v>459371</v>
       </c>
       <c r="R38" t="n">
-        <v>6987463</v>
+        <v>6987042</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210316</v>
+        <v>121210329</v>
       </c>
       <c r="B39" t="n">
-        <v>90693</v>
+        <v>90727</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459238</v>
+        <v>459208</v>
       </c>
       <c r="R39" t="n">
-        <v>6986977</v>
+        <v>6987442</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210355</v>
+        <v>121210316</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4815,21 +4815,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459361</v>
+        <v>459238</v>
       </c>
       <c r="R40" t="n">
-        <v>6986994</v>
+        <v>6986977</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210329</v>
+        <v>121210346</v>
       </c>
       <c r="B41" t="n">
-        <v>90715</v>
+        <v>74702</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459208</v>
+        <v>459235</v>
       </c>
       <c r="R41" t="n">
-        <v>6987442</v>
+        <v>6987465</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210331</v>
+        <v>121210312</v>
       </c>
       <c r="B42" t="n">
-        <v>74699</v>
+        <v>74694</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5015,25 +5015,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>492</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459255</v>
+        <v>459362</v>
       </c>
       <c r="R42" t="n">
-        <v>6987011</v>
+        <v>6987057</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5105,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210360</v>
+        <v>121210356</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459359</v>
+        <v>459060</v>
       </c>
       <c r="R43" t="n">
-        <v>6987446</v>
+        <v>6987110</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5207,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210318</v>
+        <v>121210350</v>
       </c>
       <c r="B44" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5223,21 +5223,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459210</v>
+        <v>459166</v>
       </c>
       <c r="R44" t="n">
-        <v>6986977</v>
+        <v>6987016</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210352</v>
+        <v>121210313</v>
       </c>
       <c r="B45" t="n">
-        <v>90697</v>
+        <v>95641</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,21 +5325,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459272</v>
+        <v>459274</v>
       </c>
       <c r="R45" t="n">
-        <v>6987314</v>
+        <v>6987056</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210323</v>
+        <v>121210317</v>
       </c>
       <c r="B46" t="n">
-        <v>57367</v>
+        <v>79721</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,42 +5423,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459198</v>
+        <v>459209</v>
       </c>
       <c r="R46" t="n">
-        <v>6987270</v>
+        <v>6986978</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5491,11 +5487,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,10 +5513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210326</v>
+        <v>121210323</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5534,38 +5525,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459248</v>
+        <v>459198</v>
       </c>
       <c r="R47" t="n">
-        <v>6987371</v>
+        <v>6987270</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5598,6 +5593,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5624,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210345</v>
+        <v>121210318</v>
       </c>
       <c r="B48" t="n">
-        <v>74700</v>
+        <v>90995</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459225</v>
+        <v>459210</v>
       </c>
       <c r="R48" t="n">
-        <v>6987464</v>
+        <v>6986977</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210346</v>
+        <v>121210325</v>
       </c>
       <c r="B49" t="n">
-        <v>74700</v>
+        <v>98094</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459235</v>
+        <v>459361</v>
       </c>
       <c r="R49" t="n">
-        <v>6987465</v>
+        <v>6986971</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210327</v>
+        <v>121210326</v>
       </c>
       <c r="B50" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,25 +5840,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459368</v>
+        <v>459248</v>
       </c>
       <c r="R50" t="n">
-        <v>6986960</v>
+        <v>6987371</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210312</v>
+        <v>121210333</v>
       </c>
       <c r="B51" t="n">
-        <v>74692</v>
+        <v>74701</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5942,25 +5942,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459362</v>
+        <v>459276</v>
       </c>
       <c r="R51" t="n">
-        <v>6987057</v>
+        <v>6987463</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210325</v>
+        <v>121210335</v>
       </c>
       <c r="B52" t="n">
-        <v>98081</v>
+        <v>74710</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6044,25 +6044,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459361</v>
+        <v>459344</v>
       </c>
       <c r="R52" t="n">
-        <v>6986971</v>
+        <v>6987093</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210334</v>
+        <v>121210347</v>
       </c>
       <c r="B53" t="n">
-        <v>74708</v>
+        <v>74702</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459371</v>
+        <v>459274</v>
       </c>
       <c r="R53" t="n">
-        <v>6987042</v>
+        <v>6987465</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210319</v>
+        <v>121210331</v>
       </c>
       <c r="B54" t="n">
-        <v>57504</v>
+        <v>74701</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6248,25 +6248,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>492</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459169</v>
+        <v>459255</v>
       </c>
       <c r="R54" t="n">
-        <v>6987016</v>
+        <v>6987011</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227111</v>
+        <v>121227110</v>
       </c>
       <c r="B55" t="n">
-        <v>74699</v>
+        <v>74701</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459244</v>
+        <v>459494</v>
       </c>
       <c r="R55" t="n">
-        <v>6987057</v>
+        <v>6987097</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227114</v>
+        <v>121227103</v>
       </c>
       <c r="B56" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459383</v>
+        <v>459515</v>
       </c>
       <c r="R56" t="n">
-        <v>6986968</v>
+        <v>6987120</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227098</v>
+        <v>121227092</v>
       </c>
       <c r="B57" t="n">
-        <v>90715</v>
+        <v>79685</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459468</v>
+        <v>459307</v>
       </c>
       <c r="R57" t="n">
-        <v>6987119</v>
+        <v>6986981</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227100</v>
+        <v>121227136</v>
       </c>
       <c r="B58" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,34 +6660,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459252</v>
+        <v>459339</v>
       </c>
       <c r="R58" t="n">
-        <v>6987048</v>
+        <v>6986928</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6720,6 +6728,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6746,10 +6759,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227108</v>
+        <v>121227100</v>
       </c>
       <c r="B59" t="n">
-        <v>82385</v>
+        <v>90727</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6762,21 +6775,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6799,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459299</v>
+        <v>459252</v>
       </c>
       <c r="R59" t="n">
-        <v>6987083</v>
+        <v>6987048</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,10 +6861,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227115</v>
+        <v>121227131</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6888,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459332</v>
+        <v>459299</v>
       </c>
       <c r="R60" t="n">
-        <v>6986979</v>
+        <v>6986980</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6963,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227128</v>
+        <v>121227134</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,34 +6979,50 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459291</v>
+        <v>458986</v>
       </c>
       <c r="R61" t="n">
-        <v>6987123</v>
+        <v>6987138</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7026,6 +7055,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7052,10 +7086,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227091</v>
+        <v>121227089</v>
       </c>
       <c r="B62" t="n">
-        <v>74700</v>
+        <v>90995</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,21 +7102,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7092,10 +7126,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459295</v>
+        <v>459514</v>
       </c>
       <c r="R62" t="n">
-        <v>6987078</v>
+        <v>6987120</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7154,10 +7188,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227099</v>
+        <v>121227109</v>
       </c>
       <c r="B63" t="n">
-        <v>90715</v>
+        <v>82388</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7170,21 +7204,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7194,10 +7228,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459187</v>
+        <v>459277</v>
       </c>
       <c r="R63" t="n">
-        <v>6987057</v>
+        <v>6987050</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7256,10 +7290,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227127</v>
+        <v>121227086</v>
       </c>
       <c r="B64" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7272,21 +7306,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7296,10 +7330,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459310</v>
+        <v>459312</v>
       </c>
       <c r="R64" t="n">
-        <v>6987151</v>
+        <v>6986982</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7358,10 +7392,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227103</v>
+        <v>121227094</v>
       </c>
       <c r="B65" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7374,21 +7408,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7398,10 +7432,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459515</v>
+        <v>458978</v>
       </c>
       <c r="R65" t="n">
-        <v>6987120</v>
+        <v>6987169</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7460,10 +7494,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227106</v>
+        <v>121227128</v>
       </c>
       <c r="B66" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7476,21 +7510,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7500,10 +7534,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459365</v>
+        <v>459291</v>
       </c>
       <c r="R66" t="n">
-        <v>6987091</v>
+        <v>6987123</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7562,10 +7596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227092</v>
+        <v>121227125</v>
       </c>
       <c r="B67" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7578,21 +7612,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7636,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459307</v>
+        <v>459256</v>
       </c>
       <c r="R67" t="n">
-        <v>6986981</v>
+        <v>6987066</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7664,10 +7698,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227089</v>
+        <v>121227120</v>
       </c>
       <c r="B68" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7680,21 +7714,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7704,10 +7738,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459514</v>
+        <v>459057</v>
       </c>
       <c r="R68" t="n">
-        <v>6987120</v>
+        <v>6987082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7766,10 +7800,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227119</v>
+        <v>121227088</v>
       </c>
       <c r="B69" t="n">
-        <v>78601</v>
+        <v>74694</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7778,25 +7812,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7806,10 +7840,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459217</v>
+        <v>459493</v>
       </c>
       <c r="R69" t="n">
-        <v>6987069</v>
+        <v>6987097</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7871,7 +7905,7 @@
         <v>121227123</v>
       </c>
       <c r="B70" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7970,10 +8004,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227113</v>
+        <v>121227098</v>
       </c>
       <c r="B71" t="n">
-        <v>74699</v>
+        <v>90727</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7982,41 +8016,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459280</v>
+        <v>459468</v>
       </c>
       <c r="R71" t="n">
-        <v>6987044</v>
+        <v>6987119</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8051,18 +8082,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8081,10 +8106,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227112</v>
+        <v>121227118</v>
       </c>
       <c r="B72" t="n">
-        <v>74699</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8093,25 +8118,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8121,10 +8146,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459315</v>
+        <v>459411</v>
       </c>
       <c r="R72" t="n">
-        <v>6987128</v>
+        <v>6987131</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8183,10 +8208,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227117</v>
+        <v>121227126</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8223,10 +8248,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459430</v>
+        <v>459333</v>
       </c>
       <c r="R73" t="n">
-        <v>6987144</v>
+        <v>6987132</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8285,10 +8310,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227121</v>
+        <v>121227135</v>
       </c>
       <c r="B74" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8301,34 +8326,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459050</v>
+        <v>459252</v>
       </c>
       <c r="R74" t="n">
-        <v>6987112</v>
+        <v>6987032</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8361,6 +8394,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8387,10 +8425,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227102</v>
+        <v>121227119</v>
       </c>
       <c r="B75" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8403,21 +8441,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8427,10 +8465,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459461</v>
+        <v>459217</v>
       </c>
       <c r="R75" t="n">
-        <v>6987117</v>
+        <v>6987069</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8489,10 +8527,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227101</v>
+        <v>121227117</v>
       </c>
       <c r="B76" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8505,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8532,7 +8570,7 @@
         <v>459430</v>
       </c>
       <c r="R76" t="n">
-        <v>6986932</v>
+        <v>6987144</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8591,10 +8629,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227104</v>
+        <v>121227115</v>
       </c>
       <c r="B77" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8607,21 +8645,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8631,10 +8669,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459343</v>
+        <v>459332</v>
       </c>
       <c r="R77" t="n">
-        <v>6987095</v>
+        <v>6986979</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8693,10 +8731,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227116</v>
+        <v>121227102</v>
       </c>
       <c r="B78" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8709,21 +8747,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8733,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459437</v>
+        <v>459461</v>
       </c>
       <c r="R78" t="n">
-        <v>6987156</v>
+        <v>6987117</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8795,10 +8833,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227135</v>
+        <v>121227104</v>
       </c>
       <c r="B79" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8811,42 +8849,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459252</v>
+        <v>459343</v>
       </c>
       <c r="R79" t="n">
-        <v>6987032</v>
+        <v>6987095</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8879,11 +8909,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8910,10 +8935,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227105</v>
+        <v>121227111</v>
       </c>
       <c r="B80" t="n">
-        <v>82385</v>
+        <v>74701</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8922,25 +8947,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8950,10 +8975,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459387</v>
+        <v>459244</v>
       </c>
       <c r="R80" t="n">
-        <v>6987097</v>
+        <v>6987057</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9012,10 +9037,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227124</v>
+        <v>121227122</v>
       </c>
       <c r="B81" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9052,10 +9077,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459222</v>
+        <v>459010</v>
       </c>
       <c r="R81" t="n">
-        <v>6987047</v>
+        <v>6987146</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9114,10 +9139,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227088</v>
+        <v>121227096</v>
       </c>
       <c r="B82" t="n">
-        <v>74692</v>
+        <v>74710</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9126,25 +9151,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9154,10 +9179,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459493</v>
+        <v>459090</v>
       </c>
       <c r="R82" t="n">
-        <v>6987097</v>
+        <v>6987125</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9216,10 +9241,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227094</v>
+        <v>121227099</v>
       </c>
       <c r="B83" t="n">
-        <v>79682</v>
+        <v>90727</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9232,21 +9257,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9281,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>458978</v>
+        <v>459187</v>
       </c>
       <c r="R83" t="n">
-        <v>6987169</v>
+        <v>6987057</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9318,10 +9343,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227122</v>
+        <v>121227121</v>
       </c>
       <c r="B84" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9358,10 +9383,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459010</v>
+        <v>459050</v>
       </c>
       <c r="R84" t="n">
-        <v>6987146</v>
+        <v>6987112</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9420,10 +9445,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227096</v>
+        <v>121227127</v>
       </c>
       <c r="B85" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9436,21 +9461,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9460,10 +9485,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459090</v>
+        <v>459310</v>
       </c>
       <c r="R85" t="n">
-        <v>6987125</v>
+        <v>6987151</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9522,10 +9547,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227126</v>
+        <v>121227106</v>
       </c>
       <c r="B86" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9538,21 +9563,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9562,10 +9587,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459333</v>
+        <v>459365</v>
       </c>
       <c r="R86" t="n">
-        <v>6987132</v>
+        <v>6987091</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9624,10 +9649,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227120</v>
+        <v>121227108</v>
       </c>
       <c r="B87" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9640,21 +9665,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9664,10 +9689,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459057</v>
+        <v>459299</v>
       </c>
       <c r="R87" t="n">
-        <v>6987082</v>
+        <v>6987083</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9726,10 +9751,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227097</v>
+        <v>121227091</v>
       </c>
       <c r="B88" t="n">
-        <v>74708</v>
+        <v>74702</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9742,21 +9767,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9766,10 +9791,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459089</v>
+        <v>459295</v>
       </c>
       <c r="R88" t="n">
-        <v>6987126</v>
+        <v>6987078</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9828,10 +9853,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227118</v>
+        <v>121227116</v>
       </c>
       <c r="B89" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9868,10 +9893,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459411</v>
+        <v>459437</v>
       </c>
       <c r="R89" t="n">
-        <v>6987131</v>
+        <v>6987156</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9930,10 +9955,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227129</v>
+        <v>121227105</v>
       </c>
       <c r="B90" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9946,21 +9971,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9970,10 +9995,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459255</v>
+        <v>459387</v>
       </c>
       <c r="R90" t="n">
-        <v>6987069</v>
+        <v>6987097</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10032,10 +10057,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227136</v>
+        <v>121227097</v>
       </c>
       <c r="B91" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10048,42 +10073,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459339</v>
+        <v>459089</v>
       </c>
       <c r="R91" t="n">
-        <v>6986928</v>
+        <v>6987126</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10116,11 +10133,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10147,10 +10159,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227131</v>
+        <v>121227129</v>
       </c>
       <c r="B92" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10187,10 +10199,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459299</v>
+        <v>459255</v>
       </c>
       <c r="R92" t="n">
-        <v>6986980</v>
+        <v>6987069</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10249,10 +10261,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227125</v>
+        <v>121227114</v>
       </c>
       <c r="B93" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10289,10 +10301,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459256</v>
+        <v>459383</v>
       </c>
       <c r="R93" t="n">
-        <v>6987066</v>
+        <v>6986968</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10351,10 +10363,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227134</v>
+        <v>121227112</v>
       </c>
       <c r="B94" t="n">
-        <v>57351</v>
+        <v>74701</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10363,54 +10375,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458986</v>
+        <v>459315</v>
       </c>
       <c r="R94" t="n">
-        <v>6987138</v>
+        <v>6987128</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10443,11 +10439,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,10 +10465,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227109</v>
+        <v>121227113</v>
       </c>
       <c r="B95" t="n">
-        <v>82385</v>
+        <v>74701</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10486,38 +10477,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459277</v>
+        <v>459280</v>
       </c>
       <c r="R95" t="n">
-        <v>6987050</v>
+        <v>6987044</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10552,12 +10546,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227110</v>
+        <v>121227101</v>
       </c>
       <c r="B96" t="n">
-        <v>74699</v>
+        <v>90709</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10588,25 +10588,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459494</v>
+        <v>459430</v>
       </c>
       <c r="R96" t="n">
-        <v>6987097</v>
+        <v>6986932</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227086</v>
+        <v>121227124</v>
       </c>
       <c r="B97" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459312</v>
+        <v>459222</v>
       </c>
       <c r="R97" t="n">
-        <v>6986982</v>
+        <v>6987047</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121125947</v>
+        <v>121125668</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459414</v>
+        <v>459429</v>
       </c>
       <c r="R8" t="n">
-        <v>6986942</v>
+        <v>6986951</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121127849</v>
+        <v>121125895</v>
       </c>
       <c r="B9" t="n">
-        <v>90727</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,41 +1465,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459274</v>
+        <v>459413</v>
       </c>
       <c r="R9" t="n">
-        <v>6987068</v>
+        <v>6986953</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121128967</v>
+        <v>121128992</v>
       </c>
       <c r="B10" t="n">
-        <v>90727</v>
+        <v>90710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,21 +1590,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459193</v>
+        <v>459186</v>
       </c>
       <c r="R10" t="n">
-        <v>6987308</v>
+        <v>6987297</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121126478</v>
+        <v>121128528</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459368</v>
+        <v>459225</v>
       </c>
       <c r="R11" t="n">
-        <v>6987043</v>
+        <v>6987105</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,7 +1913,7 @@
         <v>121129187</v>
       </c>
       <c r="B13" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121128528</v>
+        <v>121131481</v>
       </c>
       <c r="B14" t="n">
-        <v>90727</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,41 +2034,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459225</v>
+        <v>459308</v>
       </c>
       <c r="R14" t="n">
-        <v>6987105</v>
+        <v>6987012</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,7 +2106,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2116,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121128992</v>
+        <v>121126478</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,21 +2159,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2183,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459186</v>
+        <v>459368</v>
       </c>
       <c r="R15" t="n">
-        <v>6987297</v>
+        <v>6987043</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121125668</v>
+        <v>121125947</v>
       </c>
       <c r="B16" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459429</v>
+        <v>459414</v>
       </c>
       <c r="R16" t="n">
-        <v>6986951</v>
+        <v>6986942</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2349,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121125895</v>
+        <v>121127849</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,50 +2379,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459413</v>
+        <v>459274</v>
       </c>
       <c r="R17" t="n">
-        <v>6986953</v>
+        <v>6987068</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2452,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,7 +2482,7 @@
         <v>121126591</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121125621</v>
+        <v>121128967</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,50 +2612,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459423</v>
+        <v>459193</v>
       </c>
       <c r="R19" t="n">
-        <v>6986917</v>
+        <v>6987308</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121131481</v>
+        <v>121125621</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459308</v>
+        <v>459423</v>
       </c>
       <c r="R21" t="n">
-        <v>6987012</v>
+        <v>6986917</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210330</v>
+        <v>121210313</v>
       </c>
       <c r="B22" t="n">
-        <v>74701</v>
+        <v>95642</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,41 +2957,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>492</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459263</v>
+        <v>459274</v>
       </c>
       <c r="R22" t="n">
-        <v>6987015</v>
+        <v>6987056</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3026,18 +3023,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3056,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210319</v>
+        <v>121210333</v>
       </c>
       <c r="B23" t="n">
-        <v>57504</v>
+        <v>74701</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,25 +3059,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>492</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459169</v>
+        <v>459276</v>
       </c>
       <c r="R23" t="n">
-        <v>6987016</v>
+        <v>6987463</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3158,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210315</v>
+        <v>121210355</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,38 +3165,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459269</v>
+        <v>459361</v>
       </c>
       <c r="R24" t="n">
-        <v>6987021</v>
+        <v>6986994</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3238,11 +3225,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210320</v>
+        <v>121210324</v>
       </c>
       <c r="B25" t="n">
-        <v>82388</v>
+        <v>91366</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>898</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459321</v>
+        <v>459250</v>
       </c>
       <c r="R25" t="n">
-        <v>6987092</v>
+        <v>6987362</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3371,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210324</v>
+        <v>121210334</v>
       </c>
       <c r="B26" t="n">
-        <v>91365</v>
+        <v>74710</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,25 +3365,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459250</v>
+        <v>459371</v>
       </c>
       <c r="R26" t="n">
-        <v>6987362</v>
+        <v>6987042</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3473,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210327</v>
+        <v>121210319</v>
       </c>
       <c r="B27" t="n">
-        <v>90727</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,21 +3471,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459368</v>
+        <v>459169</v>
       </c>
       <c r="R27" t="n">
-        <v>6986960</v>
+        <v>6987016</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3575,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210345</v>
+        <v>121210336</v>
       </c>
       <c r="B28" t="n">
-        <v>74702</v>
+        <v>74710</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,21 +3573,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3615,10 +3597,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459225</v>
+        <v>459289</v>
       </c>
       <c r="R28" t="n">
-        <v>6987464</v>
+        <v>6987454</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3677,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210351</v>
+        <v>121210325</v>
       </c>
       <c r="B29" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,25 +3671,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3717,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459109</v>
+        <v>459361</v>
       </c>
       <c r="R29" t="n">
-        <v>6987053</v>
+        <v>6986971</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3779,10 +3761,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210344</v>
+        <v>121210323</v>
       </c>
       <c r="B30" t="n">
-        <v>74702</v>
+        <v>57367</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,34 +3777,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459384</v>
+        <v>459198</v>
       </c>
       <c r="R30" t="n">
-        <v>6986948</v>
+        <v>6987270</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3855,6 +3841,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,10 +3872,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210352</v>
+        <v>121210329</v>
       </c>
       <c r="B31" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3897,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459272</v>
+        <v>459208</v>
       </c>
       <c r="R31" t="n">
-        <v>6987314</v>
+        <v>6987442</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3983,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210321</v>
+        <v>121210351</v>
       </c>
       <c r="B32" t="n">
-        <v>82388</v>
+        <v>90710</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3999,21 +3990,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4014,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459138</v>
+        <v>459109</v>
       </c>
       <c r="R32" t="n">
-        <v>6987016</v>
+        <v>6987053</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4085,10 +4076,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210328</v>
+        <v>121210315</v>
       </c>
       <c r="B33" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4101,34 +4092,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459363</v>
+        <v>459269</v>
       </c>
       <c r="R33" t="n">
-        <v>6987053</v>
+        <v>6987021</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4161,6 +4156,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,10 +4187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210355</v>
+        <v>121210345</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>74702</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,21 +4203,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459361</v>
+        <v>459225</v>
       </c>
       <c r="R34" t="n">
-        <v>6986994</v>
+        <v>6987464</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210360</v>
+        <v>121210312</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
+        <v>74694</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4301,25 +4301,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459359</v>
+        <v>459362</v>
       </c>
       <c r="R35" t="n">
-        <v>6987446</v>
+        <v>6987057</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210336</v>
+        <v>121210356</v>
       </c>
       <c r="B36" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459289</v>
+        <v>459060</v>
       </c>
       <c r="R36" t="n">
-        <v>6987454</v>
+        <v>6987110</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210354</v>
+        <v>121210360</v>
       </c>
       <c r="B37" t="n">
         <v>78604</v>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459368</v>
+        <v>459359</v>
       </c>
       <c r="R37" t="n">
-        <v>6986963</v>
+        <v>6987446</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210334</v>
+        <v>121210328</v>
       </c>
       <c r="B38" t="n">
-        <v>74710</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459371</v>
+        <v>459363</v>
       </c>
       <c r="R38" t="n">
-        <v>6987042</v>
+        <v>6987053</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210329</v>
+        <v>121210350</v>
       </c>
       <c r="B39" t="n">
-        <v>90727</v>
+        <v>90710</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459208</v>
+        <v>459166</v>
       </c>
       <c r="R39" t="n">
-        <v>6987442</v>
+        <v>6987016</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210316</v>
+        <v>121210352</v>
       </c>
       <c r="B40" t="n">
-        <v>90705</v>
+        <v>90710</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4815,21 +4815,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459238</v>
+        <v>459272</v>
       </c>
       <c r="R40" t="n">
-        <v>6986977</v>
+        <v>6987314</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210346</v>
+        <v>121210326</v>
       </c>
       <c r="B41" t="n">
-        <v>74702</v>
+        <v>98095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4913,25 +4913,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459235</v>
+        <v>459248</v>
       </c>
       <c r="R41" t="n">
-        <v>6987465</v>
+        <v>6987371</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210312</v>
+        <v>121210335</v>
       </c>
       <c r="B42" t="n">
-        <v>74694</v>
+        <v>74710</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5015,25 +5015,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459362</v>
+        <v>459344</v>
       </c>
       <c r="R42" t="n">
-        <v>6987057</v>
+        <v>6987093</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5105,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210356</v>
+        <v>121210321</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459060</v>
+        <v>459138</v>
       </c>
       <c r="R43" t="n">
-        <v>6987110</v>
+        <v>6987016</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5207,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210350</v>
+        <v>121210344</v>
       </c>
       <c r="B44" t="n">
-        <v>90709</v>
+        <v>74702</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5223,21 +5223,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459166</v>
+        <v>459384</v>
       </c>
       <c r="R44" t="n">
-        <v>6987016</v>
+        <v>6986948</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210313</v>
+        <v>121210347</v>
       </c>
       <c r="B45" t="n">
-        <v>95641</v>
+        <v>74702</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,21 +5325,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
         <v>459274</v>
       </c>
       <c r="R45" t="n">
-        <v>6987056</v>
+        <v>6987465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210317</v>
+        <v>121210318</v>
       </c>
       <c r="B46" t="n">
-        <v>79721</v>
+        <v>90996</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459209</v>
+        <v>459210</v>
       </c>
       <c r="R46" t="n">
-        <v>6986978</v>
+        <v>6986977</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5513,10 +5513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210323</v>
+        <v>121210331</v>
       </c>
       <c r="B47" t="n">
-        <v>57367</v>
+        <v>74701</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5525,42 +5525,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>492</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459198</v>
+        <v>459255</v>
       </c>
       <c r="R47" t="n">
-        <v>6987270</v>
+        <v>6987011</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5593,11 +5589,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5624,10 +5615,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210318</v>
+        <v>121210330</v>
       </c>
       <c r="B48" t="n">
-        <v>90995</v>
+        <v>74701</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5636,38 +5627,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459210</v>
+        <v>459263</v>
       </c>
       <c r="R48" t="n">
-        <v>6986977</v>
+        <v>6987015</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5702,12 +5696,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210325</v>
+        <v>121210346</v>
       </c>
       <c r="B49" t="n">
-        <v>98094</v>
+        <v>74702</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459361</v>
+        <v>459235</v>
       </c>
       <c r="R49" t="n">
-        <v>6986971</v>
+        <v>6987465</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210326</v>
+        <v>121210320</v>
       </c>
       <c r="B50" t="n">
-        <v>98094</v>
+        <v>82388</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,25 +5840,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459248</v>
+        <v>459321</v>
       </c>
       <c r="R50" t="n">
-        <v>6987371</v>
+        <v>6987092</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210333</v>
+        <v>121210327</v>
       </c>
       <c r="B51" t="n">
-        <v>74701</v>
+        <v>90728</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5942,25 +5942,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459276</v>
+        <v>459368</v>
       </c>
       <c r="R51" t="n">
-        <v>6987463</v>
+        <v>6986960</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210335</v>
+        <v>121210354</v>
       </c>
       <c r="B52" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459344</v>
+        <v>459368</v>
       </c>
       <c r="R52" t="n">
-        <v>6987093</v>
+        <v>6986963</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210347</v>
+        <v>121210317</v>
       </c>
       <c r="B53" t="n">
-        <v>74702</v>
+        <v>79721</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6146,25 +6146,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459274</v>
+        <v>459209</v>
       </c>
       <c r="R53" t="n">
-        <v>6987465</v>
+        <v>6986978</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210331</v>
+        <v>121210316</v>
       </c>
       <c r="B54" t="n">
-        <v>74701</v>
+        <v>90706</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6248,25 +6248,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459255</v>
+        <v>459238</v>
       </c>
       <c r="R54" t="n">
-        <v>6987011</v>
+        <v>6986977</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227110</v>
+        <v>121227124</v>
       </c>
       <c r="B55" t="n">
-        <v>74701</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6350,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459494</v>
+        <v>459222</v>
       </c>
       <c r="R55" t="n">
-        <v>6987097</v>
+        <v>6987047</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227103</v>
+        <v>121227099</v>
       </c>
       <c r="B56" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459515</v>
+        <v>459187</v>
       </c>
       <c r="R56" t="n">
-        <v>6987120</v>
+        <v>6987057</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227092</v>
+        <v>121227091</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>74702</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459307</v>
+        <v>459295</v>
       </c>
       <c r="R57" t="n">
-        <v>6986981</v>
+        <v>6987078</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227136</v>
+        <v>121227111</v>
       </c>
       <c r="B58" t="n">
-        <v>57351</v>
+        <v>74701</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,46 +6656,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459339</v>
+        <v>459244</v>
       </c>
       <c r="R58" t="n">
-        <v>6986928</v>
+        <v>6987057</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6728,11 +6720,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6759,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227100</v>
+        <v>121227110</v>
       </c>
       <c r="B59" t="n">
-        <v>90727</v>
+        <v>74701</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6771,25 +6758,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6799,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459252</v>
+        <v>459494</v>
       </c>
       <c r="R59" t="n">
-        <v>6987048</v>
+        <v>6987097</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6861,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227131</v>
+        <v>121227106</v>
       </c>
       <c r="B60" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6877,21 +6864,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459299</v>
+        <v>459365</v>
       </c>
       <c r="R60" t="n">
-        <v>6986980</v>
+        <v>6987091</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6963,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227134</v>
+        <v>121227122</v>
       </c>
       <c r="B61" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6979,50 +6966,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458986</v>
+        <v>459010</v>
       </c>
       <c r="R61" t="n">
-        <v>6987138</v>
+        <v>6987146</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7055,11 +7026,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7086,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227089</v>
+        <v>121227096</v>
       </c>
       <c r="B62" t="n">
-        <v>90995</v>
+        <v>74710</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7102,21 +7068,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7126,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459514</v>
+        <v>459090</v>
       </c>
       <c r="R62" t="n">
-        <v>6987120</v>
+        <v>6987125</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7188,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227109</v>
+        <v>121227123</v>
       </c>
       <c r="B63" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7204,21 +7170,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7228,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459277</v>
+        <v>458981</v>
       </c>
       <c r="R63" t="n">
-        <v>6987050</v>
+        <v>6987164</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7290,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227086</v>
+        <v>121227134</v>
       </c>
       <c r="B64" t="n">
-        <v>79686</v>
+        <v>57351</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7306,34 +7272,50 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459312</v>
+        <v>458986</v>
       </c>
       <c r="R64" t="n">
-        <v>6986982</v>
+        <v>6987138</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7366,6 +7348,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7392,10 +7379,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227094</v>
+        <v>121227129</v>
       </c>
       <c r="B65" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7408,21 +7395,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7432,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458978</v>
+        <v>459255</v>
       </c>
       <c r="R65" t="n">
-        <v>6987169</v>
+        <v>6987069</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7494,10 +7481,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227128</v>
+        <v>121227094</v>
       </c>
       <c r="B66" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7510,21 +7497,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7534,10 +7521,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459291</v>
+        <v>458978</v>
       </c>
       <c r="R66" t="n">
-        <v>6987123</v>
+        <v>6987169</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7596,7 +7583,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227125</v>
+        <v>121227127</v>
       </c>
       <c r="B67" t="n">
         <v>78604</v>
@@ -7636,10 +7623,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459256</v>
+        <v>459310</v>
       </c>
       <c r="R67" t="n">
-        <v>6987066</v>
+        <v>6987151</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7698,10 +7685,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227120</v>
+        <v>121227136</v>
       </c>
       <c r="B68" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7714,34 +7701,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459057</v>
+        <v>459339</v>
       </c>
       <c r="R68" t="n">
-        <v>6987082</v>
+        <v>6986928</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7774,6 +7769,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7800,10 +7800,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227088</v>
+        <v>121227115</v>
       </c>
       <c r="B69" t="n">
-        <v>74694</v>
+        <v>78604</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7812,25 +7812,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459493</v>
+        <v>459332</v>
       </c>
       <c r="R69" t="n">
-        <v>6987097</v>
+        <v>6986979</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227123</v>
+        <v>121227105</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7918,21 +7918,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458981</v>
+        <v>459387</v>
       </c>
       <c r="R70" t="n">
-        <v>6987164</v>
+        <v>6987097</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8004,10 +8004,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227098</v>
+        <v>121227128</v>
       </c>
       <c r="B71" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8020,21 +8020,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459468</v>
+        <v>459291</v>
       </c>
       <c r="R71" t="n">
-        <v>6987119</v>
+        <v>6987123</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8106,10 +8106,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227118</v>
+        <v>121227097</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8122,21 +8122,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459411</v>
+        <v>459089</v>
       </c>
       <c r="R72" t="n">
-        <v>6987131</v>
+        <v>6987126</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8208,7 +8208,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227126</v>
+        <v>121227121</v>
       </c>
       <c r="B73" t="n">
         <v>78604</v>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459333</v>
+        <v>459050</v>
       </c>
       <c r="R73" t="n">
-        <v>6987132</v>
+        <v>6987112</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8310,10 +8310,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227135</v>
+        <v>121227100</v>
       </c>
       <c r="B74" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8326,32 +8326,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
@@ -8361,7 +8353,7 @@
         <v>459252</v>
       </c>
       <c r="R74" t="n">
-        <v>6987032</v>
+        <v>6987048</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8394,11 +8386,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8425,10 +8412,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227119</v>
+        <v>121227135</v>
       </c>
       <c r="B75" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8441,34 +8428,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459217</v>
+        <v>459252</v>
       </c>
       <c r="R75" t="n">
-        <v>6987069</v>
+        <v>6987032</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8501,6 +8496,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8527,10 +8527,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227117</v>
+        <v>121227104</v>
       </c>
       <c r="B76" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459430</v>
+        <v>459343</v>
       </c>
       <c r="R76" t="n">
-        <v>6987144</v>
+        <v>6987095</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227115</v>
+        <v>121227113</v>
       </c>
       <c r="B77" t="n">
-        <v>78604</v>
+        <v>74701</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8641,38 +8641,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459332</v>
+        <v>459280</v>
       </c>
       <c r="R77" t="n">
-        <v>6986979</v>
+        <v>6987044</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8707,12 +8710,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8731,10 +8740,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227102</v>
+        <v>121227103</v>
       </c>
       <c r="B78" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8771,10 +8780,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459461</v>
+        <v>459515</v>
       </c>
       <c r="R78" t="n">
-        <v>6987117</v>
+        <v>6987120</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8833,10 +8842,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227104</v>
+        <v>121227112</v>
       </c>
       <c r="B79" t="n">
-        <v>90709</v>
+        <v>74701</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8845,25 +8854,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8873,10 +8882,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459343</v>
+        <v>459315</v>
       </c>
       <c r="R79" t="n">
-        <v>6987095</v>
+        <v>6987128</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8935,10 +8944,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227111</v>
+        <v>121227108</v>
       </c>
       <c r="B80" t="n">
-        <v>74701</v>
+        <v>82388</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8947,25 +8956,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8975,10 +8984,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459244</v>
+        <v>459299</v>
       </c>
       <c r="R80" t="n">
-        <v>6987057</v>
+        <v>6987083</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9037,7 +9046,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227122</v>
+        <v>121227116</v>
       </c>
       <c r="B81" t="n">
         <v>78604</v>
@@ -9077,10 +9086,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459010</v>
+        <v>459437</v>
       </c>
       <c r="R81" t="n">
-        <v>6987146</v>
+        <v>6987156</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9139,10 +9148,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227096</v>
+        <v>121227131</v>
       </c>
       <c r="B82" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9155,21 +9164,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9179,10 +9188,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459090</v>
+        <v>459299</v>
       </c>
       <c r="R82" t="n">
-        <v>6987125</v>
+        <v>6986980</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9241,10 +9250,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227099</v>
+        <v>121227118</v>
       </c>
       <c r="B83" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9257,21 +9266,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9281,10 +9290,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459187</v>
+        <v>459411</v>
       </c>
       <c r="R83" t="n">
-        <v>6987057</v>
+        <v>6987131</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9343,10 +9352,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227121</v>
+        <v>121227088</v>
       </c>
       <c r="B84" t="n">
-        <v>78604</v>
+        <v>74694</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9355,25 +9364,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9383,10 +9392,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459050</v>
+        <v>459493</v>
       </c>
       <c r="R84" t="n">
-        <v>6987112</v>
+        <v>6987097</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9445,10 +9454,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227127</v>
+        <v>121227109</v>
       </c>
       <c r="B85" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9461,21 +9470,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9485,10 +9494,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459310</v>
+        <v>459277</v>
       </c>
       <c r="R85" t="n">
-        <v>6987151</v>
+        <v>6987050</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9547,10 +9556,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227106</v>
+        <v>121227089</v>
       </c>
       <c r="B86" t="n">
-        <v>82388</v>
+        <v>90996</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9563,21 +9572,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9587,10 +9596,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459365</v>
+        <v>459514</v>
       </c>
       <c r="R86" t="n">
-        <v>6987091</v>
+        <v>6987120</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9649,10 +9658,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227108</v>
+        <v>121227120</v>
       </c>
       <c r="B87" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9665,21 +9674,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9689,10 +9698,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459299</v>
+        <v>459057</v>
       </c>
       <c r="R87" t="n">
-        <v>6987083</v>
+        <v>6987082</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9751,10 +9760,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227091</v>
+        <v>121227092</v>
       </c>
       <c r="B88" t="n">
-        <v>74702</v>
+        <v>79685</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9767,21 +9776,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9791,10 +9800,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459295</v>
+        <v>459307</v>
       </c>
       <c r="R88" t="n">
-        <v>6987078</v>
+        <v>6986981</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9853,7 +9862,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227116</v>
+        <v>121227119</v>
       </c>
       <c r="B89" t="n">
         <v>78604</v>
@@ -9893,10 +9902,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459437</v>
+        <v>459217</v>
       </c>
       <c r="R89" t="n">
-        <v>6987156</v>
+        <v>6987069</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9955,10 +9964,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227105</v>
+        <v>121227102</v>
       </c>
       <c r="B90" t="n">
-        <v>82388</v>
+        <v>90710</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9971,21 +9980,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9995,10 +10004,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459387</v>
+        <v>459461</v>
       </c>
       <c r="R90" t="n">
-        <v>6987097</v>
+        <v>6987117</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10057,10 +10066,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227097</v>
+        <v>121227114</v>
       </c>
       <c r="B91" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10073,21 +10082,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10097,10 +10106,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459089</v>
+        <v>459383</v>
       </c>
       <c r="R91" t="n">
-        <v>6987126</v>
+        <v>6986968</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10159,7 +10168,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227129</v>
+        <v>121227117</v>
       </c>
       <c r="B92" t="n">
         <v>78604</v>
@@ -10199,10 +10208,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459255</v>
+        <v>459430</v>
       </c>
       <c r="R92" t="n">
-        <v>6987069</v>
+        <v>6987144</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10261,10 +10270,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227114</v>
+        <v>121227086</v>
       </c>
       <c r="B93" t="n">
-        <v>78604</v>
+        <v>79686</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10277,21 +10286,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10301,10 +10310,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459383</v>
+        <v>459312</v>
       </c>
       <c r="R93" t="n">
-        <v>6986968</v>
+        <v>6986982</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10363,10 +10372,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227112</v>
+        <v>121227098</v>
       </c>
       <c r="B94" t="n">
-        <v>74701</v>
+        <v>90728</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10375,25 +10384,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10403,10 +10412,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459315</v>
+        <v>459468</v>
       </c>
       <c r="R94" t="n">
-        <v>6987128</v>
+        <v>6987119</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10465,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227113</v>
+        <v>121227126</v>
       </c>
       <c r="B95" t="n">
-        <v>74701</v>
+        <v>78604</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10477,41 +10486,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459280</v>
+        <v>459333</v>
       </c>
       <c r="R95" t="n">
-        <v>6987044</v>
+        <v>6987132</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10546,18 +10552,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>121227101</v>
       </c>
       <c r="B96" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227124</v>
+        <v>121227125</v>
       </c>
       <c r="B97" t="n">
         <v>78604</v>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459222</v>
+        <v>459256</v>
       </c>
       <c r="R97" t="n">
-        <v>6987047</v>
+        <v>6987066</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121125668</v>
+        <v>121128967</v>
       </c>
       <c r="B8" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459429</v>
+        <v>459193</v>
       </c>
       <c r="R8" t="n">
-        <v>6986951</v>
+        <v>6987308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121125895</v>
+        <v>121127849</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,50 +1465,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459413</v>
+        <v>459274</v>
       </c>
       <c r="R9" t="n">
-        <v>6986953</v>
+        <v>6987068</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121128992</v>
+        <v>121125895</v>
       </c>
       <c r="B10" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,41 +1577,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459186</v>
+        <v>459413</v>
       </c>
       <c r="R10" t="n">
-        <v>6987297</v>
+        <v>6986953</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121128528</v>
+        <v>121125621</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,38 +1698,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459225</v>
+        <v>459423</v>
       </c>
       <c r="R11" t="n">
-        <v>6987105</v>
+        <v>6986917</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,7 +1810,7 @@
         <v>121126083</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121129187</v>
+        <v>121126591</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,41 +1931,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459243</v>
+        <v>459352</v>
       </c>
       <c r="R13" t="n">
-        <v>6987320</v>
+        <v>6987044</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121131481</v>
+        <v>121125770</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,50 +2052,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459308</v>
+        <v>459416</v>
       </c>
       <c r="R14" t="n">
-        <v>6987012</v>
+        <v>6986950</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121126478</v>
+        <v>121125668</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,37 +2168,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459368</v>
+        <v>459429</v>
       </c>
       <c r="R15" t="n">
-        <v>6987043</v>
+        <v>6986951</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2237,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121125947</v>
+        <v>121131481</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,41 +2276,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459414</v>
+        <v>459308</v>
       </c>
       <c r="R16" t="n">
-        <v>6986942</v>
+        <v>6987012</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121127849</v>
+        <v>121126478</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,17 +2421,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459274</v>
+        <v>459368</v>
       </c>
       <c r="R17" t="n">
-        <v>6987068</v>
+        <v>6987043</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121126591</v>
+        <v>121128992</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,47 +2509,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459352</v>
+        <v>459186</v>
       </c>
       <c r="R18" t="n">
-        <v>6987044</v>
+        <v>6987297</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2563,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121128967</v>
+        <v>121125947</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,34 +2625,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459193</v>
+        <v>459414</v>
       </c>
       <c r="R19" t="n">
-        <v>6987308</v>
+        <v>6986942</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121125770</v>
+        <v>121129187</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,37 +2737,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459416</v>
+        <v>459243</v>
       </c>
       <c r="R20" t="n">
-        <v>6986950</v>
+        <v>6987320</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121125621</v>
+        <v>121128528</v>
       </c>
       <c r="B21" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,47 +2845,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459423</v>
+        <v>459225</v>
       </c>
       <c r="R21" t="n">
-        <v>6986917</v>
+        <v>6987105</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210313</v>
+        <v>121210324</v>
       </c>
       <c r="B22" t="n">
-        <v>95642</v>
+        <v>91369</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,25 +2957,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459274</v>
+        <v>459250</v>
       </c>
       <c r="R22" t="n">
-        <v>6987056</v>
+        <v>6987362</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210333</v>
+        <v>121210347</v>
       </c>
       <c r="B23" t="n">
-        <v>74701</v>
+        <v>74705</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,25 +3059,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459276</v>
+        <v>459274</v>
       </c>
       <c r="R23" t="n">
-        <v>6987463</v>
+        <v>6987465</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3152,7 +3152,7 @@
         <v>121210355</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210324</v>
+        <v>121210318</v>
       </c>
       <c r="B25" t="n">
-        <v>91366</v>
+        <v>90999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459250</v>
+        <v>459210</v>
       </c>
       <c r="R25" t="n">
-        <v>6987362</v>
+        <v>6986977</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210334</v>
+        <v>121210360</v>
       </c>
       <c r="B26" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459371</v>
+        <v>459359</v>
       </c>
       <c r="R26" t="n">
-        <v>6987042</v>
+        <v>6987446</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210319</v>
+        <v>121210350</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459169</v>
+        <v>459166</v>
       </c>
       <c r="R27" t="n">
         <v>6987016</v>
@@ -3557,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210336</v>
+        <v>121210328</v>
       </c>
       <c r="B28" t="n">
-        <v>74710</v>
+        <v>90731</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459289</v>
+        <v>459363</v>
       </c>
       <c r="R28" t="n">
-        <v>6987454</v>
+        <v>6987053</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210325</v>
+        <v>121210334</v>
       </c>
       <c r="B29" t="n">
-        <v>98095</v>
+        <v>74713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3671,25 +3671,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459361</v>
+        <v>459371</v>
       </c>
       <c r="R29" t="n">
-        <v>6986971</v>
+        <v>6987042</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210323</v>
+        <v>121210317</v>
       </c>
       <c r="B30" t="n">
-        <v>57367</v>
+        <v>79724</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3773,42 +3773,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459198</v>
+        <v>459209</v>
       </c>
       <c r="R30" t="n">
-        <v>6987270</v>
+        <v>6986978</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3841,11 +3837,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3872,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210329</v>
+        <v>121210331</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>74704</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3884,25 +3875,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459208</v>
+        <v>459255</v>
       </c>
       <c r="R31" t="n">
-        <v>6987442</v>
+        <v>6987011</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3974,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210351</v>
+        <v>121210313</v>
       </c>
       <c r="B32" t="n">
-        <v>90710</v>
+        <v>95645</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3990,21 +3981,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4014,10 +4005,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459109</v>
+        <v>459274</v>
       </c>
       <c r="R32" t="n">
-        <v>6987053</v>
+        <v>6987056</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4076,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210315</v>
+        <v>121210320</v>
       </c>
       <c r="B33" t="n">
-        <v>57351</v>
+        <v>82391</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4092,38 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459269</v>
+        <v>459321</v>
       </c>
       <c r="R33" t="n">
-        <v>6987021</v>
+        <v>6987092</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4156,11 +4143,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210345</v>
+        <v>121210352</v>
       </c>
       <c r="B34" t="n">
-        <v>74702</v>
+        <v>90713</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,21 +4185,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4227,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459225</v>
+        <v>459272</v>
       </c>
       <c r="R34" t="n">
-        <v>6987464</v>
+        <v>6987314</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4289,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210312</v>
+        <v>121210356</v>
       </c>
       <c r="B35" t="n">
-        <v>74694</v>
+        <v>78607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4301,25 +4283,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4329,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459362</v>
+        <v>459060</v>
       </c>
       <c r="R35" t="n">
-        <v>6987057</v>
+        <v>6987110</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4391,10 +4373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210356</v>
+        <v>121210329</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4407,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4431,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459060</v>
+        <v>459208</v>
       </c>
       <c r="R36" t="n">
-        <v>6987110</v>
+        <v>6987442</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4493,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210360</v>
+        <v>121210336</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4509,21 +4491,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4533,10 +4515,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459359</v>
+        <v>459289</v>
       </c>
       <c r="R37" t="n">
-        <v>6987446</v>
+        <v>6987454</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4595,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210328</v>
+        <v>121210351</v>
       </c>
       <c r="B38" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4611,21 +4593,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,7 +4617,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459363</v>
+        <v>459109</v>
       </c>
       <c r="R38" t="n">
         <v>6987053</v>
@@ -4697,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210350</v>
+        <v>121210321</v>
       </c>
       <c r="B39" t="n">
-        <v>90710</v>
+        <v>82391</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,21 +4695,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,7 +4719,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459166</v>
+        <v>459138</v>
       </c>
       <c r="R39" t="n">
         <v>6987016</v>
@@ -4799,10 +4781,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210352</v>
+        <v>121210344</v>
       </c>
       <c r="B40" t="n">
-        <v>90710</v>
+        <v>74705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4815,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4839,10 +4821,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459272</v>
+        <v>459384</v>
       </c>
       <c r="R40" t="n">
-        <v>6987314</v>
+        <v>6986948</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4901,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210326</v>
+        <v>121210330</v>
       </c>
       <c r="B41" t="n">
-        <v>98095</v>
+        <v>74704</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,34 +4899,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459248</v>
+        <v>459263</v>
       </c>
       <c r="R41" t="n">
-        <v>6987371</v>
+        <v>6987015</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4979,12 +4964,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +4994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210335</v>
+        <v>121210315</v>
       </c>
       <c r="B42" t="n">
-        <v>74710</v>
+        <v>57354</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5019,34 +5010,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459344</v>
+        <v>459269</v>
       </c>
       <c r="R42" t="n">
-        <v>6987093</v>
+        <v>6987021</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5079,6 +5074,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210321</v>
+        <v>121210326</v>
       </c>
       <c r="B43" t="n">
-        <v>82388</v>
+        <v>98098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5117,25 +5117,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459138</v>
+        <v>459248</v>
       </c>
       <c r="R43" t="n">
-        <v>6987016</v>
+        <v>6987371</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5207,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210344</v>
+        <v>121210345</v>
       </c>
       <c r="B44" t="n">
-        <v>74702</v>
+        <v>74705</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459384</v>
+        <v>459225</v>
       </c>
       <c r="R44" t="n">
-        <v>6986948</v>
+        <v>6987464</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210347</v>
+        <v>121210323</v>
       </c>
       <c r="B45" t="n">
-        <v>74702</v>
+        <v>57370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,34 +5325,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459274</v>
+        <v>459198</v>
       </c>
       <c r="R45" t="n">
-        <v>6987465</v>
+        <v>6987270</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5385,6 +5389,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5411,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210318</v>
+        <v>121210312</v>
       </c>
       <c r="B46" t="n">
-        <v>90996</v>
+        <v>74697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5432,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5460,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459210</v>
+        <v>459362</v>
       </c>
       <c r="R46" t="n">
-        <v>6986977</v>
+        <v>6987057</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5513,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210331</v>
+        <v>121210335</v>
       </c>
       <c r="B47" t="n">
-        <v>74701</v>
+        <v>74713</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5525,25 +5534,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5553,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459255</v>
+        <v>459344</v>
       </c>
       <c r="R47" t="n">
-        <v>6987011</v>
+        <v>6987093</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5615,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210330</v>
+        <v>121210327</v>
       </c>
       <c r="B48" t="n">
-        <v>74701</v>
+        <v>90731</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5627,41 +5636,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459263</v>
+        <v>459368</v>
       </c>
       <c r="R48" t="n">
-        <v>6987015</v>
+        <v>6986960</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5696,18 +5702,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210346</v>
+        <v>121210333</v>
       </c>
       <c r="B49" t="n">
-        <v>74702</v>
+        <v>74704</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459235</v>
+        <v>459276</v>
       </c>
       <c r="R49" t="n">
-        <v>6987465</v>
+        <v>6987463</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210320</v>
+        <v>121210354</v>
       </c>
       <c r="B50" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,21 +5844,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459321</v>
+        <v>459368</v>
       </c>
       <c r="R50" t="n">
-        <v>6987092</v>
+        <v>6986963</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210327</v>
+        <v>121210316</v>
       </c>
       <c r="B51" t="n">
-        <v>90728</v>
+        <v>90709</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5946,21 +5946,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459368</v>
+        <v>459238</v>
       </c>
       <c r="R51" t="n">
-        <v>6986960</v>
+        <v>6986977</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210354</v>
+        <v>121210346</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>74705</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459368</v>
+        <v>459235</v>
       </c>
       <c r="R52" t="n">
-        <v>6986963</v>
+        <v>6987465</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210317</v>
+        <v>121210325</v>
       </c>
       <c r="B53" t="n">
-        <v>79721</v>
+        <v>98098</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6146,25 +6146,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459209</v>
+        <v>459361</v>
       </c>
       <c r="R53" t="n">
-        <v>6986978</v>
+        <v>6986971</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210316</v>
+        <v>121210319</v>
       </c>
       <c r="B54" t="n">
-        <v>90706</v>
+        <v>57507</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459238</v>
+        <v>459169</v>
       </c>
       <c r="R54" t="n">
-        <v>6986977</v>
+        <v>6987016</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227124</v>
+        <v>121227109</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459222</v>
+        <v>459277</v>
       </c>
       <c r="R55" t="n">
-        <v>6987047</v>
+        <v>6987050</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227099</v>
+        <v>121227098</v>
       </c>
       <c r="B56" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459187</v>
+        <v>459468</v>
       </c>
       <c r="R56" t="n">
-        <v>6987057</v>
+        <v>6987119</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227091</v>
+        <v>121227118</v>
       </c>
       <c r="B57" t="n">
-        <v>74702</v>
+        <v>78607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459295</v>
+        <v>459411</v>
       </c>
       <c r="R57" t="n">
-        <v>6987078</v>
+        <v>6987131</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227111</v>
+        <v>121227119</v>
       </c>
       <c r="B58" t="n">
-        <v>74701</v>
+        <v>78607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,25 +6656,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459244</v>
+        <v>459217</v>
       </c>
       <c r="R58" t="n">
-        <v>6987057</v>
+        <v>6987069</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227110</v>
+        <v>121227136</v>
       </c>
       <c r="B59" t="n">
-        <v>74701</v>
+        <v>57354</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6758,38 +6758,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459494</v>
+        <v>459339</v>
       </c>
       <c r="R59" t="n">
-        <v>6987097</v>
+        <v>6986928</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6822,6 +6830,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6848,10 +6861,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227106</v>
+        <v>121227086</v>
       </c>
       <c r="B60" t="n">
-        <v>82388</v>
+        <v>79689</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6864,21 +6877,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6888,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459365</v>
+        <v>459312</v>
       </c>
       <c r="R60" t="n">
-        <v>6987091</v>
+        <v>6986982</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6963,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227122</v>
+        <v>121227088</v>
       </c>
       <c r="B61" t="n">
-        <v>78604</v>
+        <v>74697</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6962,25 +6975,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6990,10 +7003,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459010</v>
+        <v>459493</v>
       </c>
       <c r="R61" t="n">
-        <v>6987146</v>
+        <v>6987097</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7052,10 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227096</v>
+        <v>121227104</v>
       </c>
       <c r="B62" t="n">
-        <v>74710</v>
+        <v>90713</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,21 +7081,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7092,10 +7105,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459090</v>
+        <v>459343</v>
       </c>
       <c r="R62" t="n">
-        <v>6987125</v>
+        <v>6987095</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7154,10 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227123</v>
+        <v>121227108</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7170,21 +7183,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7194,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458981</v>
+        <v>459299</v>
       </c>
       <c r="R63" t="n">
-        <v>6987164</v>
+        <v>6987083</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7256,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227134</v>
+        <v>121227089</v>
       </c>
       <c r="B64" t="n">
-        <v>57351</v>
+        <v>90999</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7272,50 +7285,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458986</v>
+        <v>459514</v>
       </c>
       <c r="R64" t="n">
-        <v>6987138</v>
+        <v>6987120</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7348,11 +7345,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7379,10 +7371,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227129</v>
+        <v>121227105</v>
       </c>
       <c r="B65" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7395,21 +7387,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7419,10 +7411,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459255</v>
+        <v>459387</v>
       </c>
       <c r="R65" t="n">
-        <v>6987069</v>
+        <v>6987097</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7481,10 +7473,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227094</v>
+        <v>121227134</v>
       </c>
       <c r="B66" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7497,34 +7489,50 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458978</v>
+        <v>458986</v>
       </c>
       <c r="R66" t="n">
-        <v>6987169</v>
+        <v>6987138</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7557,6 +7565,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7583,10 +7596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227127</v>
+        <v>121227122</v>
       </c>
       <c r="B67" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7623,10 +7636,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459310</v>
+        <v>459010</v>
       </c>
       <c r="R67" t="n">
-        <v>6987151</v>
+        <v>6987146</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7685,10 +7698,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227136</v>
+        <v>121227116</v>
       </c>
       <c r="B68" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7701,42 +7714,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459339</v>
+        <v>459437</v>
       </c>
       <c r="R68" t="n">
-        <v>6986928</v>
+        <v>6987156</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7769,11 +7774,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7800,10 +7800,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227115</v>
+        <v>121227091</v>
       </c>
       <c r="B69" t="n">
-        <v>78604</v>
+        <v>74705</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7816,21 +7816,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459332</v>
+        <v>459295</v>
       </c>
       <c r="R69" t="n">
-        <v>6986979</v>
+        <v>6987078</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227105</v>
+        <v>121227103</v>
       </c>
       <c r="B70" t="n">
-        <v>82388</v>
+        <v>90713</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7918,21 +7918,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459387</v>
+        <v>459515</v>
       </c>
       <c r="R70" t="n">
-        <v>6987097</v>
+        <v>6987120</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8004,10 +8004,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227128</v>
+        <v>121227100</v>
       </c>
       <c r="B71" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8020,21 +8020,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459291</v>
+        <v>459252</v>
       </c>
       <c r="R71" t="n">
-        <v>6987123</v>
+        <v>6987048</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8106,10 +8106,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227097</v>
+        <v>121227092</v>
       </c>
       <c r="B72" t="n">
-        <v>74710</v>
+        <v>79688</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8122,21 +8122,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459089</v>
+        <v>459307</v>
       </c>
       <c r="R72" t="n">
-        <v>6987126</v>
+        <v>6986981</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8211,7 +8211,7 @@
         <v>121227121</v>
       </c>
       <c r="B73" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227100</v>
+        <v>121227128</v>
       </c>
       <c r="B74" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8326,21 +8326,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459252</v>
+        <v>459291</v>
       </c>
       <c r="R74" t="n">
-        <v>6987048</v>
+        <v>6987123</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227135</v>
+        <v>121227120</v>
       </c>
       <c r="B75" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8428,42 +8428,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459252</v>
+        <v>459057</v>
       </c>
       <c r="R75" t="n">
-        <v>6987032</v>
+        <v>6987082</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8496,11 +8488,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8527,10 +8514,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227104</v>
+        <v>121227094</v>
       </c>
       <c r="B76" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8543,21 +8530,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8567,10 +8554,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459343</v>
+        <v>458978</v>
       </c>
       <c r="R76" t="n">
-        <v>6987095</v>
+        <v>6987169</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8629,10 +8616,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227113</v>
+        <v>121227127</v>
       </c>
       <c r="B77" t="n">
-        <v>74701</v>
+        <v>78607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8641,41 +8628,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459280</v>
+        <v>459310</v>
       </c>
       <c r="R77" t="n">
-        <v>6987044</v>
+        <v>6987151</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8710,18 +8694,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8740,10 +8718,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227103</v>
+        <v>121227131</v>
       </c>
       <c r="B78" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8756,21 +8734,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8780,10 +8758,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459515</v>
+        <v>459299</v>
       </c>
       <c r="R78" t="n">
-        <v>6987120</v>
+        <v>6986980</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8842,10 +8820,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227112</v>
+        <v>121227114</v>
       </c>
       <c r="B79" t="n">
-        <v>74701</v>
+        <v>78607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8854,25 +8832,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8882,10 +8860,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459315</v>
+        <v>459383</v>
       </c>
       <c r="R79" t="n">
-        <v>6987128</v>
+        <v>6986968</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8944,10 +8922,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227108</v>
+        <v>121227117</v>
       </c>
       <c r="B80" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8960,21 +8938,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8984,10 +8962,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459299</v>
+        <v>459430</v>
       </c>
       <c r="R80" t="n">
-        <v>6987083</v>
+        <v>6987144</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9046,10 +9024,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227116</v>
+        <v>121227125</v>
       </c>
       <c r="B81" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,10 +9064,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459437</v>
+        <v>459256</v>
       </c>
       <c r="R81" t="n">
-        <v>6987156</v>
+        <v>6987066</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9148,10 +9126,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227131</v>
+        <v>121227112</v>
       </c>
       <c r="B82" t="n">
-        <v>78604</v>
+        <v>74704</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9160,25 +9138,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9188,10 +9166,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459299</v>
+        <v>459315</v>
       </c>
       <c r="R82" t="n">
-        <v>6986980</v>
+        <v>6987128</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9250,10 +9228,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227118</v>
+        <v>121227111</v>
       </c>
       <c r="B83" t="n">
-        <v>78604</v>
+        <v>74704</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9262,25 +9240,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9290,10 +9268,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459411</v>
+        <v>459244</v>
       </c>
       <c r="R83" t="n">
-        <v>6987131</v>
+        <v>6987057</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9352,10 +9330,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227088</v>
+        <v>121227123</v>
       </c>
       <c r="B84" t="n">
-        <v>74694</v>
+        <v>78607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9364,25 +9342,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9392,10 +9370,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459493</v>
+        <v>458981</v>
       </c>
       <c r="R84" t="n">
-        <v>6987097</v>
+        <v>6987164</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9454,10 +9432,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227109</v>
+        <v>121227126</v>
       </c>
       <c r="B85" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9470,21 +9448,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9494,10 +9472,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459277</v>
+        <v>459333</v>
       </c>
       <c r="R85" t="n">
-        <v>6987050</v>
+        <v>6987132</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9556,10 +9534,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227089</v>
+        <v>121227102</v>
       </c>
       <c r="B86" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9572,21 +9550,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9596,10 +9574,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459514</v>
+        <v>459461</v>
       </c>
       <c r="R86" t="n">
-        <v>6987120</v>
+        <v>6987117</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9658,10 +9636,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227120</v>
+        <v>121227101</v>
       </c>
       <c r="B87" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9674,21 +9652,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9698,10 +9676,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459057</v>
+        <v>459430</v>
       </c>
       <c r="R87" t="n">
-        <v>6987082</v>
+        <v>6986932</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9760,10 +9738,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227092</v>
+        <v>121227113</v>
       </c>
       <c r="B88" t="n">
-        <v>79685</v>
+        <v>74704</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9772,38 +9750,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459307</v>
+        <v>459280</v>
       </c>
       <c r="R88" t="n">
-        <v>6986981</v>
+        <v>6987044</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9838,12 +9819,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9862,10 +9849,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227119</v>
+        <v>121227106</v>
       </c>
       <c r="B89" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9878,21 +9865,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9902,10 +9889,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459217</v>
+        <v>459365</v>
       </c>
       <c r="R89" t="n">
-        <v>6987069</v>
+        <v>6987091</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9964,10 +9951,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227102</v>
+        <v>121227110</v>
       </c>
       <c r="B90" t="n">
-        <v>90710</v>
+        <v>74704</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9976,25 +9963,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10004,10 +9991,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459461</v>
+        <v>459494</v>
       </c>
       <c r="R90" t="n">
-        <v>6987117</v>
+        <v>6987097</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10066,10 +10053,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227114</v>
+        <v>121227124</v>
       </c>
       <c r="B91" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,10 +10093,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459383</v>
+        <v>459222</v>
       </c>
       <c r="R91" t="n">
-        <v>6986968</v>
+        <v>6987047</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10168,10 +10155,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227117</v>
+        <v>121227129</v>
       </c>
       <c r="B92" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10208,10 +10195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459430</v>
+        <v>459255</v>
       </c>
       <c r="R92" t="n">
-        <v>6987144</v>
+        <v>6987069</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10270,10 +10257,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227086</v>
+        <v>121227099</v>
       </c>
       <c r="B93" t="n">
-        <v>79686</v>
+        <v>90731</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10286,21 +10273,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10310,10 +10297,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459312</v>
+        <v>459187</v>
       </c>
       <c r="R93" t="n">
-        <v>6986982</v>
+        <v>6987057</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10372,10 +10359,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227098</v>
+        <v>121227135</v>
       </c>
       <c r="B94" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10388,34 +10375,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459468</v>
+        <v>459252</v>
       </c>
       <c r="R94" t="n">
-        <v>6987119</v>
+        <v>6987032</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10448,6 +10443,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227126</v>
+        <v>121227096</v>
       </c>
       <c r="B95" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10490,21 +10490,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459333</v>
+        <v>459090</v>
       </c>
       <c r="R95" t="n">
-        <v>6987132</v>
+        <v>6987125</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227101</v>
+        <v>121227115</v>
       </c>
       <c r="B96" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10592,21 +10592,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459430</v>
+        <v>459332</v>
       </c>
       <c r="R96" t="n">
-        <v>6986932</v>
+        <v>6986979</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227125</v>
+        <v>121227097</v>
       </c>
       <c r="B97" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459256</v>
+        <v>459089</v>
       </c>
       <c r="R97" t="n">
-        <v>6987066</v>
+        <v>6987126</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121127849</v>
+        <v>121126591</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,38 +1465,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459274</v>
+        <v>459352</v>
       </c>
       <c r="R9" t="n">
-        <v>6987068</v>
+        <v>6987044</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1528,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121125895</v>
+        <v>121126478</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>90731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,47 +1586,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459413</v>
+        <v>459368</v>
       </c>
       <c r="R10" t="n">
-        <v>6986953</v>
+        <v>6987043</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121125621</v>
+        <v>121125895</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459423</v>
+        <v>459413</v>
       </c>
       <c r="R11" t="n">
-        <v>6986917</v>
+        <v>6986953</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121126083</v>
+        <v>121125668</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459373</v>
+        <v>459429</v>
       </c>
       <c r="R12" t="n">
-        <v>6986932</v>
+        <v>6986951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,7 +1919,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121126591</v>
+        <v>121125621</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1964,14 +1964,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459352</v>
+        <v>459423</v>
       </c>
       <c r="R13" t="n">
-        <v>6987044</v>
+        <v>6986917</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121125770</v>
+        <v>121127849</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459416</v>
+        <v>459274</v>
       </c>
       <c r="R14" t="n">
-        <v>6986950</v>
+        <v>6987068</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121125668</v>
+        <v>121126083</v>
       </c>
       <c r="B15" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,21 +2168,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459429</v>
+        <v>459373</v>
       </c>
       <c r="R15" t="n">
-        <v>6986951</v>
+        <v>6986932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121131481</v>
+        <v>121125947</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,50 +2276,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459308</v>
+        <v>459414</v>
       </c>
       <c r="R16" t="n">
-        <v>6987012</v>
+        <v>6986942</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121126478</v>
+        <v>121129187</v>
       </c>
       <c r="B17" t="n">
         <v>90731</v>
@@ -2425,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459368</v>
+        <v>459243</v>
       </c>
       <c r="R17" t="n">
-        <v>6987043</v>
+        <v>6987320</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121128992</v>
+        <v>121131481</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,41 +2500,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459186</v>
+        <v>459308</v>
       </c>
       <c r="R18" t="n">
-        <v>6987297</v>
+        <v>6987012</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121125947</v>
+        <v>121128528</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,21 +2625,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459414</v>
+        <v>459225</v>
       </c>
       <c r="R19" t="n">
-        <v>6986942</v>
+        <v>6987105</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121129187</v>
+        <v>121128992</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459243</v>
+        <v>459186</v>
       </c>
       <c r="R20" t="n">
-        <v>6987320</v>
+        <v>6987297</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121128528</v>
+        <v>121125770</v>
       </c>
       <c r="B21" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,21 +2849,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459225</v>
+        <v>459416</v>
       </c>
       <c r="R21" t="n">
-        <v>6987105</v>
+        <v>6986950</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210324</v>
+        <v>121210333</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>74704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>898</v>
+        <v>492</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459250</v>
+        <v>459276</v>
       </c>
       <c r="R22" t="n">
-        <v>6987362</v>
+        <v>6987463</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210347</v>
+        <v>121210356</v>
       </c>
       <c r="B23" t="n">
-        <v>74705</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459274</v>
+        <v>459060</v>
       </c>
       <c r="R23" t="n">
-        <v>6987465</v>
+        <v>6987110</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210355</v>
+        <v>121210319</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459361</v>
+        <v>459169</v>
       </c>
       <c r="R24" t="n">
-        <v>6986994</v>
+        <v>6987016</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210318</v>
+        <v>121210313</v>
       </c>
       <c r="B25" t="n">
-        <v>90999</v>
+        <v>95645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459210</v>
+        <v>459274</v>
       </c>
       <c r="R25" t="n">
-        <v>6986977</v>
+        <v>6987056</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210360</v>
+        <v>121210334</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459359</v>
+        <v>459371</v>
       </c>
       <c r="R26" t="n">
-        <v>6987446</v>
+        <v>6987042</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210350</v>
+        <v>121210328</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459166</v>
+        <v>459363</v>
       </c>
       <c r="R27" t="n">
-        <v>6987016</v>
+        <v>6987053</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3557,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210328</v>
+        <v>121210317</v>
       </c>
       <c r="B28" t="n">
-        <v>90731</v>
+        <v>79724</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3569,25 +3569,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459363</v>
+        <v>459209</v>
       </c>
       <c r="R28" t="n">
-        <v>6987053</v>
+        <v>6986978</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210334</v>
+        <v>121210325</v>
       </c>
       <c r="B29" t="n">
-        <v>74713</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3671,25 +3671,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459371</v>
+        <v>459361</v>
       </c>
       <c r="R29" t="n">
-        <v>6987042</v>
+        <v>6986971</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210317</v>
+        <v>121210326</v>
       </c>
       <c r="B30" t="n">
-        <v>79724</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3773,25 +3773,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459209</v>
+        <v>459248</v>
       </c>
       <c r="R30" t="n">
-        <v>6986978</v>
+        <v>6987371</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210331</v>
+        <v>121210347</v>
       </c>
       <c r="B31" t="n">
-        <v>74704</v>
+        <v>74705</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3875,25 +3875,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459255</v>
+        <v>459274</v>
       </c>
       <c r="R31" t="n">
-        <v>6987011</v>
+        <v>6987465</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210313</v>
+        <v>121210346</v>
       </c>
       <c r="B32" t="n">
-        <v>95645</v>
+        <v>74705</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459274</v>
+        <v>459235</v>
       </c>
       <c r="R32" t="n">
-        <v>6987056</v>
+        <v>6987465</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210320</v>
+        <v>121210312</v>
       </c>
       <c r="B33" t="n">
-        <v>82391</v>
+        <v>74697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459321</v>
+        <v>459362</v>
       </c>
       <c r="R33" t="n">
-        <v>6987092</v>
+        <v>6987057</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210352</v>
+        <v>121210354</v>
       </c>
       <c r="B34" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459272</v>
+        <v>459368</v>
       </c>
       <c r="R34" t="n">
-        <v>6987314</v>
+        <v>6986963</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210356</v>
+        <v>121210360</v>
       </c>
       <c r="B35" t="n">
         <v>78607</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459060</v>
+        <v>459359</v>
       </c>
       <c r="R35" t="n">
-        <v>6987110</v>
+        <v>6987446</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210329</v>
+        <v>121210315</v>
       </c>
       <c r="B36" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4389,34 +4389,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459208</v>
+        <v>459269</v>
       </c>
       <c r="R36" t="n">
-        <v>6987442</v>
+        <v>6987021</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4449,6 +4453,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4475,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210336</v>
+        <v>121210318</v>
       </c>
       <c r="B37" t="n">
-        <v>74713</v>
+        <v>90999</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4515,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459289</v>
+        <v>459210</v>
       </c>
       <c r="R37" t="n">
-        <v>6987454</v>
+        <v>6986977</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4577,10 +4586,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210351</v>
+        <v>121210336</v>
       </c>
       <c r="B38" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4593,21 +4602,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4617,10 +4626,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459109</v>
+        <v>459289</v>
       </c>
       <c r="R38" t="n">
-        <v>6987053</v>
+        <v>6987454</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4679,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210321</v>
+        <v>121210355</v>
       </c>
       <c r="B39" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4695,21 +4704,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4719,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459138</v>
+        <v>459361</v>
       </c>
       <c r="R39" t="n">
-        <v>6987016</v>
+        <v>6986994</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4781,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210344</v>
+        <v>121210335</v>
       </c>
       <c r="B40" t="n">
-        <v>74705</v>
+        <v>74713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4797,21 +4806,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459384</v>
+        <v>459344</v>
       </c>
       <c r="R40" t="n">
-        <v>6986948</v>
+        <v>6987093</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4883,10 +4892,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210330</v>
+        <v>121210352</v>
       </c>
       <c r="B41" t="n">
-        <v>74704</v>
+        <v>90713</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4895,41 +4904,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459263</v>
+        <v>459272</v>
       </c>
       <c r="R41" t="n">
-        <v>6987015</v>
+        <v>6987314</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4964,18 +4970,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210315</v>
+        <v>121210351</v>
       </c>
       <c r="B42" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5010,38 +5010,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459269</v>
+        <v>459109</v>
       </c>
       <c r="R42" t="n">
-        <v>6987021</v>
+        <v>6987053</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5074,11 +5070,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,10 +5096,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210326</v>
+        <v>121210324</v>
       </c>
       <c r="B43" t="n">
-        <v>98098</v>
+        <v>91369</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5121,21 +5112,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5136,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459248</v>
+        <v>459250</v>
       </c>
       <c r="R43" t="n">
-        <v>6987371</v>
+        <v>6987362</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5207,10 +5198,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210345</v>
+        <v>121210329</v>
       </c>
       <c r="B44" t="n">
-        <v>74705</v>
+        <v>90731</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5223,21 +5214,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459225</v>
+        <v>459208</v>
       </c>
       <c r="R44" t="n">
-        <v>6987464</v>
+        <v>6987442</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5309,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210323</v>
+        <v>121210330</v>
       </c>
       <c r="B45" t="n">
-        <v>57370</v>
+        <v>74704</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,31 +5312,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>492</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5353,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459198</v>
+        <v>459263</v>
       </c>
       <c r="R45" t="n">
-        <v>6987270</v>
+        <v>6987015</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5393,7 +5383,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
+          <t>Rikligt i granstubbe, se bild.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,6 +5392,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5420,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210312</v>
+        <v>121210344</v>
       </c>
       <c r="B46" t="n">
-        <v>74697</v>
+        <v>74705</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5432,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5460,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459362</v>
+        <v>459384</v>
       </c>
       <c r="R46" t="n">
-        <v>6987057</v>
+        <v>6986948</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5522,10 +5513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210335</v>
+        <v>121210320</v>
       </c>
       <c r="B47" t="n">
-        <v>74713</v>
+        <v>82391</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5538,21 +5529,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5562,10 +5553,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459344</v>
+        <v>459321</v>
       </c>
       <c r="R47" t="n">
-        <v>6987093</v>
+        <v>6987092</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5624,10 +5615,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210327</v>
+        <v>121210331</v>
       </c>
       <c r="B48" t="n">
-        <v>90731</v>
+        <v>74704</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5636,25 +5627,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5664,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459368</v>
+        <v>459255</v>
       </c>
       <c r="R48" t="n">
-        <v>6986960</v>
+        <v>6987011</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5726,10 +5717,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210333</v>
+        <v>121210350</v>
       </c>
       <c r="B49" t="n">
-        <v>74704</v>
+        <v>90713</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5729,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5757,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459276</v>
+        <v>459166</v>
       </c>
       <c r="R49" t="n">
-        <v>6987463</v>
+        <v>6987016</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210354</v>
+        <v>121210316</v>
       </c>
       <c r="B50" t="n">
-        <v>78607</v>
+        <v>90709</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,21 +5835,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459368</v>
+        <v>459238</v>
       </c>
       <c r="R50" t="n">
-        <v>6986963</v>
+        <v>6986977</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210316</v>
+        <v>121210323</v>
       </c>
       <c r="B51" t="n">
-        <v>90709</v>
+        <v>57370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5946,34 +5937,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459238</v>
+        <v>459198</v>
       </c>
       <c r="R51" t="n">
-        <v>6986977</v>
+        <v>6987270</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6006,6 +6001,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210346</v>
+        <v>121210327</v>
       </c>
       <c r="B52" t="n">
-        <v>74705</v>
+        <v>90731</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459235</v>
+        <v>459368</v>
       </c>
       <c r="R52" t="n">
-        <v>6987465</v>
+        <v>6986960</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210325</v>
+        <v>121210345</v>
       </c>
       <c r="B53" t="n">
-        <v>98098</v>
+        <v>74705</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6146,25 +6146,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459361</v>
+        <v>459225</v>
       </c>
       <c r="R53" t="n">
-        <v>6986971</v>
+        <v>6987464</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210319</v>
+        <v>121210321</v>
       </c>
       <c r="B54" t="n">
-        <v>57507</v>
+        <v>82391</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459169</v>
+        <v>459138</v>
       </c>
       <c r="R54" t="n">
         <v>6987016</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227109</v>
+        <v>121227118</v>
       </c>
       <c r="B55" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459277</v>
+        <v>459411</v>
       </c>
       <c r="R55" t="n">
-        <v>6987050</v>
+        <v>6987131</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227098</v>
+        <v>121227128</v>
       </c>
       <c r="B56" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459468</v>
+        <v>459291</v>
       </c>
       <c r="R56" t="n">
-        <v>6987119</v>
+        <v>6987123</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227118</v>
+        <v>121227100</v>
       </c>
       <c r="B57" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459411</v>
+        <v>459252</v>
       </c>
       <c r="R57" t="n">
-        <v>6987131</v>
+        <v>6987048</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227119</v>
+        <v>121227135</v>
       </c>
       <c r="B58" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,34 +6660,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459217</v>
+        <v>459252</v>
       </c>
       <c r="R58" t="n">
-        <v>6987069</v>
+        <v>6987032</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6720,6 +6728,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6746,10 +6759,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227136</v>
+        <v>121227091</v>
       </c>
       <c r="B59" t="n">
-        <v>57354</v>
+        <v>74705</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6762,42 +6775,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459339</v>
+        <v>459295</v>
       </c>
       <c r="R59" t="n">
-        <v>6986928</v>
+        <v>6987078</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6830,11 +6835,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6861,10 +6861,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227086</v>
+        <v>121227088</v>
       </c>
       <c r="B60" t="n">
-        <v>79689</v>
+        <v>74697</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6873,25 +6873,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459312</v>
+        <v>459493</v>
       </c>
       <c r="R60" t="n">
-        <v>6986982</v>
+        <v>6987097</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6963,10 +6963,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227088</v>
+        <v>121227115</v>
       </c>
       <c r="B61" t="n">
-        <v>74697</v>
+        <v>78607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6975,25 +6975,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459493</v>
+        <v>459332</v>
       </c>
       <c r="R61" t="n">
-        <v>6987097</v>
+        <v>6986979</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7065,10 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227104</v>
+        <v>121227121</v>
       </c>
       <c r="B62" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7081,21 +7081,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459343</v>
+        <v>459050</v>
       </c>
       <c r="R62" t="n">
-        <v>6987095</v>
+        <v>6987112</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227108</v>
+        <v>121227127</v>
       </c>
       <c r="B63" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7183,21 +7183,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459299</v>
+        <v>459310</v>
       </c>
       <c r="R63" t="n">
-        <v>6987083</v>
+        <v>6987151</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7269,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227089</v>
+        <v>121227092</v>
       </c>
       <c r="B64" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7285,21 +7285,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459514</v>
+        <v>459307</v>
       </c>
       <c r="R64" t="n">
-        <v>6987120</v>
+        <v>6986981</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227105</v>
+        <v>121227098</v>
       </c>
       <c r="B65" t="n">
-        <v>82391</v>
+        <v>90731</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7387,21 +7387,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459387</v>
+        <v>459468</v>
       </c>
       <c r="R65" t="n">
-        <v>6987097</v>
+        <v>6987119</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7473,10 +7473,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227134</v>
+        <v>121227099</v>
       </c>
       <c r="B66" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7489,50 +7489,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458986</v>
+        <v>459187</v>
       </c>
       <c r="R66" t="n">
-        <v>6987138</v>
+        <v>6987057</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7565,11 +7549,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7596,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227122</v>
+        <v>121227104</v>
       </c>
       <c r="B67" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7612,21 +7591,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7636,10 +7615,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459010</v>
+        <v>459343</v>
       </c>
       <c r="R67" t="n">
-        <v>6987146</v>
+        <v>6987095</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7698,10 +7677,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227116</v>
+        <v>121227110</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>74704</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7710,25 +7689,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7738,10 +7717,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459437</v>
+        <v>459494</v>
       </c>
       <c r="R68" t="n">
-        <v>6987156</v>
+        <v>6987097</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7800,10 +7779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227091</v>
+        <v>121227126</v>
       </c>
       <c r="B69" t="n">
-        <v>74705</v>
+        <v>78607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7816,21 +7795,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7840,10 +7819,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459295</v>
+        <v>459333</v>
       </c>
       <c r="R69" t="n">
-        <v>6987078</v>
+        <v>6987132</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7902,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227103</v>
+        <v>121227094</v>
       </c>
       <c r="B70" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7918,21 +7897,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7942,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459515</v>
+        <v>458978</v>
       </c>
       <c r="R70" t="n">
-        <v>6987120</v>
+        <v>6987169</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8004,10 +7983,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227100</v>
+        <v>121227097</v>
       </c>
       <c r="B71" t="n">
-        <v>90731</v>
+        <v>74713</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8020,21 +7999,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8044,10 +8023,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459252</v>
+        <v>459089</v>
       </c>
       <c r="R71" t="n">
-        <v>6987048</v>
+        <v>6987126</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8106,10 +8085,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227092</v>
+        <v>121227123</v>
       </c>
       <c r="B72" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8122,21 +8101,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8146,10 +8125,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459307</v>
+        <v>458981</v>
       </c>
       <c r="R72" t="n">
-        <v>6986981</v>
+        <v>6987164</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8208,7 +8187,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227121</v>
+        <v>121227125</v>
       </c>
       <c r="B73" t="n">
         <v>78607</v>
@@ -8248,10 +8227,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459050</v>
+        <v>459256</v>
       </c>
       <c r="R73" t="n">
-        <v>6987112</v>
+        <v>6987066</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8310,10 +8289,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227128</v>
+        <v>121227086</v>
       </c>
       <c r="B74" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8326,21 +8305,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8350,10 +8329,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459291</v>
+        <v>459312</v>
       </c>
       <c r="R74" t="n">
-        <v>6987123</v>
+        <v>6986982</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8412,7 +8391,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227120</v>
+        <v>121227116</v>
       </c>
       <c r="B75" t="n">
         <v>78607</v>
@@ -8452,10 +8431,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459057</v>
+        <v>459437</v>
       </c>
       <c r="R75" t="n">
-        <v>6987082</v>
+        <v>6987156</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8514,10 +8493,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227094</v>
+        <v>121227096</v>
       </c>
       <c r="B76" t="n">
-        <v>79688</v>
+        <v>74713</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8530,21 +8509,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8554,10 +8533,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458978</v>
+        <v>459090</v>
       </c>
       <c r="R76" t="n">
-        <v>6987169</v>
+        <v>6987125</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8616,7 +8595,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227127</v>
+        <v>121227120</v>
       </c>
       <c r="B77" t="n">
         <v>78607</v>
@@ -8656,10 +8635,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459310</v>
+        <v>459057</v>
       </c>
       <c r="R77" t="n">
-        <v>6987151</v>
+        <v>6987082</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8718,10 +8697,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227131</v>
+        <v>121227105</v>
       </c>
       <c r="B78" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8734,21 +8713,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8758,10 +8737,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459299</v>
+        <v>459387</v>
       </c>
       <c r="R78" t="n">
-        <v>6986980</v>
+        <v>6987097</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8820,7 +8799,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227114</v>
+        <v>121227124</v>
       </c>
       <c r="B79" t="n">
         <v>78607</v>
@@ -8860,10 +8839,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459383</v>
+        <v>459222</v>
       </c>
       <c r="R79" t="n">
-        <v>6986968</v>
+        <v>6987047</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8922,10 +8901,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227117</v>
+        <v>121227108</v>
       </c>
       <c r="B80" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8938,21 +8917,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8962,10 +8941,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459430</v>
+        <v>459299</v>
       </c>
       <c r="R80" t="n">
-        <v>6987144</v>
+        <v>6987083</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9024,10 +9003,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227125</v>
+        <v>121227103</v>
       </c>
       <c r="B81" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9040,21 +9019,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9064,10 +9043,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459256</v>
+        <v>459515</v>
       </c>
       <c r="R81" t="n">
-        <v>6987066</v>
+        <v>6987120</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9126,10 +9105,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227112</v>
+        <v>121227134</v>
       </c>
       <c r="B82" t="n">
-        <v>74704</v>
+        <v>57354</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9138,38 +9117,54 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459315</v>
+        <v>458986</v>
       </c>
       <c r="R82" t="n">
-        <v>6987128</v>
+        <v>6987138</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9202,6 +9197,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9228,7 +9228,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227111</v>
+        <v>121227112</v>
       </c>
       <c r="B83" t="n">
         <v>74704</v>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459244</v>
+        <v>459315</v>
       </c>
       <c r="R83" t="n">
-        <v>6987057</v>
+        <v>6987128</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227123</v>
+        <v>121227117</v>
       </c>
       <c r="B84" t="n">
         <v>78607</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458981</v>
+        <v>459430</v>
       </c>
       <c r="R84" t="n">
-        <v>6987164</v>
+        <v>6987144</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227126</v>
+        <v>121227129</v>
       </c>
       <c r="B85" t="n">
         <v>78607</v>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459333</v>
+        <v>459255</v>
       </c>
       <c r="R85" t="n">
-        <v>6987132</v>
+        <v>6987069</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227102</v>
+        <v>121227136</v>
       </c>
       <c r="B86" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9550,34 +9550,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459461</v>
+        <v>459339</v>
       </c>
       <c r="R86" t="n">
-        <v>6987117</v>
+        <v>6986928</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9610,6 +9618,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9636,10 +9649,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227101</v>
+        <v>121227122</v>
       </c>
       <c r="B87" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9652,21 +9665,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9676,10 +9689,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459430</v>
+        <v>459010</v>
       </c>
       <c r="R87" t="n">
-        <v>6986932</v>
+        <v>6987146</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9849,10 +9862,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227106</v>
+        <v>121227102</v>
       </c>
       <c r="B89" t="n">
-        <v>82391</v>
+        <v>90713</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9865,21 +9878,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9889,10 +9902,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459365</v>
+        <v>459461</v>
       </c>
       <c r="R89" t="n">
-        <v>6987091</v>
+        <v>6987117</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9951,10 +9964,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227110</v>
+        <v>121227101</v>
       </c>
       <c r="B90" t="n">
-        <v>74704</v>
+        <v>90713</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9963,25 +9976,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9991,10 +10004,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459494</v>
+        <v>459430</v>
       </c>
       <c r="R90" t="n">
-        <v>6987097</v>
+        <v>6986932</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10053,10 +10066,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227124</v>
+        <v>121227109</v>
       </c>
       <c r="B91" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10069,21 +10082,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10093,10 +10106,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459222</v>
+        <v>459277</v>
       </c>
       <c r="R91" t="n">
-        <v>6987047</v>
+        <v>6987050</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10155,7 +10168,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227129</v>
+        <v>121227114</v>
       </c>
       <c r="B92" t="n">
         <v>78607</v>
@@ -10195,10 +10208,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459255</v>
+        <v>459383</v>
       </c>
       <c r="R92" t="n">
-        <v>6987069</v>
+        <v>6986968</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10257,10 +10270,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227099</v>
+        <v>121227089</v>
       </c>
       <c r="B93" t="n">
-        <v>90731</v>
+        <v>90999</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10273,21 +10286,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10297,10 +10310,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459187</v>
+        <v>459514</v>
       </c>
       <c r="R93" t="n">
-        <v>6987057</v>
+        <v>6987120</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10359,10 +10372,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227135</v>
+        <v>121227106</v>
       </c>
       <c r="B94" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10375,42 +10388,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459252</v>
+        <v>459365</v>
       </c>
       <c r="R94" t="n">
-        <v>6987032</v>
+        <v>6987091</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10443,11 +10448,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10474,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227096</v>
+        <v>121227131</v>
       </c>
       <c r="B95" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10490,21 +10490,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459090</v>
+        <v>459299</v>
       </c>
       <c r="R95" t="n">
-        <v>6987125</v>
+        <v>6986980</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227115</v>
+        <v>121227119</v>
       </c>
       <c r="B96" t="n">
         <v>78607</v>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459332</v>
+        <v>459217</v>
       </c>
       <c r="R96" t="n">
-        <v>6986979</v>
+        <v>6987069</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227097</v>
+        <v>121227111</v>
       </c>
       <c r="B97" t="n">
-        <v>74713</v>
+        <v>74704</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10690,25 +10690,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459089</v>
+        <v>459244</v>
       </c>
       <c r="R97" t="n">
-        <v>6987126</v>
+        <v>6987057</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -5096,10 +5096,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210324</v>
+        <v>121210329</v>
       </c>
       <c r="B43" t="n">
-        <v>91369</v>
+        <v>90731</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5108,25 +5108,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459250</v>
+        <v>459208</v>
       </c>
       <c r="R43" t="n">
-        <v>6987362</v>
+        <v>6987442</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210329</v>
+        <v>121210324</v>
       </c>
       <c r="B44" t="n">
-        <v>90731</v>
+        <v>91369</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5210,25 +5210,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459208</v>
+        <v>459250</v>
       </c>
       <c r="R44" t="n">
-        <v>6987442</v>
+        <v>6987362</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227118</v>
+        <v>121227100</v>
       </c>
       <c r="B55" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459411</v>
+        <v>459252</v>
       </c>
       <c r="R55" t="n">
-        <v>6987131</v>
+        <v>6987048</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227128</v>
+        <v>121227118</v>
       </c>
       <c r="B56" t="n">
         <v>78607</v>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459291</v>
+        <v>459411</v>
       </c>
       <c r="R56" t="n">
-        <v>6987123</v>
+        <v>6987131</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227100</v>
+        <v>121227128</v>
       </c>
       <c r="B57" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459252</v>
+        <v>459291</v>
       </c>
       <c r="R57" t="n">
-        <v>6987048</v>
+        <v>6987123</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227135</v>
+        <v>121227088</v>
       </c>
       <c r="B58" t="n">
-        <v>57354</v>
+        <v>74697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,46 +6656,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459252</v>
+        <v>459493</v>
       </c>
       <c r="R58" t="n">
-        <v>6987032</v>
+        <v>6987097</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6728,11 +6720,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6759,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227091</v>
+        <v>121227115</v>
       </c>
       <c r="B59" t="n">
-        <v>74705</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6775,21 +6762,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6799,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459295</v>
+        <v>459332</v>
       </c>
       <c r="R59" t="n">
-        <v>6987078</v>
+        <v>6986979</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6861,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227088</v>
+        <v>121227091</v>
       </c>
       <c r="B60" t="n">
-        <v>74697</v>
+        <v>74705</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6873,25 +6860,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459493</v>
+        <v>459295</v>
       </c>
       <c r="R60" t="n">
-        <v>6987097</v>
+        <v>6987078</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6963,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227115</v>
+        <v>121227135</v>
       </c>
       <c r="B61" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6979,34 +6966,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459332</v>
+        <v>459252</v>
       </c>
       <c r="R61" t="n">
-        <v>6986979</v>
+        <v>6987032</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7039,6 +7034,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210354</v>
+        <v>121210318</v>
       </c>
       <c r="B34" t="n">
-        <v>78607</v>
+        <v>90999</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459368</v>
+        <v>459210</v>
       </c>
       <c r="R34" t="n">
-        <v>6986963</v>
+        <v>6986977</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210360</v>
+        <v>121210354</v>
       </c>
       <c r="B35" t="n">
         <v>78607</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459359</v>
+        <v>459368</v>
       </c>
       <c r="R35" t="n">
-        <v>6987446</v>
+        <v>6986963</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210315</v>
+        <v>121210360</v>
       </c>
       <c r="B36" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4389,38 +4389,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459269</v>
+        <v>459359</v>
       </c>
       <c r="R36" t="n">
-        <v>6987021</v>
+        <v>6987446</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4453,11 +4449,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210318</v>
+        <v>121210315</v>
       </c>
       <c r="B37" t="n">
-        <v>90999</v>
+        <v>57354</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4500,34 +4491,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459210</v>
+        <v>459269</v>
       </c>
       <c r="R37" t="n">
-        <v>6986977</v>
+        <v>6987021</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4560,6 +4555,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4790,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210335</v>
+        <v>121210352</v>
       </c>
       <c r="B40" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,21 +4806,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459344</v>
+        <v>459272</v>
       </c>
       <c r="R40" t="n">
-        <v>6987093</v>
+        <v>6987314</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210352</v>
+        <v>121210351</v>
       </c>
       <c r="B41" t="n">
         <v>90713</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459272</v>
+        <v>459109</v>
       </c>
       <c r="R41" t="n">
-        <v>6987314</v>
+        <v>6987053</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210351</v>
+        <v>121210335</v>
       </c>
       <c r="B42" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459109</v>
+        <v>459344</v>
       </c>
       <c r="R42" t="n">
-        <v>6987053</v>
+        <v>6987093</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210333</v>
+        <v>121210315</v>
       </c>
       <c r="B22" t="n">
-        <v>74704</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,38 +2957,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459276</v>
+        <v>459269</v>
       </c>
       <c r="R22" t="n">
-        <v>6987463</v>
+        <v>6987021</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3021,6 +3025,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210356</v>
+        <v>121210351</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3072,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3096,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459060</v>
+        <v>459109</v>
       </c>
       <c r="R23" t="n">
-        <v>6987110</v>
+        <v>6987053</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3149,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210319</v>
+        <v>121210334</v>
       </c>
       <c r="B24" t="n">
-        <v>57507</v>
+        <v>74714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459169</v>
+        <v>459371</v>
       </c>
       <c r="R24" t="n">
-        <v>6987016</v>
+        <v>6987042</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3251,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210313</v>
+        <v>121210336</v>
       </c>
       <c r="B25" t="n">
-        <v>95645</v>
+        <v>74714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459274</v>
+        <v>459289</v>
       </c>
       <c r="R25" t="n">
-        <v>6987056</v>
+        <v>6987454</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3353,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210334</v>
+        <v>121210325</v>
       </c>
       <c r="B26" t="n">
-        <v>74713</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,25 +3374,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459371</v>
+        <v>459361</v>
       </c>
       <c r="R26" t="n">
-        <v>6987042</v>
+        <v>6986971</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3455,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210328</v>
+        <v>121210317</v>
       </c>
       <c r="B27" t="n">
-        <v>90731</v>
+        <v>79725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,25 +3476,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459363</v>
+        <v>459209</v>
       </c>
       <c r="R27" t="n">
-        <v>6987053</v>
+        <v>6986978</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3557,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210317</v>
+        <v>121210355</v>
       </c>
       <c r="B28" t="n">
-        <v>79724</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3569,25 +3578,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3597,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459209</v>
+        <v>459361</v>
       </c>
       <c r="R28" t="n">
-        <v>6986978</v>
+        <v>6986994</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3659,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210325</v>
+        <v>121210319</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>57508</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3671,25 +3680,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3699,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459361</v>
+        <v>459169</v>
       </c>
       <c r="R29" t="n">
-        <v>6986971</v>
+        <v>6987016</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3764,7 +3773,7 @@
         <v>121210326</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3863,10 +3872,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210347</v>
+        <v>121210316</v>
       </c>
       <c r="B31" t="n">
-        <v>74705</v>
+        <v>90715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3879,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459274</v>
+        <v>459238</v>
       </c>
       <c r="R31" t="n">
-        <v>6987465</v>
+        <v>6986977</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3965,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210346</v>
+        <v>121210344</v>
       </c>
       <c r="B32" t="n">
-        <v>74705</v>
+        <v>74706</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4005,10 +4014,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459235</v>
+        <v>459384</v>
       </c>
       <c r="R32" t="n">
-        <v>6987465</v>
+        <v>6986948</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4067,10 +4076,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210312</v>
+        <v>121210323</v>
       </c>
       <c r="B33" t="n">
-        <v>74697</v>
+        <v>57371</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4079,38 +4088,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459362</v>
+        <v>459198</v>
       </c>
       <c r="R33" t="n">
-        <v>6987057</v>
+        <v>6987270</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4143,6 +4156,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,10 +4187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210318</v>
+        <v>121210360</v>
       </c>
       <c r="B34" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4185,21 +4203,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4209,10 +4227,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459210</v>
+        <v>459359</v>
       </c>
       <c r="R34" t="n">
-        <v>6986977</v>
+        <v>6987446</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4271,10 +4289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210354</v>
+        <v>121210318</v>
       </c>
       <c r="B35" t="n">
-        <v>78607</v>
+        <v>91005</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4287,21 +4305,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4311,10 +4329,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459368</v>
+        <v>459210</v>
       </c>
       <c r="R35" t="n">
-        <v>6986963</v>
+        <v>6986977</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4373,10 +4391,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210360</v>
+        <v>121210330</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>74705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4385,38 +4403,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459359</v>
+        <v>459263</v>
       </c>
       <c r="R36" t="n">
-        <v>6987446</v>
+        <v>6987015</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4451,12 +4472,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210315</v>
+        <v>121210327</v>
       </c>
       <c r="B37" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,38 +4518,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459269</v>
+        <v>459368</v>
       </c>
       <c r="R37" t="n">
-        <v>6987021</v>
+        <v>6986960</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4555,11 +4578,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210336</v>
+        <v>121210328</v>
       </c>
       <c r="B38" t="n">
-        <v>74713</v>
+        <v>90737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4602,21 +4620,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4626,10 +4644,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459289</v>
+        <v>459363</v>
       </c>
       <c r="R38" t="n">
-        <v>6987454</v>
+        <v>6987053</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4688,10 +4706,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210355</v>
+        <v>121210329</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4704,21 +4722,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459361</v>
+        <v>459208</v>
       </c>
       <c r="R39" t="n">
-        <v>6986994</v>
+        <v>6987442</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4790,10 +4808,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210352</v>
+        <v>121210321</v>
       </c>
       <c r="B40" t="n">
-        <v>90713</v>
+        <v>82392</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,21 +4824,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459272</v>
+        <v>459138</v>
       </c>
       <c r="R40" t="n">
-        <v>6987314</v>
+        <v>6987016</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4892,10 +4910,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210351</v>
+        <v>121210350</v>
       </c>
       <c r="B41" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4932,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459109</v>
+        <v>459166</v>
       </c>
       <c r="R41" t="n">
-        <v>6987053</v>
+        <v>6987016</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4994,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210335</v>
+        <v>121210324</v>
       </c>
       <c r="B42" t="n">
-        <v>74713</v>
+        <v>91375</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5006,25 +5024,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5034,10 +5052,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459344</v>
+        <v>459250</v>
       </c>
       <c r="R42" t="n">
-        <v>6987093</v>
+        <v>6987362</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5096,10 +5114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210329</v>
+        <v>121210335</v>
       </c>
       <c r="B43" t="n">
-        <v>90731</v>
+        <v>74714</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5112,21 +5130,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5136,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459208</v>
+        <v>459344</v>
       </c>
       <c r="R43" t="n">
-        <v>6987442</v>
+        <v>6987093</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5198,10 +5216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210324</v>
+        <v>121210345</v>
       </c>
       <c r="B44" t="n">
-        <v>91369</v>
+        <v>74706</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5210,25 +5228,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5238,10 +5256,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459250</v>
+        <v>459225</v>
       </c>
       <c r="R44" t="n">
-        <v>6987362</v>
+        <v>6987464</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5300,10 +5318,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210330</v>
+        <v>121210333</v>
       </c>
       <c r="B45" t="n">
-        <v>74704</v>
+        <v>74705</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5334,19 +5352,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459263</v>
+        <v>459276</v>
       </c>
       <c r="R45" t="n">
-        <v>6987015</v>
+        <v>6987463</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5381,18 +5396,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5411,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210344</v>
+        <v>121210346</v>
       </c>
       <c r="B46" t="n">
-        <v>74705</v>
+        <v>74706</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,10 +5460,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459384</v>
+        <v>459235</v>
       </c>
       <c r="R46" t="n">
-        <v>6986948</v>
+        <v>6987465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5513,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210320</v>
+        <v>121210354</v>
       </c>
       <c r="B47" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5529,21 +5538,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5553,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459321</v>
+        <v>459368</v>
       </c>
       <c r="R47" t="n">
-        <v>6987092</v>
+        <v>6986963</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5615,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210331</v>
+        <v>121210320</v>
       </c>
       <c r="B48" t="n">
-        <v>74704</v>
+        <v>82392</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5627,25 +5636,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459255</v>
+        <v>459321</v>
       </c>
       <c r="R48" t="n">
-        <v>6987011</v>
+        <v>6987092</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5717,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210350</v>
+        <v>121210312</v>
       </c>
       <c r="B49" t="n">
-        <v>90713</v>
+        <v>74698</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5729,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5757,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459166</v>
+        <v>459362</v>
       </c>
       <c r="R49" t="n">
-        <v>6987016</v>
+        <v>6987057</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5819,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210316</v>
+        <v>121210331</v>
       </c>
       <c r="B50" t="n">
-        <v>90709</v>
+        <v>74705</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5831,25 +5840,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>492</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5859,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459238</v>
+        <v>459255</v>
       </c>
       <c r="R50" t="n">
-        <v>6986977</v>
+        <v>6987011</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5921,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210323</v>
+        <v>121210347</v>
       </c>
       <c r="B51" t="n">
-        <v>57370</v>
+        <v>74706</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5937,38 +5946,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459198</v>
+        <v>459274</v>
       </c>
       <c r="R51" t="n">
-        <v>6987270</v>
+        <v>6987465</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6001,11 +6006,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210327</v>
+        <v>121210313</v>
       </c>
       <c r="B52" t="n">
-        <v>90731</v>
+        <v>95651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459368</v>
+        <v>459274</v>
       </c>
       <c r="R52" t="n">
-        <v>6986960</v>
+        <v>6987056</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210345</v>
+        <v>121210356</v>
       </c>
       <c r="B53" t="n">
-        <v>74705</v>
+        <v>78608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459225</v>
+        <v>459060</v>
       </c>
       <c r="R53" t="n">
-        <v>6987464</v>
+        <v>6987110</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210321</v>
+        <v>121210352</v>
       </c>
       <c r="B54" t="n">
-        <v>82391</v>
+        <v>90719</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459138</v>
+        <v>459272</v>
       </c>
       <c r="R54" t="n">
-        <v>6987016</v>
+        <v>6987314</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227100</v>
+        <v>121227126</v>
       </c>
       <c r="B55" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459252</v>
+        <v>459333</v>
       </c>
       <c r="R55" t="n">
-        <v>6987048</v>
+        <v>6987132</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227118</v>
+        <v>121227102</v>
       </c>
       <c r="B56" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459411</v>
+        <v>459461</v>
       </c>
       <c r="R56" t="n">
-        <v>6987131</v>
+        <v>6987117</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227128</v>
+        <v>121227086</v>
       </c>
       <c r="B57" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459291</v>
+        <v>459312</v>
       </c>
       <c r="R57" t="n">
-        <v>6987123</v>
+        <v>6986982</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227088</v>
+        <v>121227116</v>
       </c>
       <c r="B58" t="n">
-        <v>74697</v>
+        <v>78608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,25 +6656,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459493</v>
+        <v>459437</v>
       </c>
       <c r="R58" t="n">
-        <v>6987097</v>
+        <v>6987156</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227115</v>
+        <v>121227109</v>
       </c>
       <c r="B59" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459332</v>
+        <v>459277</v>
       </c>
       <c r="R59" t="n">
-        <v>6986979</v>
+        <v>6987050</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227091</v>
+        <v>121227103</v>
       </c>
       <c r="B60" t="n">
-        <v>74705</v>
+        <v>90719</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6864,21 +6864,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459295</v>
+        <v>459515</v>
       </c>
       <c r="R60" t="n">
-        <v>6987078</v>
+        <v>6987120</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227135</v>
+        <v>121227128</v>
       </c>
       <c r="B61" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,42 +6966,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459252</v>
+        <v>459291</v>
       </c>
       <c r="R61" t="n">
-        <v>6987032</v>
+        <v>6987123</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7034,11 +7026,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7065,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227121</v>
+        <v>121227136</v>
       </c>
       <c r="B62" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7081,34 +7068,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459050</v>
+        <v>459339</v>
       </c>
       <c r="R62" t="n">
-        <v>6987112</v>
+        <v>6986928</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7141,6 +7136,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7167,10 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227127</v>
+        <v>121227100</v>
       </c>
       <c r="B63" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7183,21 +7183,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459310</v>
+        <v>459252</v>
       </c>
       <c r="R63" t="n">
-        <v>6987151</v>
+        <v>6987048</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7269,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227092</v>
+        <v>121227121</v>
       </c>
       <c r="B64" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7285,21 +7285,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459307</v>
+        <v>459050</v>
       </c>
       <c r="R64" t="n">
-        <v>6986981</v>
+        <v>6987112</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227098</v>
+        <v>121227119</v>
       </c>
       <c r="B65" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7387,21 +7387,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459468</v>
+        <v>459217</v>
       </c>
       <c r="R65" t="n">
-        <v>6987119</v>
+        <v>6987069</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7473,10 +7473,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227099</v>
+        <v>121227089</v>
       </c>
       <c r="B66" t="n">
-        <v>90731</v>
+        <v>91005</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7489,21 +7489,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459187</v>
+        <v>459514</v>
       </c>
       <c r="R66" t="n">
-        <v>6987057</v>
+        <v>6987120</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7575,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227104</v>
+        <v>121227127</v>
       </c>
       <c r="B67" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7591,21 +7591,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459343</v>
+        <v>459310</v>
       </c>
       <c r="R67" t="n">
-        <v>6987095</v>
+        <v>6987151</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227110</v>
+        <v>121227120</v>
       </c>
       <c r="B68" t="n">
-        <v>74704</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7689,25 +7689,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459494</v>
+        <v>459057</v>
       </c>
       <c r="R68" t="n">
-        <v>6987097</v>
+        <v>6987082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227126</v>
+        <v>121227094</v>
       </c>
       <c r="B69" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7795,21 +7795,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459333</v>
+        <v>458978</v>
       </c>
       <c r="R69" t="n">
-        <v>6987132</v>
+        <v>6987169</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227094</v>
+        <v>121227091</v>
       </c>
       <c r="B70" t="n">
-        <v>79688</v>
+        <v>74706</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7897,21 +7897,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458978</v>
+        <v>459295</v>
       </c>
       <c r="R70" t="n">
-        <v>6987169</v>
+        <v>6987078</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7983,10 +7983,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227097</v>
+        <v>121227104</v>
       </c>
       <c r="B71" t="n">
-        <v>74713</v>
+        <v>90719</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459089</v>
+        <v>459343</v>
       </c>
       <c r="R71" t="n">
-        <v>6987126</v>
+        <v>6987095</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8088,7 +8088,7 @@
         <v>121227123</v>
       </c>
       <c r="B72" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227125</v>
+        <v>121227135</v>
       </c>
       <c r="B73" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8203,34 +8203,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459256</v>
+        <v>459252</v>
       </c>
       <c r="R73" t="n">
-        <v>6987066</v>
+        <v>6987032</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8263,6 +8271,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8289,10 +8302,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227086</v>
+        <v>121227114</v>
       </c>
       <c r="B74" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8305,21 +8318,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8329,10 +8342,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459312</v>
+        <v>459383</v>
       </c>
       <c r="R74" t="n">
-        <v>6986982</v>
+        <v>6986968</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8391,10 +8404,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227116</v>
+        <v>121227118</v>
       </c>
       <c r="B75" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8431,10 +8444,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459437</v>
+        <v>459411</v>
       </c>
       <c r="R75" t="n">
-        <v>6987156</v>
+        <v>6987131</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8493,10 +8506,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227096</v>
+        <v>121227101</v>
       </c>
       <c r="B76" t="n">
-        <v>74713</v>
+        <v>90719</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8509,21 +8522,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8533,10 +8546,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459090</v>
+        <v>459430</v>
       </c>
       <c r="R76" t="n">
-        <v>6987125</v>
+        <v>6986932</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8595,10 +8608,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227120</v>
+        <v>121227105</v>
       </c>
       <c r="B77" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8611,21 +8624,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8635,10 +8648,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459057</v>
+        <v>459387</v>
       </c>
       <c r="R77" t="n">
-        <v>6987082</v>
+        <v>6987097</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8697,10 +8710,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227105</v>
+        <v>121227134</v>
       </c>
       <c r="B78" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8713,34 +8726,50 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459387</v>
+        <v>458986</v>
       </c>
       <c r="R78" t="n">
-        <v>6987097</v>
+        <v>6987138</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8773,6 +8802,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8799,10 +8833,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227124</v>
+        <v>121227115</v>
       </c>
       <c r="B79" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8839,10 +8873,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459222</v>
+        <v>459332</v>
       </c>
       <c r="R79" t="n">
-        <v>6987047</v>
+        <v>6986979</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8901,10 +8935,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227108</v>
+        <v>121227122</v>
       </c>
       <c r="B80" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8917,21 +8951,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8941,10 +8975,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459299</v>
+        <v>459010</v>
       </c>
       <c r="R80" t="n">
-        <v>6987083</v>
+        <v>6987146</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9003,10 +9037,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227103</v>
+        <v>121227131</v>
       </c>
       <c r="B81" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9019,21 +9053,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9043,10 +9077,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459515</v>
+        <v>459299</v>
       </c>
       <c r="R81" t="n">
-        <v>6987120</v>
+        <v>6986980</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9105,10 +9139,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227134</v>
+        <v>121227124</v>
       </c>
       <c r="B82" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9121,50 +9155,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458986</v>
+        <v>459222</v>
       </c>
       <c r="R82" t="n">
-        <v>6987138</v>
+        <v>6987047</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9197,11 +9215,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9228,10 +9241,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227112</v>
+        <v>121227110</v>
       </c>
       <c r="B83" t="n">
-        <v>74704</v>
+        <v>74705</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9268,10 +9281,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459315</v>
+        <v>459494</v>
       </c>
       <c r="R83" t="n">
-        <v>6987128</v>
+        <v>6987097</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9330,10 +9343,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227117</v>
+        <v>121227108</v>
       </c>
       <c r="B84" t="n">
-        <v>78607</v>
+        <v>82392</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9346,21 +9359,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9370,10 +9383,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459430</v>
+        <v>459299</v>
       </c>
       <c r="R84" t="n">
-        <v>6987144</v>
+        <v>6987083</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9432,10 +9445,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227129</v>
+        <v>121227096</v>
       </c>
       <c r="B85" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9448,21 +9461,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9472,10 +9485,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459255</v>
+        <v>459090</v>
       </c>
       <c r="R85" t="n">
-        <v>6987069</v>
+        <v>6987125</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9534,10 +9547,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227136</v>
+        <v>121227125</v>
       </c>
       <c r="B86" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9550,42 +9563,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459339</v>
+        <v>459256</v>
       </c>
       <c r="R86" t="n">
-        <v>6986928</v>
+        <v>6987066</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9618,11 +9623,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9649,10 +9649,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227122</v>
+        <v>121227092</v>
       </c>
       <c r="B87" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9665,21 +9665,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459010</v>
+        <v>459307</v>
       </c>
       <c r="R87" t="n">
-        <v>6987146</v>
+        <v>6986981</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9751,10 +9751,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227113</v>
+        <v>121227112</v>
       </c>
       <c r="B88" t="n">
-        <v>74704</v>
+        <v>74705</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9785,19 +9785,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459280</v>
+        <v>459315</v>
       </c>
       <c r="R88" t="n">
-        <v>6987044</v>
+        <v>6987128</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9832,18 +9829,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9862,10 +9853,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227102</v>
+        <v>121227098</v>
       </c>
       <c r="B89" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9878,21 +9869,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9902,10 +9893,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459461</v>
+        <v>459468</v>
       </c>
       <c r="R89" t="n">
-        <v>6987117</v>
+        <v>6987119</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9964,10 +9955,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227101</v>
+        <v>121227106</v>
       </c>
       <c r="B90" t="n">
-        <v>90713</v>
+        <v>82392</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9980,21 +9971,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10004,10 +9995,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459430</v>
+        <v>459365</v>
       </c>
       <c r="R90" t="n">
-        <v>6986932</v>
+        <v>6987091</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10066,10 +10057,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227109</v>
+        <v>121227111</v>
       </c>
       <c r="B91" t="n">
-        <v>82391</v>
+        <v>74705</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10078,25 +10069,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10106,10 +10097,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459277</v>
+        <v>459244</v>
       </c>
       <c r="R91" t="n">
-        <v>6987050</v>
+        <v>6987057</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10168,10 +10159,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227114</v>
+        <v>121227099</v>
       </c>
       <c r="B92" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10184,21 +10175,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10208,10 +10199,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459383</v>
+        <v>459187</v>
       </c>
       <c r="R92" t="n">
-        <v>6986968</v>
+        <v>6987057</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10270,10 +10261,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227089</v>
+        <v>121227129</v>
       </c>
       <c r="B93" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10286,21 +10277,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10310,10 +10301,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459514</v>
+        <v>459255</v>
       </c>
       <c r="R93" t="n">
-        <v>6987120</v>
+        <v>6987069</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10372,10 +10363,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227106</v>
+        <v>121227113</v>
       </c>
       <c r="B94" t="n">
-        <v>82391</v>
+        <v>74705</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10384,38 +10375,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459365</v>
+        <v>459280</v>
       </c>
       <c r="R94" t="n">
-        <v>6987091</v>
+        <v>6987044</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10450,12 +10444,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227131</v>
+        <v>121227088</v>
       </c>
       <c r="B95" t="n">
-        <v>78607</v>
+        <v>74698</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10486,25 +10486,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459299</v>
+        <v>459493</v>
       </c>
       <c r="R95" t="n">
-        <v>6986980</v>
+        <v>6987097</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227119</v>
+        <v>121227097</v>
       </c>
       <c r="B96" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10592,21 +10592,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459217</v>
+        <v>459089</v>
       </c>
       <c r="R96" t="n">
-        <v>6987069</v>
+        <v>6987126</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227111</v>
+        <v>121227117</v>
       </c>
       <c r="B97" t="n">
-        <v>74704</v>
+        <v>78608</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10690,25 +10690,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459244</v>
+        <v>459430</v>
       </c>
       <c r="R97" t="n">
-        <v>6987057</v>
+        <v>6987144</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -9241,10 +9241,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227110</v>
+        <v>121227108</v>
       </c>
       <c r="B83" t="n">
-        <v>74705</v>
+        <v>82392</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9253,25 +9253,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459494</v>
+        <v>459299</v>
       </c>
       <c r="R83" t="n">
-        <v>6987097</v>
+        <v>6987083</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9343,10 +9343,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227108</v>
+        <v>121227110</v>
       </c>
       <c r="B84" t="n">
-        <v>82392</v>
+        <v>74705</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9355,25 +9355,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459299</v>
+        <v>459494</v>
       </c>
       <c r="R84" t="n">
-        <v>6987083</v>
+        <v>6987097</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210315</v>
+        <v>121210346</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>74707</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,38 +2961,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459269</v>
+        <v>459235</v>
       </c>
       <c r="R22" t="n">
-        <v>6987021</v>
+        <v>6987465</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3025,11 +3021,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210351</v>
+        <v>121210347</v>
       </c>
       <c r="B23" t="n">
-        <v>90719</v>
+        <v>74707</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,21 +3063,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459109</v>
+        <v>459274</v>
       </c>
       <c r="R23" t="n">
-        <v>6987053</v>
+        <v>6987465</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3161,7 +3152,7 @@
         <v>121210334</v>
       </c>
       <c r="B24" t="n">
-        <v>74714</v>
+        <v>74715</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210336</v>
+        <v>121210352</v>
       </c>
       <c r="B25" t="n">
-        <v>74714</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459289</v>
+        <v>459272</v>
       </c>
       <c r="R25" t="n">
-        <v>6987454</v>
+        <v>6987314</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3362,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210325</v>
+        <v>121210320</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
+        <v>82393</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,25 +3365,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459361</v>
+        <v>459321</v>
       </c>
       <c r="R26" t="n">
-        <v>6986971</v>
+        <v>6987092</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3464,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210317</v>
+        <v>121210356</v>
       </c>
       <c r="B27" t="n">
-        <v>79725</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,25 +3467,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3504,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459209</v>
+        <v>459060</v>
       </c>
       <c r="R27" t="n">
-        <v>6986978</v>
+        <v>6987110</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3566,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210355</v>
+        <v>121210351</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,21 +3573,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3597,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459361</v>
+        <v>459109</v>
       </c>
       <c r="R28" t="n">
-        <v>6986994</v>
+        <v>6987053</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3668,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210319</v>
+        <v>121210328</v>
       </c>
       <c r="B29" t="n">
-        <v>57508</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3684,21 +3675,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3708,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459169</v>
+        <v>459363</v>
       </c>
       <c r="R29" t="n">
-        <v>6987016</v>
+        <v>6987053</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3770,10 +3761,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210326</v>
+        <v>121210350</v>
       </c>
       <c r="B30" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3782,25 +3773,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3810,10 +3801,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459248</v>
+        <v>459166</v>
       </c>
       <c r="R30" t="n">
-        <v>6987371</v>
+        <v>6987016</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3872,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210316</v>
+        <v>121210335</v>
       </c>
       <c r="B31" t="n">
-        <v>90715</v>
+        <v>74715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459238</v>
+        <v>459344</v>
       </c>
       <c r="R31" t="n">
-        <v>6986977</v>
+        <v>6987093</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3974,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210344</v>
+        <v>121210354</v>
       </c>
       <c r="B32" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3990,21 +3981,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4014,10 +4005,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459384</v>
+        <v>459368</v>
       </c>
       <c r="R32" t="n">
-        <v>6986948</v>
+        <v>6986963</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4076,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210323</v>
+        <v>121210313</v>
       </c>
       <c r="B33" t="n">
-        <v>57371</v>
+        <v>95652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4092,38 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459198</v>
+        <v>459274</v>
       </c>
       <c r="R33" t="n">
-        <v>6987270</v>
+        <v>6987056</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4156,11 +4143,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210360</v>
+        <v>121210325</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4199,25 +4181,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4227,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459359</v>
+        <v>459361</v>
       </c>
       <c r="R34" t="n">
-        <v>6987446</v>
+        <v>6986971</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4289,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210318</v>
+        <v>121210333</v>
       </c>
       <c r="B35" t="n">
-        <v>91005</v>
+        <v>74706</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4301,25 +4283,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4329,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459210</v>
+        <v>459276</v>
       </c>
       <c r="R35" t="n">
-        <v>6986977</v>
+        <v>6987463</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4391,10 +4373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210330</v>
+        <v>121210312</v>
       </c>
       <c r="B36" t="n">
-        <v>74705</v>
+        <v>74699</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4403,41 +4385,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>6439</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459263</v>
+        <v>459362</v>
       </c>
       <c r="R36" t="n">
-        <v>6987015</v>
+        <v>6987057</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4472,18 +4451,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4502,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210327</v>
+        <v>121210329</v>
       </c>
       <c r="B37" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4542,10 +4515,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459368</v>
+        <v>459208</v>
       </c>
       <c r="R37" t="n">
-        <v>6986960</v>
+        <v>6987442</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4604,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210328</v>
+        <v>121210316</v>
       </c>
       <c r="B38" t="n">
-        <v>90737</v>
+        <v>90716</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4620,21 +4593,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4644,10 +4617,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459363</v>
+        <v>459238</v>
       </c>
       <c r="R38" t="n">
-        <v>6987053</v>
+        <v>6986977</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4706,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210329</v>
+        <v>121210315</v>
       </c>
       <c r="B39" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4722,34 +4695,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459208</v>
+        <v>459269</v>
       </c>
       <c r="R39" t="n">
-        <v>6987442</v>
+        <v>6987021</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4782,6 +4759,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,10 +4790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210321</v>
+        <v>121210324</v>
       </c>
       <c r="B40" t="n">
-        <v>82392</v>
+        <v>91376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4820,25 +4802,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4848,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459138</v>
+        <v>459250</v>
       </c>
       <c r="R40" t="n">
-        <v>6987016</v>
+        <v>6987362</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4910,10 +4892,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210350</v>
+        <v>121210317</v>
       </c>
       <c r="B41" t="n">
-        <v>90719</v>
+        <v>79726</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4922,25 +4904,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4932,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459166</v>
+        <v>459209</v>
       </c>
       <c r="R41" t="n">
-        <v>6987016</v>
+        <v>6986978</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5012,10 +4994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210324</v>
+        <v>121210323</v>
       </c>
       <c r="B42" t="n">
-        <v>91375</v>
+        <v>57372</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5024,38 +5006,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459250</v>
+        <v>459198</v>
       </c>
       <c r="R42" t="n">
-        <v>6987362</v>
+        <v>6987270</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5088,6 +5074,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5114,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210335</v>
+        <v>121210345</v>
       </c>
       <c r="B43" t="n">
-        <v>74714</v>
+        <v>74707</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5130,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5154,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459344</v>
+        <v>459225</v>
       </c>
       <c r="R43" t="n">
-        <v>6987093</v>
+        <v>6987464</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5216,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210345</v>
+        <v>121210344</v>
       </c>
       <c r="B44" t="n">
-        <v>74706</v>
+        <v>74707</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5256,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459225</v>
+        <v>459384</v>
       </c>
       <c r="R44" t="n">
-        <v>6987464</v>
+        <v>6986948</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5318,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210333</v>
+        <v>121210318</v>
       </c>
       <c r="B45" t="n">
-        <v>74705</v>
+        <v>91006</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5330,25 +5321,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>492</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5358,10 +5349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459276</v>
+        <v>459210</v>
       </c>
       <c r="R45" t="n">
-        <v>6987463</v>
+        <v>6986977</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5420,7 +5411,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210346</v>
+        <v>121210331</v>
       </c>
       <c r="B46" t="n">
         <v>74706</v>
@@ -5432,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5460,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459235</v>
+        <v>459255</v>
       </c>
       <c r="R46" t="n">
-        <v>6987465</v>
+        <v>6987011</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5522,10 +5513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210354</v>
+        <v>121210326</v>
       </c>
       <c r="B47" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5534,25 +5525,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5562,10 +5553,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459368</v>
+        <v>459248</v>
       </c>
       <c r="R47" t="n">
-        <v>6986963</v>
+        <v>6987371</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5624,10 +5615,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210320</v>
+        <v>121210336</v>
       </c>
       <c r="B48" t="n">
-        <v>82392</v>
+        <v>74715</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,21 +5631,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5664,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459321</v>
+        <v>459289</v>
       </c>
       <c r="R48" t="n">
-        <v>6987092</v>
+        <v>6987454</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5726,10 +5717,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210312</v>
+        <v>121210355</v>
       </c>
       <c r="B49" t="n">
-        <v>74698</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,25 +5729,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5757,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459362</v>
+        <v>459361</v>
       </c>
       <c r="R49" t="n">
-        <v>6987057</v>
+        <v>6986994</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5828,10 +5819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210331</v>
+        <v>121210327</v>
       </c>
       <c r="B50" t="n">
-        <v>74705</v>
+        <v>90738</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,25 +5831,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459255</v>
+        <v>459368</v>
       </c>
       <c r="R50" t="n">
-        <v>6987011</v>
+        <v>6986960</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5930,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210347</v>
+        <v>121210360</v>
       </c>
       <c r="B51" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5946,21 +5937,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459274</v>
+        <v>459359</v>
       </c>
       <c r="R51" t="n">
-        <v>6987465</v>
+        <v>6987446</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6032,10 +6023,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210313</v>
+        <v>121210321</v>
       </c>
       <c r="B52" t="n">
-        <v>95651</v>
+        <v>82393</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,21 +6039,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6072,10 +6063,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459274</v>
+        <v>459138</v>
       </c>
       <c r="R52" t="n">
-        <v>6987056</v>
+        <v>6987016</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6134,10 +6125,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210356</v>
+        <v>121210330</v>
       </c>
       <c r="B53" t="n">
-        <v>78608</v>
+        <v>74706</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6146,38 +6137,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459060</v>
+        <v>459263</v>
       </c>
       <c r="R53" t="n">
-        <v>6987110</v>
+        <v>6987015</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6212,12 +6206,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210352</v>
+        <v>121210319</v>
       </c>
       <c r="B54" t="n">
-        <v>90719</v>
+        <v>57509</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459272</v>
+        <v>459169</v>
       </c>
       <c r="R54" t="n">
-        <v>6987314</v>
+        <v>6987016</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227126</v>
+        <v>121227086</v>
       </c>
       <c r="B55" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459333</v>
+        <v>459312</v>
       </c>
       <c r="R55" t="n">
-        <v>6987132</v>
+        <v>6986982</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227102</v>
+        <v>121227115</v>
       </c>
       <c r="B56" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459461</v>
+        <v>459332</v>
       </c>
       <c r="R56" t="n">
-        <v>6987117</v>
+        <v>6986979</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227086</v>
+        <v>121227119</v>
       </c>
       <c r="B57" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459312</v>
+        <v>459217</v>
       </c>
       <c r="R57" t="n">
-        <v>6986982</v>
+        <v>6987069</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227116</v>
+        <v>121227114</v>
       </c>
       <c r="B58" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459437</v>
+        <v>459383</v>
       </c>
       <c r="R58" t="n">
-        <v>6987156</v>
+        <v>6986968</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227109</v>
+        <v>121227112</v>
       </c>
       <c r="B59" t="n">
-        <v>82392</v>
+        <v>74706</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6758,25 +6758,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459277</v>
+        <v>459315</v>
       </c>
       <c r="R59" t="n">
-        <v>6987050</v>
+        <v>6987128</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227103</v>
+        <v>121227111</v>
       </c>
       <c r="B60" t="n">
-        <v>90719</v>
+        <v>74706</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6860,25 +6860,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459515</v>
+        <v>459244</v>
       </c>
       <c r="R60" t="n">
-        <v>6987120</v>
+        <v>6987057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227128</v>
+        <v>121227117</v>
       </c>
       <c r="B61" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459291</v>
+        <v>459430</v>
       </c>
       <c r="R61" t="n">
-        <v>6987123</v>
+        <v>6987144</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7052,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227136</v>
+        <v>121227104</v>
       </c>
       <c r="B62" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,42 +7068,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459339</v>
+        <v>459343</v>
       </c>
       <c r="R62" t="n">
-        <v>6986928</v>
+        <v>6987095</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7136,11 +7128,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7167,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227100</v>
+        <v>121227102</v>
       </c>
       <c r="B63" t="n">
-        <v>90737</v>
+        <v>90720</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7183,21 +7170,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459252</v>
+        <v>459461</v>
       </c>
       <c r="R63" t="n">
-        <v>6987048</v>
+        <v>6987117</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7269,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227121</v>
+        <v>121227128</v>
       </c>
       <c r="B64" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7309,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459050</v>
+        <v>459291</v>
       </c>
       <c r="R64" t="n">
-        <v>6987112</v>
+        <v>6987123</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7371,10 +7358,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227119</v>
+        <v>121227121</v>
       </c>
       <c r="B65" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7411,10 +7398,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459217</v>
+        <v>459050</v>
       </c>
       <c r="R65" t="n">
-        <v>6987069</v>
+        <v>6987112</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7473,10 +7460,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227089</v>
+        <v>121227123</v>
       </c>
       <c r="B66" t="n">
-        <v>91005</v>
+        <v>78609</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7489,21 +7476,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7513,10 +7500,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459514</v>
+        <v>458981</v>
       </c>
       <c r="R66" t="n">
-        <v>6987120</v>
+        <v>6987164</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7575,10 +7562,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227127</v>
+        <v>121227105</v>
       </c>
       <c r="B67" t="n">
-        <v>78608</v>
+        <v>82393</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7591,21 +7578,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7615,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459310</v>
+        <v>459387</v>
       </c>
       <c r="R67" t="n">
-        <v>6987151</v>
+        <v>6987097</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7677,10 +7664,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227120</v>
+        <v>121227094</v>
       </c>
       <c r="B68" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7693,21 +7680,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7717,10 +7704,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459057</v>
+        <v>458978</v>
       </c>
       <c r="R68" t="n">
-        <v>6987082</v>
+        <v>6987169</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7779,10 +7766,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227094</v>
+        <v>121227088</v>
       </c>
       <c r="B69" t="n">
-        <v>79689</v>
+        <v>74699</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7791,25 +7778,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7819,10 +7806,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458978</v>
+        <v>459493</v>
       </c>
       <c r="R69" t="n">
-        <v>6987169</v>
+        <v>6987097</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7881,10 +7868,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227091</v>
+        <v>121227092</v>
       </c>
       <c r="B70" t="n">
-        <v>74706</v>
+        <v>79690</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7897,21 +7884,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7921,10 +7908,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459295</v>
+        <v>459307</v>
       </c>
       <c r="R70" t="n">
-        <v>6987078</v>
+        <v>6986981</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7983,10 +7970,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227104</v>
+        <v>121227120</v>
       </c>
       <c r="B71" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7999,21 +7986,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8023,10 +8010,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459343</v>
+        <v>459057</v>
       </c>
       <c r="R71" t="n">
-        <v>6987095</v>
+        <v>6987082</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8085,10 +8072,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227123</v>
+        <v>121227135</v>
       </c>
       <c r="B72" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8101,34 +8088,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458981</v>
+        <v>459252</v>
       </c>
       <c r="R72" t="n">
-        <v>6987164</v>
+        <v>6987032</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8161,6 +8156,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8187,10 +8187,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227135</v>
+        <v>121227127</v>
       </c>
       <c r="B73" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8203,42 +8203,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459252</v>
+        <v>459310</v>
       </c>
       <c r="R73" t="n">
-        <v>6987032</v>
+        <v>6987151</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8271,11 +8263,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8302,10 +8289,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227114</v>
+        <v>121227098</v>
       </c>
       <c r="B74" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8318,21 +8305,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8342,10 +8329,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459383</v>
+        <v>459468</v>
       </c>
       <c r="R74" t="n">
-        <v>6986968</v>
+        <v>6987119</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8404,10 +8391,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227118</v>
+        <v>121227099</v>
       </c>
       <c r="B75" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8420,21 +8407,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8444,10 +8431,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459411</v>
+        <v>459187</v>
       </c>
       <c r="R75" t="n">
-        <v>6987131</v>
+        <v>6987057</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8506,10 +8493,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227101</v>
+        <v>121227096</v>
       </c>
       <c r="B76" t="n">
-        <v>90719</v>
+        <v>74715</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8522,21 +8509,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8546,10 +8533,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459430</v>
+        <v>459090</v>
       </c>
       <c r="R76" t="n">
-        <v>6986932</v>
+        <v>6987125</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8608,10 +8595,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227105</v>
+        <v>121227136</v>
       </c>
       <c r="B77" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8624,34 +8611,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459387</v>
+        <v>459339</v>
       </c>
       <c r="R77" t="n">
-        <v>6987097</v>
+        <v>6986928</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8684,6 +8679,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227134</v>
+        <v>121227106</v>
       </c>
       <c r="B78" t="n">
-        <v>57355</v>
+        <v>82393</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8726,50 +8726,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458986</v>
+        <v>459365</v>
       </c>
       <c r="R78" t="n">
-        <v>6987138</v>
+        <v>6987091</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8802,11 +8786,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8833,10 +8812,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227115</v>
+        <v>121227116</v>
       </c>
       <c r="B79" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8873,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459332</v>
+        <v>459437</v>
       </c>
       <c r="R79" t="n">
-        <v>6986979</v>
+        <v>6987156</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8935,10 +8914,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227122</v>
+        <v>121227124</v>
       </c>
       <c r="B80" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8975,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459010</v>
+        <v>459222</v>
       </c>
       <c r="R80" t="n">
-        <v>6987146</v>
+        <v>6987047</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9037,10 +9016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227131</v>
+        <v>121227103</v>
       </c>
       <c r="B81" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9053,21 +9032,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9077,10 +9056,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459299</v>
+        <v>459515</v>
       </c>
       <c r="R81" t="n">
-        <v>6986980</v>
+        <v>6987120</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9139,10 +9118,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227124</v>
+        <v>121227110</v>
       </c>
       <c r="B82" t="n">
-        <v>78608</v>
+        <v>74706</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9151,25 +9130,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9179,10 +9158,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459222</v>
+        <v>459494</v>
       </c>
       <c r="R82" t="n">
-        <v>6987047</v>
+        <v>6987097</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9244,7 +9223,7 @@
         <v>121227108</v>
       </c>
       <c r="B83" t="n">
-        <v>82392</v>
+        <v>82393</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9343,10 +9322,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227110</v>
+        <v>121227109</v>
       </c>
       <c r="B84" t="n">
-        <v>74705</v>
+        <v>82393</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9355,25 +9334,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9383,10 +9362,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459494</v>
+        <v>459277</v>
       </c>
       <c r="R84" t="n">
-        <v>6987097</v>
+        <v>6987050</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9445,10 +9424,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227096</v>
+        <v>121227129</v>
       </c>
       <c r="B85" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9461,21 +9440,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9485,10 +9464,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459090</v>
+        <v>459255</v>
       </c>
       <c r="R85" t="n">
-        <v>6987125</v>
+        <v>6987069</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9547,10 +9526,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227125</v>
+        <v>121227134</v>
       </c>
       <c r="B86" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9563,34 +9542,50 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459256</v>
+        <v>458986</v>
       </c>
       <c r="R86" t="n">
-        <v>6987066</v>
+        <v>6987138</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9623,6 +9618,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9649,10 +9649,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227092</v>
+        <v>121227113</v>
       </c>
       <c r="B87" t="n">
-        <v>79689</v>
+        <v>74706</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9661,38 +9661,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459307</v>
+        <v>459280</v>
       </c>
       <c r="R87" t="n">
-        <v>6986981</v>
+        <v>6987044</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9727,12 +9730,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9751,10 +9760,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227112</v>
+        <v>121227126</v>
       </c>
       <c r="B88" t="n">
-        <v>74705</v>
+        <v>78609</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9763,25 +9772,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9791,10 +9800,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459315</v>
+        <v>459333</v>
       </c>
       <c r="R88" t="n">
-        <v>6987128</v>
+        <v>6987132</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9853,10 +9862,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227098</v>
+        <v>121227131</v>
       </c>
       <c r="B89" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9869,21 +9878,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9893,10 +9902,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459468</v>
+        <v>459299</v>
       </c>
       <c r="R89" t="n">
-        <v>6987119</v>
+        <v>6986980</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9955,10 +9964,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227106</v>
+        <v>121227122</v>
       </c>
       <c r="B90" t="n">
-        <v>82392</v>
+        <v>78609</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9971,21 +9980,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9995,10 +10004,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459365</v>
+        <v>459010</v>
       </c>
       <c r="R90" t="n">
-        <v>6987091</v>
+        <v>6987146</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10057,10 +10066,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227111</v>
+        <v>121227091</v>
       </c>
       <c r="B91" t="n">
-        <v>74705</v>
+        <v>74707</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10069,25 +10078,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10097,10 +10106,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459244</v>
+        <v>459295</v>
       </c>
       <c r="R91" t="n">
-        <v>6987057</v>
+        <v>6987078</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10159,10 +10168,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227099</v>
+        <v>121227100</v>
       </c>
       <c r="B92" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10199,10 +10208,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459187</v>
+        <v>459252</v>
       </c>
       <c r="R92" t="n">
-        <v>6987057</v>
+        <v>6987048</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10261,10 +10270,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227129</v>
+        <v>121227101</v>
       </c>
       <c r="B93" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10277,21 +10286,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10301,10 +10310,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459255</v>
+        <v>459430</v>
       </c>
       <c r="R93" t="n">
-        <v>6987069</v>
+        <v>6986932</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10363,10 +10372,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227113</v>
+        <v>121227118</v>
       </c>
       <c r="B94" t="n">
-        <v>74705</v>
+        <v>78609</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10375,41 +10384,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459280</v>
+        <v>459411</v>
       </c>
       <c r="R94" t="n">
-        <v>6987044</v>
+        <v>6987131</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10444,18 +10450,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227088</v>
+        <v>121227125</v>
       </c>
       <c r="B95" t="n">
-        <v>74698</v>
+        <v>78609</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10486,25 +10486,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459493</v>
+        <v>459256</v>
       </c>
       <c r="R95" t="n">
-        <v>6987097</v>
+        <v>6987066</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227097</v>
+        <v>121227089</v>
       </c>
       <c r="B96" t="n">
-        <v>74714</v>
+        <v>91006</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10592,21 +10592,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459089</v>
+        <v>459514</v>
       </c>
       <c r="R96" t="n">
-        <v>6987126</v>
+        <v>6987120</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227117</v>
+        <v>121227097</v>
       </c>
       <c r="B97" t="n">
-        <v>78608</v>
+        <v>74715</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459430</v>
+        <v>459089</v>
       </c>
       <c r="R97" t="n">
-        <v>6987144</v>
+        <v>6987126</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -2945,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121210346</v>
+        <v>121210317</v>
       </c>
       <c r="B22" t="n">
-        <v>74707</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,25 +2957,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459235</v>
+        <v>459209</v>
       </c>
       <c r="R22" t="n">
-        <v>6987465</v>
+        <v>6986978</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121210347</v>
+        <v>121210315</v>
       </c>
       <c r="B23" t="n">
-        <v>74707</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3063,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459274</v>
+        <v>459269</v>
       </c>
       <c r="R23" t="n">
-        <v>6987465</v>
+        <v>6987021</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3123,6 +3127,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121210334</v>
+        <v>121210323</v>
       </c>
       <c r="B24" t="n">
-        <v>74715</v>
+        <v>57372</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,34 +3174,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459371</v>
+        <v>459198</v>
       </c>
       <c r="R24" t="n">
-        <v>6987042</v>
+        <v>6987270</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3225,6 +3238,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121210352</v>
+        <v>121210320</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459272</v>
+        <v>459321</v>
       </c>
       <c r="R25" t="n">
-        <v>6987314</v>
+        <v>6987092</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3353,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121210320</v>
+        <v>121210326</v>
       </c>
       <c r="B26" t="n">
-        <v>82393</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,25 +3383,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459321</v>
+        <v>459248</v>
       </c>
       <c r="R26" t="n">
-        <v>6987092</v>
+        <v>6987371</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3455,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121210356</v>
+        <v>121210350</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,21 +3489,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,10 +3513,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459060</v>
+        <v>459166</v>
       </c>
       <c r="R27" t="n">
-        <v>6987110</v>
+        <v>6987016</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3557,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121210351</v>
+        <v>121210333</v>
       </c>
       <c r="B28" t="n">
-        <v>90720</v>
+        <v>74706</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3569,25 +3587,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3597,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459109</v>
+        <v>459276</v>
       </c>
       <c r="R28" t="n">
-        <v>6987053</v>
+        <v>6987463</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3659,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121210328</v>
+        <v>121210352</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3675,21 +3693,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3699,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459363</v>
+        <v>459272</v>
       </c>
       <c r="R29" t="n">
-        <v>6987053</v>
+        <v>6987314</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3761,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121210350</v>
+        <v>121210354</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3777,21 +3795,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3801,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459166</v>
+        <v>459368</v>
       </c>
       <c r="R30" t="n">
-        <v>6987016</v>
+        <v>6986963</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3863,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121210335</v>
+        <v>121210330</v>
       </c>
       <c r="B31" t="n">
-        <v>74715</v>
+        <v>74706</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3875,38 +3893,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459344</v>
+        <v>459263</v>
       </c>
       <c r="R31" t="n">
-        <v>6987093</v>
+        <v>6987015</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3941,12 +3962,18 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3965,10 +3992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121210354</v>
+        <v>121210319</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3981,21 +4008,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4005,10 +4032,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459368</v>
+        <v>459169</v>
       </c>
       <c r="R32" t="n">
-        <v>6986963</v>
+        <v>6987016</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4067,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121210313</v>
+        <v>121210312</v>
       </c>
       <c r="B33" t="n">
-        <v>95652</v>
+        <v>74699</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4079,25 +4106,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,10 +4134,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459274</v>
+        <v>459362</v>
       </c>
       <c r="R33" t="n">
-        <v>6987056</v>
+        <v>6987057</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4169,10 +4196,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121210325</v>
+        <v>121210318</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4181,25 +4208,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4209,10 +4236,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459361</v>
+        <v>459210</v>
       </c>
       <c r="R34" t="n">
-        <v>6986971</v>
+        <v>6986977</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4271,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121210333</v>
+        <v>121210336</v>
       </c>
       <c r="B35" t="n">
-        <v>74706</v>
+        <v>74715</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4283,25 +4310,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4311,10 +4338,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459276</v>
+        <v>459289</v>
       </c>
       <c r="R35" t="n">
-        <v>6987463</v>
+        <v>6987454</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4373,10 +4400,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121210312</v>
+        <v>121210316</v>
       </c>
       <c r="B36" t="n">
-        <v>74699</v>
+        <v>90716</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4385,25 +4412,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4440,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459362</v>
+        <v>459238</v>
       </c>
       <c r="R36" t="n">
-        <v>6987057</v>
+        <v>6986977</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4475,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121210329</v>
+        <v>121210351</v>
       </c>
       <c r="B37" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,21 +4518,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4515,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459208</v>
+        <v>459109</v>
       </c>
       <c r="R37" t="n">
-        <v>6987442</v>
+        <v>6987053</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4577,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121210316</v>
+        <v>121210335</v>
       </c>
       <c r="B38" t="n">
-        <v>90716</v>
+        <v>74715</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4593,21 +4620,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4617,10 +4644,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459238</v>
+        <v>459344</v>
       </c>
       <c r="R38" t="n">
-        <v>6986977</v>
+        <v>6987093</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4679,10 +4706,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121210315</v>
+        <v>121210334</v>
       </c>
       <c r="B39" t="n">
-        <v>57356</v>
+        <v>74715</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4695,38 +4722,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459269</v>
+        <v>459371</v>
       </c>
       <c r="R39" t="n">
-        <v>6987021</v>
+        <v>6987042</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4759,11 +4782,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,10 +4808,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121210324</v>
+        <v>121210360</v>
       </c>
       <c r="B40" t="n">
-        <v>91376</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,25 +4820,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4830,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459250</v>
+        <v>459359</v>
       </c>
       <c r="R40" t="n">
-        <v>6987362</v>
+        <v>6987446</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4892,10 +4910,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121210317</v>
+        <v>121210345</v>
       </c>
       <c r="B41" t="n">
-        <v>79726</v>
+        <v>74707</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4904,25 +4922,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4932,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459209</v>
+        <v>459225</v>
       </c>
       <c r="R41" t="n">
-        <v>6986978</v>
+        <v>6987464</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4994,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121210323</v>
+        <v>121210346</v>
       </c>
       <c r="B42" t="n">
-        <v>57372</v>
+        <v>74707</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5010,38 +5028,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459198</v>
+        <v>459235</v>
       </c>
       <c r="R42" t="n">
-        <v>6987270</v>
+        <v>6987465</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5074,11 +5088,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,10 +5114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121210345</v>
+        <v>121210321</v>
       </c>
       <c r="B43" t="n">
-        <v>74707</v>
+        <v>82393</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5121,21 +5130,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459225</v>
+        <v>459138</v>
       </c>
       <c r="R43" t="n">
-        <v>6987464</v>
+        <v>6987016</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5207,10 +5216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121210344</v>
+        <v>121210329</v>
       </c>
       <c r="B44" t="n">
-        <v>74707</v>
+        <v>90738</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5223,21 +5232,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5256,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459384</v>
+        <v>459208</v>
       </c>
       <c r="R44" t="n">
-        <v>6986948</v>
+        <v>6987442</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5309,10 +5318,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121210318</v>
+        <v>121210328</v>
       </c>
       <c r="B45" t="n">
-        <v>91006</v>
+        <v>90738</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,21 +5334,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5349,10 +5358,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459210</v>
+        <v>459363</v>
       </c>
       <c r="R45" t="n">
-        <v>6986977</v>
+        <v>6987053</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5411,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121210331</v>
+        <v>121210324</v>
       </c>
       <c r="B46" t="n">
-        <v>74706</v>
+        <v>91376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5436,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>492</v>
+        <v>898</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5460,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459255</v>
+        <v>459250</v>
       </c>
       <c r="R46" t="n">
-        <v>6987011</v>
+        <v>6987362</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5513,10 +5522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121210326</v>
+        <v>121210327</v>
       </c>
       <c r="B47" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5525,25 +5534,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5553,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459248</v>
+        <v>459368</v>
       </c>
       <c r="R47" t="n">
-        <v>6987371</v>
+        <v>6986960</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5615,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121210336</v>
+        <v>121210313</v>
       </c>
       <c r="B48" t="n">
-        <v>74715</v>
+        <v>95652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5631,21 +5640,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459289</v>
+        <v>459274</v>
       </c>
       <c r="R48" t="n">
-        <v>6987454</v>
+        <v>6987056</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5717,7 +5726,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121210355</v>
+        <v>121210356</v>
       </c>
       <c r="B49" t="n">
         <v>78609</v>
@@ -5757,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459361</v>
+        <v>459060</v>
       </c>
       <c r="R49" t="n">
-        <v>6986994</v>
+        <v>6987110</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5819,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121210327</v>
+        <v>121210325</v>
       </c>
       <c r="B50" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5831,25 +5840,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5859,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459368</v>
+        <v>459361</v>
       </c>
       <c r="R50" t="n">
-        <v>6986960</v>
+        <v>6986971</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5921,10 +5930,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121210360</v>
+        <v>121210331</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5933,25 +5942,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5961,10 +5970,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459359</v>
+        <v>459255</v>
       </c>
       <c r="R51" t="n">
-        <v>6987446</v>
+        <v>6987011</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6023,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121210321</v>
+        <v>121210355</v>
       </c>
       <c r="B52" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6039,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6063,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459138</v>
+        <v>459361</v>
       </c>
       <c r="R52" t="n">
-        <v>6987016</v>
+        <v>6986994</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6125,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121210330</v>
+        <v>121210347</v>
       </c>
       <c r="B53" t="n">
-        <v>74706</v>
+        <v>74707</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6137,41 +6146,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459263</v>
+        <v>459274</v>
       </c>
       <c r="R53" t="n">
-        <v>6987015</v>
+        <v>6987465</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6206,18 +6212,12 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121210319</v>
+        <v>121210344</v>
       </c>
       <c r="B54" t="n">
-        <v>57509</v>
+        <v>74707</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459169</v>
+        <v>459384</v>
       </c>
       <c r="R54" t="n">
-        <v>6987016</v>
+        <v>6986948</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227086</v>
+        <v>121227125</v>
       </c>
       <c r="B55" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459312</v>
+        <v>459256</v>
       </c>
       <c r="R55" t="n">
-        <v>6986982</v>
+        <v>6987066</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227115</v>
+        <v>121227100</v>
       </c>
       <c r="B56" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459332</v>
+        <v>459252</v>
       </c>
       <c r="R56" t="n">
-        <v>6986979</v>
+        <v>6987048</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227119</v>
+        <v>121227108</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459217</v>
+        <v>459299</v>
       </c>
       <c r="R57" t="n">
-        <v>6987069</v>
+        <v>6987083</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227114</v>
+        <v>121227122</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459383</v>
+        <v>459010</v>
       </c>
       <c r="R58" t="n">
-        <v>6986968</v>
+        <v>6987146</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227112</v>
+        <v>121227120</v>
       </c>
       <c r="B59" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6758,25 +6758,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459315</v>
+        <v>459057</v>
       </c>
       <c r="R59" t="n">
-        <v>6987128</v>
+        <v>6987082</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227111</v>
+        <v>121227101</v>
       </c>
       <c r="B60" t="n">
-        <v>74706</v>
+        <v>90720</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6860,25 +6860,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459244</v>
+        <v>459430</v>
       </c>
       <c r="R60" t="n">
-        <v>6987057</v>
+        <v>6986932</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227117</v>
+        <v>121227135</v>
       </c>
       <c r="B61" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,34 +6966,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459430</v>
+        <v>459252</v>
       </c>
       <c r="R61" t="n">
-        <v>6987144</v>
+        <v>6987032</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7026,6 +7034,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7052,10 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227104</v>
+        <v>121227099</v>
       </c>
       <c r="B62" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,21 +7081,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7092,10 +7105,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459343</v>
+        <v>459187</v>
       </c>
       <c r="R62" t="n">
-        <v>6987095</v>
+        <v>6987057</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7154,10 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227102</v>
+        <v>121227111</v>
       </c>
       <c r="B63" t="n">
-        <v>90720</v>
+        <v>74706</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7166,25 +7179,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7194,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459461</v>
+        <v>459244</v>
       </c>
       <c r="R63" t="n">
-        <v>6987117</v>
+        <v>6987057</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7256,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227128</v>
+        <v>121227110</v>
       </c>
       <c r="B64" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7268,25 +7281,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7296,10 +7309,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459291</v>
+        <v>459494</v>
       </c>
       <c r="R64" t="n">
-        <v>6987123</v>
+        <v>6987097</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7358,7 +7371,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227121</v>
+        <v>121227127</v>
       </c>
       <c r="B65" t="n">
         <v>78609</v>
@@ -7398,10 +7411,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459050</v>
+        <v>459310</v>
       </c>
       <c r="R65" t="n">
-        <v>6987112</v>
+        <v>6987151</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7460,10 +7473,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227123</v>
+        <v>121227097</v>
       </c>
       <c r="B66" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7476,21 +7489,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7500,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458981</v>
+        <v>459089</v>
       </c>
       <c r="R66" t="n">
-        <v>6987164</v>
+        <v>6987126</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7562,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227105</v>
+        <v>121227131</v>
       </c>
       <c r="B67" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7578,21 +7591,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7602,10 +7615,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459387</v>
+        <v>459299</v>
       </c>
       <c r="R67" t="n">
-        <v>6987097</v>
+        <v>6986980</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7664,10 +7677,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227094</v>
+        <v>121227128</v>
       </c>
       <c r="B68" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7680,21 +7693,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7704,10 +7717,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458978</v>
+        <v>459291</v>
       </c>
       <c r="R68" t="n">
-        <v>6987169</v>
+        <v>6987123</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7868,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227092</v>
+        <v>121227115</v>
       </c>
       <c r="B70" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7884,21 +7897,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7908,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459307</v>
+        <v>459332</v>
       </c>
       <c r="R70" t="n">
-        <v>6986981</v>
+        <v>6986979</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7970,7 +7983,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227120</v>
+        <v>121227114</v>
       </c>
       <c r="B71" t="n">
         <v>78609</v>
@@ -8010,10 +8023,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459057</v>
+        <v>459383</v>
       </c>
       <c r="R71" t="n">
-        <v>6987082</v>
+        <v>6986968</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8072,7 +8085,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227135</v>
+        <v>121227136</v>
       </c>
       <c r="B72" t="n">
         <v>57356</v>
@@ -8120,10 +8133,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459252</v>
+        <v>459339</v>
       </c>
       <c r="R72" t="n">
-        <v>6987032</v>
+        <v>6986928</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8187,7 +8200,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227127</v>
+        <v>121227123</v>
       </c>
       <c r="B73" t="n">
         <v>78609</v>
@@ -8227,10 +8240,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459310</v>
+        <v>458981</v>
       </c>
       <c r="R73" t="n">
-        <v>6987151</v>
+        <v>6987164</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8289,10 +8302,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227098</v>
+        <v>121227121</v>
       </c>
       <c r="B74" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8305,21 +8318,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8329,10 +8342,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459468</v>
+        <v>459050</v>
       </c>
       <c r="R74" t="n">
-        <v>6987119</v>
+        <v>6987112</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8391,10 +8404,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227099</v>
+        <v>121227091</v>
       </c>
       <c r="B75" t="n">
-        <v>90738</v>
+        <v>74707</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8407,21 +8420,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8431,10 +8444,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459187</v>
+        <v>459295</v>
       </c>
       <c r="R75" t="n">
-        <v>6987057</v>
+        <v>6987078</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8493,10 +8506,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227096</v>
+        <v>121227098</v>
       </c>
       <c r="B76" t="n">
-        <v>74715</v>
+        <v>90738</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8509,21 +8522,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8533,10 +8546,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459090</v>
+        <v>459468</v>
       </c>
       <c r="R76" t="n">
-        <v>6987125</v>
+        <v>6987119</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8595,10 +8608,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227136</v>
+        <v>121227126</v>
       </c>
       <c r="B77" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8611,42 +8624,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459339</v>
+        <v>459333</v>
       </c>
       <c r="R77" t="n">
-        <v>6986928</v>
+        <v>6987132</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8679,11 +8684,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8710,10 +8710,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227106</v>
+        <v>121227118</v>
       </c>
       <c r="B78" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459365</v>
+        <v>459411</v>
       </c>
       <c r="R78" t="n">
-        <v>6987091</v>
+        <v>6987131</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227116</v>
+        <v>121227096</v>
       </c>
       <c r="B79" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459437</v>
+        <v>459090</v>
       </c>
       <c r="R79" t="n">
-        <v>6987156</v>
+        <v>6987125</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227124</v>
+        <v>121227117</v>
       </c>
       <c r="B80" t="n">
         <v>78609</v>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459222</v>
+        <v>459430</v>
       </c>
       <c r="R80" t="n">
-        <v>6987047</v>
+        <v>6987144</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9118,10 +9118,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227110</v>
+        <v>121227129</v>
       </c>
       <c r="B82" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9130,25 +9130,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459494</v>
+        <v>459255</v>
       </c>
       <c r="R82" t="n">
-        <v>6987097</v>
+        <v>6987069</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227108</v>
+        <v>121227106</v>
       </c>
       <c r="B83" t="n">
         <v>82393</v>
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459299</v>
+        <v>459365</v>
       </c>
       <c r="R83" t="n">
-        <v>6987083</v>
+        <v>6987091</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9424,10 +9424,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227129</v>
+        <v>121227089</v>
       </c>
       <c r="B85" t="n">
-        <v>78609</v>
+        <v>91006</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9440,21 +9440,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459255</v>
+        <v>459514</v>
       </c>
       <c r="R85" t="n">
-        <v>6987069</v>
+        <v>6987120</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9526,10 +9526,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227134</v>
+        <v>121227112</v>
       </c>
       <c r="B86" t="n">
-        <v>57356</v>
+        <v>74706</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9538,54 +9538,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458986</v>
+        <v>459315</v>
       </c>
       <c r="R86" t="n">
-        <v>6987138</v>
+        <v>6987128</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9618,11 +9602,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9760,10 +9739,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227126</v>
+        <v>121227092</v>
       </c>
       <c r="B88" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9776,21 +9755,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9800,10 +9779,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459333</v>
+        <v>459307</v>
       </c>
       <c r="R88" t="n">
-        <v>6987132</v>
+        <v>6986981</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9862,7 +9841,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227131</v>
+        <v>121227124</v>
       </c>
       <c r="B89" t="n">
         <v>78609</v>
@@ -9902,10 +9881,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459299</v>
+        <v>459222</v>
       </c>
       <c r="R89" t="n">
-        <v>6986980</v>
+        <v>6987047</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9964,10 +9943,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227122</v>
+        <v>121227105</v>
       </c>
       <c r="B90" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9980,21 +9959,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10004,10 +9983,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459010</v>
+        <v>459387</v>
       </c>
       <c r="R90" t="n">
-        <v>6987146</v>
+        <v>6987097</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10066,10 +10045,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227091</v>
+        <v>121227086</v>
       </c>
       <c r="B91" t="n">
-        <v>74707</v>
+        <v>79691</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10082,21 +10061,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10106,10 +10085,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459295</v>
+        <v>459312</v>
       </c>
       <c r="R91" t="n">
-        <v>6987078</v>
+        <v>6986982</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10168,10 +10147,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227100</v>
+        <v>121227119</v>
       </c>
       <c r="B92" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10184,21 +10163,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10208,10 +10187,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459252</v>
+        <v>459217</v>
       </c>
       <c r="R92" t="n">
-        <v>6987048</v>
+        <v>6987069</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10270,10 +10249,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227101</v>
+        <v>121227116</v>
       </c>
       <c r="B93" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10286,21 +10265,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10310,10 +10289,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459430</v>
+        <v>459437</v>
       </c>
       <c r="R93" t="n">
-        <v>6986932</v>
+        <v>6987156</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10372,10 +10351,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227118</v>
+        <v>121227102</v>
       </c>
       <c r="B94" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10388,21 +10367,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10412,10 +10391,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459411</v>
+        <v>459461</v>
       </c>
       <c r="R94" t="n">
-        <v>6987131</v>
+        <v>6987117</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10474,10 +10453,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227125</v>
+        <v>121227094</v>
       </c>
       <c r="B95" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10490,21 +10469,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10514,10 +10493,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459256</v>
+        <v>458978</v>
       </c>
       <c r="R95" t="n">
-        <v>6987066</v>
+        <v>6987169</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10576,10 +10555,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227089</v>
+        <v>121227104</v>
       </c>
       <c r="B96" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10592,21 +10571,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10616,10 +10595,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459514</v>
+        <v>459343</v>
       </c>
       <c r="R96" t="n">
-        <v>6987120</v>
+        <v>6987095</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10678,10 +10657,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227097</v>
+        <v>121227134</v>
       </c>
       <c r="B97" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10694,34 +10673,50 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459089</v>
+        <v>458986</v>
       </c>
       <c r="R97" t="n">
-        <v>6987126</v>
+        <v>6987138</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10754,6 +10749,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 48997-2024 artfynd.xlsx
+++ b/artfynd/A 48997-2024 artfynd.xlsx
@@ -6338,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121227125</v>
+        <v>121227112</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6350,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459256</v>
+        <v>459315</v>
       </c>
       <c r="R55" t="n">
-        <v>6987066</v>
+        <v>6987128</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121227100</v>
+        <v>121227114</v>
       </c>
       <c r="B56" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459252</v>
+        <v>459383</v>
       </c>
       <c r="R56" t="n">
-        <v>6987048</v>
+        <v>6986968</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121227108</v>
+        <v>121227131</v>
       </c>
       <c r="B57" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6585,7 +6585,7 @@
         <v>459299</v>
       </c>
       <c r="R57" t="n">
-        <v>6987083</v>
+        <v>6986980</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121227122</v>
+        <v>121227106</v>
       </c>
       <c r="B58" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459010</v>
+        <v>459365</v>
       </c>
       <c r="R58" t="n">
-        <v>6987146</v>
+        <v>6987091</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121227120</v>
+        <v>121227097</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459057</v>
+        <v>459089</v>
       </c>
       <c r="R59" t="n">
-        <v>6987082</v>
+        <v>6987126</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121227101</v>
+        <v>121227109</v>
       </c>
       <c r="B60" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6864,21 +6864,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459430</v>
+        <v>459277</v>
       </c>
       <c r="R60" t="n">
-        <v>6986932</v>
+        <v>6987050</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121227135</v>
+        <v>121227128</v>
       </c>
       <c r="B61" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,42 +6966,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459252</v>
+        <v>459291</v>
       </c>
       <c r="R61" t="n">
-        <v>6987032</v>
+        <v>6987123</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7034,11 +7026,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7065,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121227099</v>
+        <v>121227127</v>
       </c>
       <c r="B62" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7081,21 +7068,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7105,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459187</v>
+        <v>459310</v>
       </c>
       <c r="R62" t="n">
-        <v>6987057</v>
+        <v>6987151</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7167,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121227111</v>
+        <v>121227129</v>
       </c>
       <c r="B63" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7179,25 +7166,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459244</v>
+        <v>459255</v>
       </c>
       <c r="R63" t="n">
-        <v>6987057</v>
+        <v>6987069</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7269,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121227110</v>
+        <v>121227123</v>
       </c>
       <c r="B64" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7281,25 +7268,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7309,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459494</v>
+        <v>458981</v>
       </c>
       <c r="R64" t="n">
-        <v>6987097</v>
+        <v>6987164</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7371,10 +7358,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121227127</v>
+        <v>121227091</v>
       </c>
       <c r="B65" t="n">
-        <v>78609</v>
+        <v>74707</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7387,21 +7374,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7411,10 +7398,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459310</v>
+        <v>459295</v>
       </c>
       <c r="R65" t="n">
-        <v>6987151</v>
+        <v>6987078</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7473,10 +7460,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121227097</v>
+        <v>121227101</v>
       </c>
       <c r="B66" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7489,21 +7476,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7513,10 +7500,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459089</v>
+        <v>459430</v>
       </c>
       <c r="R66" t="n">
-        <v>6987126</v>
+        <v>6986932</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7575,10 +7562,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121227131</v>
+        <v>121227111</v>
       </c>
       <c r="B67" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7587,25 +7574,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7615,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459299</v>
+        <v>459244</v>
       </c>
       <c r="R67" t="n">
-        <v>6986980</v>
+        <v>6987057</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7677,10 +7664,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121227128</v>
+        <v>121227089</v>
       </c>
       <c r="B68" t="n">
-        <v>78609</v>
+        <v>91006</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7693,21 +7680,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7717,10 +7704,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459291</v>
+        <v>459514</v>
       </c>
       <c r="R68" t="n">
-        <v>6987123</v>
+        <v>6987120</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7779,10 +7766,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121227088</v>
+        <v>121227113</v>
       </c>
       <c r="B69" t="n">
-        <v>74699</v>
+        <v>74706</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7791,38 +7778,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459493</v>
+        <v>459280</v>
       </c>
       <c r="R69" t="n">
-        <v>6987097</v>
+        <v>6987044</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7857,12 +7847,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7881,10 +7877,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121227115</v>
+        <v>121227100</v>
       </c>
       <c r="B70" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7897,21 +7893,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7921,10 +7917,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459332</v>
+        <v>459252</v>
       </c>
       <c r="R70" t="n">
-        <v>6986979</v>
+        <v>6987048</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7983,10 +7979,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121227114</v>
+        <v>121227088</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7995,25 +7991,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8023,10 +8019,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459383</v>
+        <v>459493</v>
       </c>
       <c r="R71" t="n">
-        <v>6986968</v>
+        <v>6987097</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8085,10 +8081,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121227136</v>
+        <v>121227105</v>
       </c>
       <c r="B72" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8101,42 +8097,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459339</v>
+        <v>459387</v>
       </c>
       <c r="R72" t="n">
-        <v>6986928</v>
+        <v>6987097</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8169,11 +8157,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8200,10 +8183,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121227123</v>
+        <v>121227110</v>
       </c>
       <c r="B73" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8212,25 +8195,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8240,10 +8223,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458981</v>
+        <v>459494</v>
       </c>
       <c r="R73" t="n">
-        <v>6987164</v>
+        <v>6987097</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8302,7 +8285,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121227121</v>
+        <v>121227118</v>
       </c>
       <c r="B74" t="n">
         <v>78609</v>
@@ -8342,10 +8325,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>459050</v>
+        <v>459411</v>
       </c>
       <c r="R74" t="n">
-        <v>6987112</v>
+        <v>6987131</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8404,10 +8387,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121227091</v>
+        <v>121227126</v>
       </c>
       <c r="B75" t="n">
-        <v>74707</v>
+        <v>78609</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8420,21 +8403,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8444,10 +8427,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>459295</v>
+        <v>459333</v>
       </c>
       <c r="R75" t="n">
-        <v>6987078</v>
+        <v>6987132</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8506,10 +8489,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121227098</v>
+        <v>121227094</v>
       </c>
       <c r="B76" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8522,21 +8505,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8546,10 +8529,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459468</v>
+        <v>458978</v>
       </c>
       <c r="R76" t="n">
-        <v>6987119</v>
+        <v>6987169</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8608,10 +8591,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121227126</v>
+        <v>121227096</v>
       </c>
       <c r="B77" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8624,21 +8607,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8648,10 +8631,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459333</v>
+        <v>459090</v>
       </c>
       <c r="R77" t="n">
-        <v>6987132</v>
+        <v>6987125</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8710,7 +8693,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121227118</v>
+        <v>121227119</v>
       </c>
       <c r="B78" t="n">
         <v>78609</v>
@@ -8750,10 +8733,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459411</v>
+        <v>459217</v>
       </c>
       <c r="R78" t="n">
-        <v>6987131</v>
+        <v>6987069</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8812,10 +8795,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121227096</v>
+        <v>121227120</v>
       </c>
       <c r="B79" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8828,21 +8811,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8852,10 +8835,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459090</v>
+        <v>459057</v>
       </c>
       <c r="R79" t="n">
-        <v>6987125</v>
+        <v>6987082</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8914,10 +8897,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121227117</v>
+        <v>121227086</v>
       </c>
       <c r="B80" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8930,21 +8913,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8954,10 +8937,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459430</v>
+        <v>459312</v>
       </c>
       <c r="R80" t="n">
-        <v>6987144</v>
+        <v>6986982</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9016,10 +8999,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121227103</v>
+        <v>121227092</v>
       </c>
       <c r="B81" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9032,21 +9015,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9056,10 +9039,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>459515</v>
+        <v>459307</v>
       </c>
       <c r="R81" t="n">
-        <v>6987120</v>
+        <v>6986981</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9118,10 +9101,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121227129</v>
+        <v>121227136</v>
       </c>
       <c r="B82" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9134,34 +9117,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>459255</v>
+        <v>459339</v>
       </c>
       <c r="R82" t="n">
-        <v>6987069</v>
+        <v>6986928</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9194,6 +9185,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9220,10 +9216,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121227106</v>
+        <v>121227121</v>
       </c>
       <c r="B83" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9236,21 +9232,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9260,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>459365</v>
+        <v>459050</v>
       </c>
       <c r="R83" t="n">
-        <v>6987091</v>
+        <v>6987112</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9322,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121227109</v>
+        <v>121227102</v>
       </c>
       <c r="B84" t="n">
-        <v>82393</v>
+        <v>90720</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9338,21 +9334,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9362,10 +9358,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459277</v>
+        <v>459461</v>
       </c>
       <c r="R84" t="n">
-        <v>6987050</v>
+        <v>6987117</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9424,10 +9420,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121227089</v>
+        <v>121227135</v>
       </c>
       <c r="B85" t="n">
-        <v>91006</v>
+        <v>57356</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9440,34 +9436,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459514</v>
+        <v>459252</v>
       </c>
       <c r="R85" t="n">
-        <v>6987120</v>
+        <v>6987032</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9500,6 +9504,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9526,10 +9535,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121227112</v>
+        <v>121227124</v>
       </c>
       <c r="B86" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9538,25 +9547,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9566,10 +9575,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>459315</v>
+        <v>459222</v>
       </c>
       <c r="R86" t="n">
-        <v>6987128</v>
+        <v>6987047</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9628,10 +9637,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121227113</v>
+        <v>121227108</v>
       </c>
       <c r="B87" t="n">
-        <v>74706</v>
+        <v>82393</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9640,41 +9649,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>459280</v>
+        <v>459299</v>
       </c>
       <c r="R87" t="n">
-        <v>6987044</v>
+        <v>6987083</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9709,18 +9715,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9739,10 +9739,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121227092</v>
+        <v>121227115</v>
       </c>
       <c r="B88" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9755,21 +9755,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459307</v>
+        <v>459332</v>
       </c>
       <c r="R88" t="n">
-        <v>6986981</v>
+        <v>6986979</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9841,10 +9841,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121227124</v>
+        <v>121227104</v>
       </c>
       <c r="B89" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9857,21 +9857,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459222</v>
+        <v>459343</v>
       </c>
       <c r="R89" t="n">
-        <v>6987047</v>
+        <v>6987095</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9943,10 +9943,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121227105</v>
+        <v>121227116</v>
       </c>
       <c r="B90" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9959,21 +9959,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9983,10 +9983,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459387</v>
+        <v>459437</v>
       </c>
       <c r="R90" t="n">
-        <v>6987097</v>
+        <v>6987156</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10045,10 +10045,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121227086</v>
+        <v>121227134</v>
       </c>
       <c r="B91" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10061,34 +10061,50 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459312</v>
+        <v>458986</v>
       </c>
       <c r="R91" t="n">
-        <v>6986982</v>
+        <v>6987138</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10121,6 +10137,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10147,7 +10168,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121227119</v>
+        <v>121227122</v>
       </c>
       <c r="B92" t="n">
         <v>78609</v>
@@ -10187,10 +10208,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459217</v>
+        <v>459010</v>
       </c>
       <c r="R92" t="n">
-        <v>6987069</v>
+        <v>6987146</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10249,10 +10270,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121227116</v>
+        <v>121227098</v>
       </c>
       <c r="B93" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10265,21 +10286,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10289,10 +10310,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459437</v>
+        <v>459468</v>
       </c>
       <c r="R93" t="n">
-        <v>6987156</v>
+        <v>6987119</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10351,10 +10372,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121227102</v>
+        <v>121227099</v>
       </c>
       <c r="B94" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10367,21 +10388,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10391,10 +10412,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459461</v>
+        <v>459187</v>
       </c>
       <c r="R94" t="n">
-        <v>6987117</v>
+        <v>6987057</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10453,10 +10474,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121227094</v>
+        <v>121227103</v>
       </c>
       <c r="B95" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10469,21 +10490,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10493,10 +10514,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458978</v>
+        <v>459515</v>
       </c>
       <c r="R95" t="n">
-        <v>6987169</v>
+        <v>6987120</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10555,10 +10576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121227104</v>
+        <v>121227117</v>
       </c>
       <c r="B96" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10571,21 +10592,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10595,10 +10616,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459343</v>
+        <v>459430</v>
       </c>
       <c r="R96" t="n">
-        <v>6987095</v>
+        <v>6987144</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10657,10 +10678,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121227134</v>
+        <v>121227125</v>
       </c>
       <c r="B97" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10673,50 +10694,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458986</v>
+        <v>459256</v>
       </c>
       <c r="R97" t="n">
-        <v>6987138</v>
+        <v>6987066</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10749,11 +10754,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD97" t="b">
